--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_3FA3112190F2E404F161B51768A2211586063D4F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42782C79-B455-4D65-B076-A4E8E069D3AF}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="11_3FA3112190F2E404F161B51768A2211586063D4F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB9B05CB-FA39-42E7-B12B-FECF8C0F6298}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1452" uniqueCount="976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="984">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -2956,16 +2956,40 @@
     <t>Environment gate + D1-D13 approval + blockers cleared</t>
   </si>
   <si>
-    <t>Gate now PASSES: Node v24.19.0, npm 11.17.0, npm ping PONG, git 2.35.1, no proxy or TLS interception. All D1-D13 settled (11 as recommended; D9 and D13 amended). Stray home-level .git confirmed gone; git init -b main run inside the project folder with .gitignore written before any commit - git status shows 5 files, none from the user profile. No commit made yet.</t>
-  </si>
-  <si>
-    <t>B1 and B2 CLOSED. Two new open items: B5 - the project sits in a syncing corporate OneDrive folder, so node_modules will cause sync thrash and EPERM/EBUSY install failures once npm install runs; recommend relocating outside OneDrive before CHUNK 01. B6 - git user.email is the work address raymund.bermudes@gdslinkasia.com, which would be permanent and public in the commit history of a personal portfolio; set a repo-local identity before the first commit.</t>
-  </si>
-  <si>
-    <t>Owner decides B5 (project location) and B6 (commit identity), then CHUNK 01. CHUNK 00 needs neither and is the critical path.</t>
-  </si>
-  <si>
     <t>Ready to start</t>
+  </si>
+  <si>
+    <t>Raymund Ryan Bermudes</t>
+  </si>
+  <si>
+    <t>D14</t>
+  </si>
+  <si>
+    <t>GitHub repository visibility</t>
+  </si>
+  <si>
+    <t>Public repo; public with planning docs excluded; public with docs sanitised; private repo</t>
+  </si>
+  <si>
+    <t>PRIVATE repository</t>
+  </si>
+  <si>
+    <t>Not anticipated in the discovery report - raised when the first commit was prepared. A scan of the four planning documents found CTBC, CASECenter and SBC named throughout (CLAUDE.md, HANDOFF.md, PHASE-1-DISCOVERY.md and this workbook), and PHASE-1-DISCOVERY.md states that the SBC engagement involved security remediation - the exact association D5 places at Abstracted tier. A public repository would publish what D5 forbids, and git history is permanent: deleting files later does not remove them from history, existing clones or cached views. Vercel deploys from a private repo on the Hobby plan with no change to the site.</t>
+  </si>
+  <si>
+    <t>CRITICAL and IRREVERSIBLE if wrong. Never make this repo public without first rewriting history. Repo privacy does NOT relax D5 for the published site, and Vercel preview deployments remain publicly addressable - confirm preview protection at CHUNK 01.</t>
+  </si>
+  <si>
+    <t>DECIDED by owner 2026-09-22 - Private</t>
+  </si>
+  <si>
+    <t>Gate now PASSES: Node v24.19.0, npm 11.17.0, npm ping PONG, git 2.35.1, no proxy or TLS interception. All D1-D13 settled (11 as recommended; D9 and D13 amended), plus new D14. Stray home-level .git confirmed gone; git init -b main run inside the project folder; .gitignore written before any commit; repo-local user.email set to the GitHub noreply address with global config untouched. Commits ad51196 (planning artefacts) and 77f8cd1 (D14 + blockers closed).</t>
+  </si>
+  <si>
+    <t>B1, B2, B5 and B6 all CLOSED. New decision D14 raised and settled: a pre-commit scan found client names throughout the planning docs, so the GitHub repository must be PRIVATE. Remaining OneDrive mitigation: exclude node_modules from sync once CHUNK 01 creates it, and suspect OneDrive first if npm install fails with EPERM or EBUSY.</t>
+  </si>
+  <si>
+    <t>Owner creates an empty PRIVATE GitHub repo and a Vercel account; then CHUNK 01. CHUNK 00 needs neither and remains the critical path.</t>
   </si>
 </sst>
 </file>
@@ -3084,7 +3108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3114,6 +3138,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3448,7 +3473,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>973</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4000,19 +4025,19 @@
         <v>971</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>972</v>
+        <v>981</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>970</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>973</v>
+        <v>982</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>974</v>
+        <v>983</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -4063,7 +4088,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4438,6 +4463,32 @@
       </c>
       <c r="H14" s="4" t="s">
         <v>966</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>555</v>
+      </c>
+      <c r="B15" t="s">
+        <v>974</v>
+      </c>
+      <c r="C15" t="s">
+        <v>975</v>
+      </c>
+      <c r="D15" t="s">
+        <v>976</v>
+      </c>
+      <c r="E15" t="s">
+        <v>977</v>
+      </c>
+      <c r="F15" t="s">
+        <v>978</v>
+      </c>
+      <c r="G15" t="s">
+        <v>979</v>
+      </c>
+      <c r="H15" t="s">
+        <v>980</v>
       </c>
     </row>
   </sheetData>

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RaymundBermudes\OneDrive - GDS Link, LLC\Documents\Rr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_3FA3112190F2E404F161B51768A2211586063D4F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB9B05CB-FA39-42E7-B12B-FECF8C0F6298}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD11F8FE-0DB8-4702-B965-22DAC0583F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="983">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -2950,15 +2950,6 @@
     <t>Not used - no engagement is published at Named tier</t>
   </si>
   <si>
-    <t>HANDOFF.md</t>
-  </si>
-  <si>
-    <t>Environment gate + D1-D13 approval + blockers cleared</t>
-  </si>
-  <si>
-    <t>Ready to start</t>
-  </si>
-  <si>
     <t>Raymund Ryan Bermudes</t>
   </si>
   <si>
@@ -2983,13 +2974,19 @@
     <t>DECIDED by owner 2026-09-22 - Private</t>
   </si>
   <si>
-    <t>Gate now PASSES: Node v24.19.0, npm 11.17.0, npm ping PONG, git 2.35.1, no proxy or TLS interception. All D1-D13 settled (11 as recommended; D9 and D13 amended), plus new D14. Stray home-level .git confirmed gone; git init -b main run inside the project folder; .gitignore written before any commit; repo-local user.email set to the GitHub noreply address with global config untouched. Commits ad51196 (planning artefacts) and 77f8cd1 (D14 + blockers closed).</t>
-  </si>
-  <si>
-    <t>B1, B2, B5 and B6 all CLOSED. New decision D14 raised and settled: a pre-commit scan found client names throughout the planning docs, so the GitHub repository must be PRIVATE. Remaining OneDrive mitigation: exclude node_modules from sync once CHUNK 01 creates it, and suspect OneDrive first if npm install fails with EPERM or EBUSY.</t>
-  </si>
-  <si>
-    <t>Owner creates an empty PRIVATE GitHub repo and a Vercel account; then CHUNK 01. CHUNK 00 needs neither and remains the critical path.</t>
+    <t>CHUNK 01 - project foundation + security headers</t>
+  </si>
+  <si>
+    <t>Environment gate PASSES (Node v24.19.0, npm 11.17.0, npm ping PONG). All D1-D14 settled. Repo re-rooted, .gitignore and commit identity set. CHUNK 01 scaffolded: Astro 7.3.3 static, TypeScript strict, @astrojs/check, engines node &gt;=22.12.0 (verified against the registry, not assumed). vercel.json carries CSP, HSTS, X-Content-Type-Options, Referrer-Policy, Permissions-Policy, X-Frame-Options, COOP, CORP and immutable caching for hashed assets. Astro build telemetry disabled. Placeholder home page with noindex. Tailwind, MDX and the real pages deliberately deferred to their own chunks.</t>
+  </si>
+  <si>
+    <t>Commits ad51196, 77f8cd1, ac73cdb, b1f806c</t>
+  </si>
+  <si>
+    <t>CHUNK 01 is NOT complete: the deploy is outstanding and needs a private GitHub repo URL from the owner. Security headers are therefore UNPROVEN - vercel.json has no effect on the dev server and must be verified against a live deployment. astro.config.mjs `site` is still commented out and CHUNK 15 cannot complete without it.</t>
+  </si>
+  <si>
+    <t>Owner supplies the private GitHub repo URL; push, import to Vercel (Hobby), set `site`, then verify headers against the deployment. CHUNK 02 (design system) and CHUNK 04 (content layer) are unblocked and can start in parallel. CHUNK 00 remains the critical path.</t>
   </si>
 </sst>
 </file>
@@ -3134,11 +3131,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3449,13 +3446,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
     </row>
     <row r="2" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -3473,7 +3470,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4022,22 +4019,22 @@
         <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>970</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>983</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>972</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -4466,29 +4463,29 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="9" t="s">
         <v>555</v>
       </c>
       <c r="B15" t="s">
+        <v>971</v>
+      </c>
+      <c r="C15" t="s">
+        <v>972</v>
+      </c>
+      <c r="D15" t="s">
+        <v>973</v>
+      </c>
+      <c r="E15" t="s">
         <v>974</v>
       </c>
-      <c r="C15" t="s">
+      <c r="F15" t="s">
         <v>975</v>
       </c>
-      <c r="D15" t="s">
+      <c r="G15" t="s">
         <v>976</v>
       </c>
-      <c r="E15" t="s">
+      <c r="H15" t="s">
         <v>977</v>
-      </c>
-      <c r="F15" t="s">
-        <v>978</v>
-      </c>
-      <c r="G15" t="s">
-        <v>979</v>
-      </c>
-      <c r="H15" t="s">
-        <v>980</v>
       </c>
     </row>
   </sheetData>

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RaymundBermudes\OneDrive - GDS Link, LLC\Documents\Rr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD11F8FE-0DB8-4702-B965-22DAC0583F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A649B4-0AE9-4B43-BDA5-79CDD1922589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="983">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="984">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -2977,16 +2977,19 @@
     <t>CHUNK 01 - project foundation + security headers</t>
   </si>
   <si>
-    <t>Environment gate PASSES (Node v24.19.0, npm 11.17.0, npm ping PONG). All D1-D14 settled. Repo re-rooted, .gitignore and commit identity set. CHUNK 01 scaffolded: Astro 7.3.3 static, TypeScript strict, @astrojs/check, engines node &gt;=22.12.0 (verified against the registry, not assumed). vercel.json carries CSP, HSTS, X-Content-Type-Options, Referrer-Policy, Permissions-Policy, X-Frame-Options, COOP, CORP and immutable caching for hashed assets. Astro build telemetry disabled. Placeholder home page with noindex. Tailwind, MDX and the real pages deliberately deferred to their own chunks.</t>
-  </si>
-  <si>
-    <t>Commits ad51196, 77f8cd1, ac73cdb, b1f806c</t>
-  </si>
-  <si>
-    <t>CHUNK 01 is NOT complete: the deploy is outstanding and needs a private GitHub repo URL from the owner. Security headers are therefore UNPROVEN - vercel.json has no effect on the dev server and must be verified against a live deployment. astro.config.mjs `site` is still commented out and CHUNK 15 cannot complete without it.</t>
-  </si>
-  <si>
-    <t>Owner supplies the private GitHub repo URL; push, import to Vercel (Hobby), set `site`, then verify headers against the deployment. CHUNK 02 (design system) and CHUNK 04 (content layer) are unblocked and can start in parallel. CHUNK 00 remains the critical path.</t>
+    <t>CHUNK 01 built and DEPLOYED. Astro 7.3.3 static, TypeScript strict, engines node &gt;=22.12.0 (verified against the registry). Live at https://raymundbermudes.vercel.app on the Hobby plan from the private repo rrcreations69/ClaudePortfolio, deployed by the personal account. All NINE security headers verified against a real HTTP response from the live deployment, not against vercel.json: CSP, HSTS, X-Content-Type-Options, Referrer-Policy, Permissions-Policy, X-Frame-Options, COOP, CORP, X-DNS-Prefetch-Control. Output is zero JavaScript, 2,387 bytes. Astro build telemetry disabled. site set in astro.config.mjs.</t>
+  </si>
+  <si>
+    <t>https://raymundbermudes.vercel.app</t>
+  </si>
+  <si>
+    <t>FINDING: Vercel preview/branch deployment URLs are PUBLIC - both alternate URLs returned HTTP 200 unauthenticated. Harmless now (placeholder content) but a confidentiality risk from CHUNK 07: a draft case study pushed to any branch is publicly readable before D5 clearance. MITIGATION (plan-independent): make confidentiality clearance a PRE-COMMIT gate, never rely on branch privacy. Also noted: Vercel adds Access-Control-Allow-Origin: * which we did not set - benign on a credential-free static site, flagged for CHUNK 16 review.</t>
+  </si>
+  <si>
+    <t>Push the `site` config commit and confirm the redeploy, then CHUNK 01 is Complete. CHUNK 02 (design system) and CHUNK 04 (content layer) are unblocked. CHUNK 00 remains the critical path.</t>
+  </si>
+  <si>
+    <t>Review</t>
   </si>
 </sst>
 </file>
@@ -4034,7 +4037,7 @@
         <v>982</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>43</v>
+        <v>983</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RaymundBermudes\OneDrive - GDS Link, LLC\Documents\Rr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A649B4-0AE9-4B43-BDA5-79CDD1922589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="983">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>Owner</t>
-  </si>
-  <si>
-    <t>Raymund Ryan Bermudes, Jr.</t>
   </si>
   <si>
     <t>Positioning</t>
@@ -3473,7 +3470,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3481,10 +3478,10 @@
     </row>
     <row r="4" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -3492,10 +3489,10 @@
     </row>
     <row r="5" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -3503,10 +3500,10 @@
     </row>
     <row r="6" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -3514,10 +3511,10 @@
     </row>
     <row r="7" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -3525,10 +3522,10 @@
     </row>
     <row r="8" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -3536,10 +3533,10 @@
     </row>
     <row r="9" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -3547,10 +3544,10 @@
     </row>
     <row r="10" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -3577,316 +3574,316 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>497</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>509</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>516</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>527</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>528</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>529</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>530</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>537</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>539</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>541</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>542</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>548</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -3912,168 +3909,168 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>554</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>560</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>565</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>570</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>978</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>980</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>981</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>982</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -4103,392 +4100,392 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>578</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>584</v>
-      </c>
       <c r="H2" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>589</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>595</v>
-      </c>
       <c r="H4" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>601</v>
-      </c>
       <c r="H5" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>960</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>606</v>
-      </c>
       <c r="H6" s="5" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>612</v>
-      </c>
       <c r="H7" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>617</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>618</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>619</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>623</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>625</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>626</v>
-      </c>
       <c r="E10" s="5" t="s">
+        <v>960</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>962</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>961</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>963</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>964</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>627</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>630</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>631</v>
-      </c>
       <c r="G11" s="5" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>636</v>
-      </c>
       <c r="G12" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>642</v>
-      </c>
       <c r="H13" s="5" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>966</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>965</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>967</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B15" t="s">
+        <v>970</v>
+      </c>
+      <c r="C15" t="s">
         <v>971</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>972</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>973</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>974</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>975</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>976</v>
-      </c>
-      <c r="H15" t="s">
-        <v>977</v>
       </c>
     </row>
   </sheetData>
@@ -4510,301 +4507,301 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>648</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>649</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>657</v>
-      </c>
       <c r="F3" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>661</v>
-      </c>
       <c r="F4" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>664</v>
-      </c>
       <c r="F5" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>667</v>
-      </c>
       <c r="F6" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>670</v>
-      </c>
       <c r="F7" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>673</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>677</v>
-      </c>
       <c r="F9" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>653</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>680</v>
-      </c>
       <c r="F10" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>653</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>683</v>
-      </c>
       <c r="F11" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>653</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>686</v>
-      </c>
       <c r="F12" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>653</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>689</v>
-      </c>
       <c r="F13" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>653</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>654</v>
       </c>
     </row>
   </sheetData>
@@ -4824,114 +4821,114 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>692</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>695</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>696</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>698</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>699</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>700</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>701</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>702</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>703</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>704</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>705</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>706</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>708</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>709</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>710</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>711</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>712</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -4953,72 +4950,72 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>715</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>719</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>732</v>
       </c>
     </row>
   </sheetData>
@@ -5041,307 +5038,307 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>733</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>734</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>735</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>736</v>
-      </c>
       <c r="F1" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>736</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>740</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>741</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>743</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>739</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>740</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>745</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>746</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>747</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>750</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>751</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>752</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>739</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>753</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>754</v>
-      </c>
       <c r="F5" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>755</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>758</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>759</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>760</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>761</v>
-      </c>
       <c r="F7" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>763</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>753</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>764</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>768</v>
-      </c>
       <c r="F9" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>769</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>772</v>
-      </c>
       <c r="F10" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>774</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>775</v>
-      </c>
       <c r="F11" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>776</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>777</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>779</v>
-      </c>
       <c r="F12" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>781</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>739</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>740</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>782</v>
-      </c>
       <c r="F13" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>783</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>784</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>786</v>
-      </c>
       <c r="F14" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>788</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>789</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>790</v>
-      </c>
       <c r="F15" s="5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
   </sheetData>
@@ -5363,367 +5360,367 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>793</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>794</v>
-      </c>
       <c r="F1" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>795</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>796</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>797</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>798</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>799</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>800</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>801</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>802</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>803</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>804</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>806</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>807</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>810</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>811</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>812</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>813</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>814</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>815</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>817</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>818</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>819</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>820</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>821</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>822</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>823</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>825</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>826</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>827</v>
-      </c>
       <c r="F9" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>828</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>829</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>830</v>
-      </c>
       <c r="E10" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>831</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>832</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>833</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>834</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>835</v>
-      </c>
       <c r="F11" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>836</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>837</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>838</v>
-      </c>
       <c r="F12" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>839</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>840</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>841</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>842</v>
-      </c>
       <c r="F13" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>843</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>844</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>845</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>846</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>847</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>848</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>849</v>
-      </c>
       <c r="E15" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>850</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>851</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>852</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>853</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>854</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>855</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>856</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>857</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>858</v>
-      </c>
       <c r="F18" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="358.8" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
   </sheetData>
@@ -5745,483 +5742,483 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>860</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>861</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>862</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>864</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>865</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>866</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>867</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>868</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>869</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>870</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>871</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>872</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>873</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>874</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>875</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>876</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>877</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>878</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>879</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>880</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>881</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>882</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>883</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>884</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>885</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>886</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>887</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>888</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>889</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>890</v>
-      </c>
       <c r="E10" s="5" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>891</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>893</v>
-      </c>
       <c r="E11" s="5" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>894</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>895</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>896</v>
-      </c>
       <c r="E12" s="5" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>897</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>898</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>899</v>
-      </c>
       <c r="E13" s="5" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>900</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>901</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>902</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>903</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>904</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>905</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>906</v>
-      </c>
       <c r="E15" s="5" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>907</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>908</v>
-      </c>
       <c r="D16" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>909</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>910</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>911</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>913</v>
-      </c>
       <c r="E18" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="138" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>916</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>917</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>918</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>920</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>921</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>922</v>
-      </c>
       <c r="E23" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>923</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>924</v>
-      </c>
       <c r="D24" s="4" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>925</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>926</v>
-      </c>
       <c r="D25" s="4" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>927</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>928</v>
-      </c>
       <c r="D26" s="4" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>929</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>930</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>931</v>
-      </c>
       <c r="E27" s="4" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>932</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>933</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>934</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>935</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>936</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>937</v>
-      </c>
       <c r="E29" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>938</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>939</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>940</v>
-      </c>
       <c r="E30" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -6243,75 +6240,75 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>941</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>942</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>944</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>945</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>946</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>947</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>948</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>948</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>949</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>950</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>951</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>952</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>953</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>954</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>955</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>956</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
   </sheetData>
@@ -6338,895 +6335,895 @@
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="J17" s="2"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:10" ht="216" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26" s="2" t="s">
+      <c r="J26" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="G27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="J29" s="2"/>
     </row>
@@ -7255,262 +7252,262 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="D1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="F1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>196</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>202</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>224</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -7534,142 +7531,142 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -7690,206 +7687,206 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>272</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -7912,260 +7909,260 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>331</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -8191,156 +8188,156 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>384</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>387</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>390</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>393</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>396</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>399</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>402</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>405</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>408</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>411</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>414</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -8361,223 +8358,223 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>417</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>434</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>443</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>447</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>451</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>454</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>458</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>463</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>467</v>
-      </c>
       <c r="E13" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -8598,223 +8595,223 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>470</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>473</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>480</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>482</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>484</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>486</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>488</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>492</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>494</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RaymundBermudes\OneDrive - GDS Link, LLC\Documents\Rr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D2363A6-56CC-4225-8998-E8F39D57D29D}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="983">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1076">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -2464,24 +2464,12 @@
     <t>CHUNK 03</t>
   </si>
   <si>
-    <t>BaseLayout, SiteHeader, MobileNav island, SiteFooter, SkipLink, SEOHead scaffold, 404</t>
-  </si>
-  <si>
-    <t>Nav works at all 8 widths; keyboard-only traversal complete; mobile panel traps focus and closes on Esc</t>
-  </si>
-  <si>
     <t>CHUNK 04</t>
   </si>
   <si>
     <t>Content layer</t>
   </si>
   <si>
-    <t>content/config.ts schemas, data/*.ts, one placeholder MDX project proving the pipeline</t>
-  </si>
-  <si>
-    <t>Build fails on an invalid project and succeeds on a valid one; types flow to components</t>
-  </si>
-  <si>
     <t>CHUNK 05</t>
   </si>
   <si>
@@ -2491,9 +2479,6 @@
     <t>/work, ProjectCard, ProjectGrid, ProjectMeta</t>
   </si>
   <si>
-    <t>Cards show problem/role/stack/outcome; whole card is one link with a correct accessible name</t>
-  </si>
-  <si>
     <t>CHUNK 06</t>
   </si>
   <si>
@@ -2980,13 +2965,307 @@
     <t>https://raymundbermudes.vercel.app</t>
   </si>
   <si>
-    <t>FINDING: Vercel preview/branch deployment URLs are PUBLIC - both alternate URLs returned HTTP 200 unauthenticated. Harmless now (placeholder content) but a confidentiality risk from CHUNK 07: a draft case study pushed to any branch is publicly readable before D5 clearance. MITIGATION (plan-independent): make confidentiality clearance a PRE-COMMIT gate, never rely on branch privacy. Also noted: Vercel adds Access-Control-Allow-Origin: * which we did not set - benign on a credential-free static site, flagged for CHUNK 16 review.</t>
-  </si>
-  <si>
-    <t>Push the `site` config commit and confirm the redeploy, then CHUNK 01 is Complete. CHUNK 02 (design system) and CHUNK 04 (content layer) are unblocked. CHUNK 00 remains the critical path.</t>
-  </si>
-  <si>
     <t>Review</t>
+  </si>
+  <si>
+    <t>BaseLayout, SiteHeader, SiteFooter, SkipLink, Link component enforcing rel=noopener noreferrer, typed site config, 404</t>
+  </si>
+  <si>
+    <t>AMENDED 2026-09-23 (D19): no MobileNav island. Three nav items and one action have nothing to collapse, so the nav wraps below 560px. Done when: nav works at all 8 widths, keyboard-only traversal complete, all targets &gt;=44x44, and the whole shell works with JavaScript disabled.</t>
+  </si>
+  <si>
+    <t>content.config.ts + Zod schema with confidentiality guards, data/*.ts, scripts/check-schema.ts</t>
+  </si>
+  <si>
+    <t>AMENDED 2026-09-23 (D21): no placeholder MDX project is committed - a fabricated case study would breach the no-fabrication rule. The pipeline is proven instead by scripts/check-schema.ts, which asserts every schema guard rejects what it should and that a valid entry still passes. Done when: 22/22 guards pass and types flow to components.</t>
+  </si>
+  <si>
+    <t>AMENDED 2026-09-23 (D20): the title is the only link, not the whole card. Making the card one link means either nesting interactive elements or an overlay that breaks text selection; the card responds to :hover and :focus-within instead. Done when: cards show problem/role/stack/outcome and the title link has a correct accessible name.</t>
+  </si>
+  <si>
+    <t>GAP: tracker CHUNK 01 requires ESLint/Prettier and green CI. Neither exists - no linter, no formatter, no .github/workflows. Never built and not previously reported. Chunk therefore stays Review, not Complete. Also open: Vercel preview/branch URLs are PUBLIC (verified HTTP 200 unauthenticated) - mitigation is that confidentiality clearance is a pre-commit gate (D23), never pre-merge.</t>
+  </si>
+  <si>
+    <t>Add ESLint + Prettier + a CI workflow, then CHUNK 01 can close.</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>CHUNK 02 - design system</t>
+  </si>
+  <si>
+    <t>Tokens as real CSS custom properties in src/styles/tokens.css, consumed by Tailwind 4 via @theme so the two cannot drift. Both light and dark palettes at the specified values; dark applies on OS preference unless the user has explicitly chosen light, which is the override CHUNK 12 needs. Geist Sans and Geist Mono self-hosted via Astro Fonts API - 2 variable files, inside the 3-file cap. Strict 4px spacing scale; shell 1200, wide 1040, prose 68ch. Motion tokens with one global prefers-reduced-motion kill switch. Focus ring and skip link present from the start. Temporary /styleguide route renders every token.</t>
+  </si>
+  <si>
+    <t>commit ef57d98; /styleguide</t>
+  </si>
+  <si>
+    <t>GAP: tracker requires "styleguide passes axe". axe has NEVER been run. Contrast was verified by token value and by measuring computed styles in-browser, not by tooling. Chunk stays Review, not Complete.</t>
+  </si>
+  <si>
+    <t>Run axe on /styleguide, then CHUNK 02 can close.</t>
+  </si>
+  <si>
+    <t>CHUNK 03 - global shell</t>
+  </si>
+  <si>
+    <t>BaseLayout owns the document, head, fonts, skip link, header, footer and the main landmark. SiteHeader: name, three nav items, one action, with aria-current carried by an underline as well as colour. SiteFooter. Link component enforces rel=noopener noreferrer on external links in one place. Typed site config in src/data/site.ts. Placeholder /work /about /contact /404 so the shell is navigable end to end, each naming the content it waits on and carrying noindex. Resume button renders only when the CV file exists, so no 404 link can ship.</t>
+  </si>
+  <si>
+    <t>commit e55648f</t>
+  </si>
+  <si>
+    <t>DEVIATION ACCEPTED 2026-09-23 (D19): no MobileNav island - spec amended. Fixed during verification: nav touch targets were 44px tall but only 37px wide, failing the &gt;=44x44 rule. Untested: the Link component external-link branch, since no page has an external link until CHUNK 11.</t>
+  </si>
+  <si>
+    <t>Nothing outstanding. External-link branch to be exercised at CHUNK 11.</t>
+  </si>
+  <si>
+    <t>CHUNK 04 - content layer</t>
+  </si>
+  <si>
+    <t>One collection loaded from src/content/work/*.mdx with a Zod schema that moves three Critical requirements out of memory and into the build: myRole/outcome/clientDescriptor are .min(1); confidentialityReview is a dated event with a named reviewer whose tierConfirmed must equal disclosure; client is permitted only at the named tier. Restricted client names are blocked from EVERY public string - slug, title, description, clientDescriptor, problem, myRole, outcome - normalised to lowercase alphanumerics first so c-t-b-c and C.T.B.C collapse to the same string. Typed, deliberately empty data/experience.ts and data/skills.ts.</t>
+  </si>
+  <si>
+    <t>commit b13ca45; npm run check:schema</t>
+  </si>
+  <si>
+    <t>DEVIATION ACCEPTED 2026-09-23 (D21): no placeholder MDX project - spec amended. Pipeline proven by scripts/check-schema.ts, 22/22 guards passing, rather than by a committed fixture. Note the guards are a forcing function, NOT verification: they cannot tell whether a sentence is true. Build logs one expected warning that the collection is empty; it clears at CHUNK 07.</t>
+  </si>
+  <si>
+    <t>Nothing outstanding.</t>
+  </si>
+  <si>
+    <t>CHUNK 05 - work index and ProjectCard</t>
+  </si>
+  <si>
+    <t>Evidence card: every card carries the same four facts in the same order - Problem, My role, Stack, Outcome - so a recruiter comparing candidates finds the same information in the same place. No hero image, no "View project" link, and no metric slot: there is no large-numeral treatment anywhere in the design system, because an empty box invites something to fill it. ProjectMeta renders the disclosure tier as plain English ("Client anonymised") rather than the internal word. ProjectGrid is a real ol because the order is curated. Tags are non-interactive because filtering is deferred (D4).</t>
+  </si>
+  <si>
+    <t>commit e2dc08d</t>
+  </si>
+  <si>
+    <t>DEVIATION ACCEPTED 2026-09-23 (D20): title-only link, not whole-card - spec amended. Fixed during verification: at narrow widths the meta separator dots wrapped to the start of a line and read as list bullets. Verified against a temporary fixture which was then deleted and confirmed absent from source, git and build output.</t>
+  </si>
+  <si>
+    <t>CHUNK 06 - case study system and Delivery Thread</t>
+  </si>
+  <si>
+    <t>The rail is a nav of anchor links built from the headings Astro actually rendered, so it can never link to a missing section nor omit a present one. With JavaScript off it is a plain table of contents and every link works; the island only adds aria-current. IntersectionObserver rather than a scroll handler. Sticky beside the prose at &gt;=1024px, static above it below that. The current marker thickens the rule and darkens the text as well as using accent, so it reads without colour perception. CaseStudyHeader elevates My Role into the page header. CaseStudyNav renders only what exists.</t>
+  </si>
+  <si>
+    <t>commit ecde816</t>
+  </si>
+  <si>
+    <t>GAP: tracker CHUNK 06 requires Disclosure (native details), CodeBlock and ArchitectureFigure. NONE were built - only Callout. Never reported until the alignment review. Chunk stays Review. IMPORTANT FIX: Astro inlines island scripts into the HTML, but vercel.json sets script-src self with no unsafe-inline, so the scroll spy would have been silently blocked in production while working on localhost, where vercel.json headers never apply. vite.build.assetsInlineLimit is now 0 (D22). Verified against the real production bundle via astro preview. STILL UNVERIFIED against the live deployment with the real CSP. Also unverified: the 68ch measure on an actual case study page.</t>
+  </si>
+  <si>
+    <t>Build Disclosure, CodeBlock and ArchitectureFigure; verify the island against the live CSP after a push. Then CHUNK 06 can close.</t>
+  </si>
+  <si>
+    <t>D15</t>
+  </si>
+  <si>
+    <t>Positioning line and role</t>
+  </si>
+  <si>
+    <t>Solutions Analyst &amp; Enterprise Systems Developer (CV); Solution Analyst &amp; Android Developer (original); a bridge of both</t>
+  </si>
+  <si>
+    <t>Solutions Analyst &amp; Enterprise Systems Developer</t>
+  </si>
+  <si>
+    <t>Raymund supplied his CV, which says Enterprise Systems Developer. A portfolio must not contradict the CV attached to it - it is the first inconsistency a recruiter can check. The CV also showed the original framing was wrong on the facts: Android was the previous role (Junior Android Developer, Jul 2022 - Dec 2023), not the current one (Solutions Analyst, Jan 2024 - present). Android remains genuine current work as sole maintainer of a production app, but it is one strand rather than the headline.</t>
+  </si>
+  <si>
+    <t>High. Consequence: all three positioning-line drafts in PHASE-1-DISCOVERY.md 10.1 lead with Android and are now STALE. CG-09 needs fresh drafts before CHUNK 08.</t>
+  </si>
+  <si>
+    <t>DECIDED by owner 2026-09-23</t>
+  </si>
+  <si>
+    <t>D16</t>
+  </si>
+  <si>
+    <t>Attributable-experience guardrail widened</t>
+  </si>
+  <si>
+    <t>Keep the original narrow list; widen to match the CV; widen with owner editing each item</t>
+  </si>
+  <si>
+    <t>Widen to match the CV</t>
+  </si>
+  <si>
+    <t>CLAUDE.md listed what could be attributed to Raymund and omitted C#, JavaScript, PHP, Oracle PL/SQL, Agile/Scrum, client demos and training, production deployments, incident escalation and mentoring - all on his CV. The list was incomplete rather than wrong, written before the CV was available, and an incomplete guardrail blocks accurate history.</t>
+  </si>
+  <si>
+    <t>Medium. The rule itself is unchanged: anything absent is still unattributable without asking. n8n, Claude Code and Codex remain EXCLUDED - learning, not delivery experience - and must not appear in Skills.</t>
+  </si>
+  <si>
+    <t>D17</t>
+  </si>
+  <si>
+    <t>Security case study publishes at abstracted, overriding its engagement tier</t>
+  </si>
+  <si>
+    <t>Publish at the engagement default (sectoral); publish at abstracted; omit entirely</t>
+  </si>
+  <si>
+    <t>Abstracted - the stricter tier wins</t>
+  </si>
+  <si>
+    <t>The VAPT remediation belongs to an engagement tiered sectoral, but Sheet 18 tiers anything touching security, incidents, credentials or internal architecture at Abstracted, and PHASE-1-DISCOVERY.md calls a public account of security remediation at a named financial institution the single highest-risk sentence this portfolio could contain.</t>
+  </si>
+  <si>
+    <t>CRITICAL and IRREVERSIBLE. No client, no sector, no geography, and NO specific vulnerabilities, library names, versions or attack paths - publishing what was wrong is a roadmap for anyone who finds an unpatched build. Gates cleared by owner: remediation is closed and released, and he is free to say an assessment took place.</t>
+  </si>
+  <si>
+    <t>DECIDED by owner 2026-09-22</t>
+  </si>
+  <si>
+    <t>D18</t>
+  </si>
+  <si>
+    <t>CASECenter, the employer and the sector are publicly nameable</t>
+  </si>
+  <si>
+    <t>Treat CASECenter as restricted; treat it as nameable</t>
+  </si>
+  <si>
+    <t>Nameable</t>
+  </si>
+  <si>
+    <t>Raymund's own CV already states GDS Link Asia as employer, CASE Center as the tool, and fintech / credit decisioning as the sector. The portfolio naming them discloses nothing new. An earlier concern that naming the tool would identify a client was based on a false premise - the tool spans many clients - and is withdrawn.</t>
+  </si>
+  <si>
+    <t>Low, and it does NOT loosen D5. Individual clients (CTBC, SBC) remain restricted in every public string and are blocked by src/lib/confidentiality.ts.</t>
+  </si>
+  <si>
+    <t>D19</t>
+  </si>
+  <si>
+    <t>No MobileNav island; island budget reduced from 4 to 3</t>
+  </si>
+  <si>
+    <t>Build the MobileNav island as planned; let the nav wrap</t>
+  </si>
+  <si>
+    <t>Let the nav wrap - no island</t>
+  </si>
+  <si>
+    <t>Three nav items and one action have nothing to collapse. Below 560px the nav takes its own row. That works at 320px, needs no focus trap, no aria-expanded, no scroll lock and no Esc handling. Interaction rule 5 decides it: a hamburger would put every destination one tap further away for no gain.</t>
+  </si>
+  <si>
+    <t>Low and reversible. Tracker CHUNK 03 "Done when" amended to match. Island budget is now MobileNav-free: deliveryThread, ThemeToggle, and one spare.</t>
+  </si>
+  <si>
+    <t>ACCEPTED as spec by owner 2026-09-23</t>
+  </si>
+  <si>
+    <t>D20</t>
+  </si>
+  <si>
+    <t>ProjectCard: the title is the only link, not the whole card</t>
+  </si>
+  <si>
+    <t>Whole card as one link (tracker original); title-only link</t>
+  </si>
+  <si>
+    <t>Title-only link</t>
+  </si>
+  <si>
+    <t>Making the whole card a link means either nesting interactive elements inside an anchor or covering the card with an overlay that breaks text selection. The card responds to :hover and :focus-within instead, so keyboard users get the same affordance without either problem.</t>
+  </si>
+  <si>
+    <t>Low. Tracker CHUNK 05 "Done when" amended to match.</t>
+  </si>
+  <si>
+    <t>D21</t>
+  </si>
+  <si>
+    <t>No placeholder MDX project is committed to the collection</t>
+  </si>
+  <si>
+    <t>Commit a placeholder project (tracker original); prove the pipeline by test instead</t>
+  </si>
+  <si>
+    <t>No placeholder; prove by test</t>
+  </si>
+  <si>
+    <t>A fabricated case study breaches the first rule in CLAUDE.md, and a half-real one is worse because it looks trustworthy. scripts/check-schema.ts asserts every guard rejects what it should and that a valid entry still passes - 22 checks, wired into npm run verify.</t>
+  </si>
+  <si>
+    <t>Low. Tracker CHUNK 04 "Done when" amended to match. Build logs one expected empty-collection warning until CHUNK 07.</t>
+  </si>
+  <si>
+    <t>D22</t>
+  </si>
+  <si>
+    <t>Scripts are emitted as external files, never inlined</t>
+  </si>
+  <si>
+    <t>Allow Astro to inline island scripts and add per-script CSP hashes; force external files</t>
+  </si>
+  <si>
+    <t>Force external files (vite.build.assetsInlineLimit = 0)</t>
+  </si>
+  <si>
+    <t>Astro inlines small island scripts as script type=module, but vercel.json sets script-src self with no unsafe-inline. The delivery thread would have been silently blocked in production while working perfectly on localhost, where vercel.json headers never apply. CSP hashes were rejected because they need regenerating on every build and rot the first time someone forgets.</t>
+  </si>
+  <si>
+    <t>Medium. Keeps the strict CSP honest. Verified against the real production bundle: zero inline scripts, one external file from /_astro/. STILL to be verified against the live deployment.</t>
+  </si>
+  <si>
+    <t>DECIDED by Claude 2026-09-23, reported to owner</t>
+  </si>
+  <si>
+    <t>D23</t>
+  </si>
+  <si>
+    <t>Confidentiality clearance is a PRE-COMMIT gate, never pre-merge</t>
+  </si>
+  <si>
+    <t>Clear content before merge; clear content before commit</t>
+  </si>
+  <si>
+    <t>Before commit</t>
+  </si>
+  <si>
+    <t>Vercel preview and branch deployment URLs are PUBLIC - verified, both returned HTTP 200 to an unauthenticated request. Pushing an uncleared draft to any branch publishes it at a public URL before review. "It is only on a branch" is not a confidentiality control.</t>
+  </si>
+  <si>
+    <t>CRITICAL from CHUNK 07 onward. Harmless today because every deployment serves placeholder content.</t>
+  </si>
+  <si>
+    <t>DECIDED by Claude 2026-09-22, reported to owner</t>
+  </si>
+  <si>
+    <t>Built and deployed, but tracker CHUNK 01 also requires ESLint/Prettier and green CI. Neither exists.</t>
+  </si>
+  <si>
+    <t>Rail, header and prev/next built. Disclosure, CodeBlock and ArchitectureFigure not built.</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-22 - D5 confirmed by owner</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-23 - exact roles, employers and dates taken from the CV</t>
+  </si>
+  <si>
+    <t>Open - CV gives a starting list, but Raymund must still filter it to what he would defend in an interview</t>
+  </si>
+  <si>
+    <t>Partially closed 2026-09-23 - email and LinkedIn from the CV. GitHub URL still OPEN (and note the portfolio repo is private, D14)</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-23 - Cavite, Philippines; open to relocation to Europe/UK/US with visa sponsorship</t>
+  </si>
+  <si>
+    <t>Open - and now HARDER: all three drafted options lead with Android and are stale after D15. Fresh drafts needed.</t>
+  </si>
+  <si>
+    <t>Open - reframed. CTBC and SBC are separate client engagements; the original row named CASECenter, which is a tool, not an engagement.</t>
   </si>
 </sst>
 </file>
@@ -3105,7 +3384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3136,6 +3415,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3470,7 +3755,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -3895,7 +4180,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4019,63 +4304,193 @@
         <v>95</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>984</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>985</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>986</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>988</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>989</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>990</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>992</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>993</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>994</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>995</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>996</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>997</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>999</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>998</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2" t="s">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2" t="s">
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>48</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H7" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4085,7 +4500,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4147,7 +4562,7 @@
         <v>583</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4173,7 +4588,7 @@
         <v>131</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4199,7 +4614,7 @@
         <v>594</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4225,7 +4640,7 @@
         <v>600</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -4242,7 +4657,7 @@
         <v>603</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>604</v>
@@ -4251,7 +4666,7 @@
         <v>605</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4277,7 +4692,7 @@
         <v>611</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4303,7 +4718,7 @@
         <v>617</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4329,7 +4744,7 @@
         <v>622</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -4346,16 +4761,16 @@
         <v>625</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -4381,7 +4796,7 @@
         <v>617</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4407,7 +4822,7 @@
         <v>131</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4433,7 +4848,7 @@
         <v>641</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -4450,16 +4865,16 @@
         <v>644</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>645</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -4467,25 +4882,259 @@
         <v>554</v>
       </c>
       <c r="B15" t="s">
+        <v>965</v>
+      </c>
+      <c r="C15" t="s">
+        <v>966</v>
+      </c>
+      <c r="D15" t="s">
+        <v>967</v>
+      </c>
+      <c r="E15" t="s">
+        <v>968</v>
+      </c>
+      <c r="F15" t="s">
+        <v>969</v>
+      </c>
+      <c r="G15" t="s">
         <v>970</v>
       </c>
-      <c r="C15" t="s">
+      <c r="H15" t="s">
         <v>971</v>
       </c>
-      <c r="D15" t="s">
-        <v>972</v>
-      </c>
-      <c r="E15" t="s">
-        <v>973</v>
-      </c>
-      <c r="F15" t="s">
-        <v>974</v>
-      </c>
-      <c r="G15" t="s">
-        <v>975</v>
-      </c>
-      <c r="H15" t="s">
-        <v>976</v>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H20" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H23" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="9" t="s">
+        <v>983</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H24" t="s">
+        <v>1066</v>
       </c>
     </row>
   </sheetData>
@@ -5096,7 +5745,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>745</v>
       </c>
@@ -5113,7 +5762,7 @@
         <v>749</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>741</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -5136,7 +5785,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>754</v>
       </c>
@@ -5153,10 +5802,10 @@
         <v>757</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>758</v>
       </c>
@@ -5173,10 +5822,10 @@
         <v>760</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>761</v>
       </c>
@@ -5193,10 +5842,10 @@
         <v>763</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>764</v>
       </c>
@@ -5213,10 +5862,10 @@
         <v>767</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>768</v>
       </c>
@@ -5233,7 +5882,7 @@
         <v>771</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>653</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -5316,7 +5965,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="144" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>786</v>
       </c>
@@ -5333,7 +5982,7 @@
         <v>789</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>653</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
@@ -5395,7 +6044,7 @@
         <v>798</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -5415,7 +6064,7 @@
         <v>803</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>48</v>
+        <v>975</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -5435,10 +6084,10 @@
         <v>81</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>807</v>
       </c>
@@ -5446,76 +6095,76 @@
         <v>101</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>808</v>
+        <v>976</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>809</v>
+        <v>977</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>100</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>812</v>
+        <v>978</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>813</v>
+        <v>979</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>38</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>817</v>
+        <v>980</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>109</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>48</v>
+        <v>975</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -5523,16 +6172,16 @@
         <v>739</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>48</v>
@@ -5543,13 +6192,13 @@
         <v>770</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>104</v>
@@ -5560,19 +6209,19 @@
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>48</v>
@@ -5586,13 +6235,13 @@
         <v>128</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>48</v>
@@ -5603,16 +6252,16 @@
         <v>752</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>48</v>
@@ -5620,16 +6269,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>141</v>
@@ -5640,16 +6289,16 @@
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>148</v>
@@ -5660,16 +6309,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>154</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>153</v>
@@ -5686,10 +6335,10 @@
         <v>159</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>158</v>
@@ -5703,16 +6352,16 @@
         <v>573</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>48</v>
@@ -5720,7 +6369,7 @@
     </row>
     <row r="20" spans="1:6" ht="358.8" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
     </row>
   </sheetData>
@@ -5745,16 +6394,16 @@
         <v>494</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -5762,16 +6411,16 @@
         <v>154</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5779,16 +6428,16 @@
         <v>154</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -5796,16 +6445,16 @@
         <v>154</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -5813,16 +6462,16 @@
         <v>154</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -5830,16 +6479,16 @@
         <v>154</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -5847,16 +6496,16 @@
         <v>154</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -5864,16 +6513,16 @@
         <v>154</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -5881,16 +6530,16 @@
         <v>149</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -5898,16 +6547,16 @@
         <v>149</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -5915,16 +6564,16 @@
         <v>149</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -5932,16 +6581,16 @@
         <v>149</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -5949,16 +6598,16 @@
         <v>149</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -5966,67 +6615,67 @@
         <v>149</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>902</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>906</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>907</v>
-      </c>
       <c r="D16" s="5" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -6034,13 +6683,13 @@
         <v>164</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>573</v>
@@ -6051,13 +6700,13 @@
         <v>221</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>573</v>
@@ -6065,7 +6714,7 @@
     </row>
     <row r="21" spans="1:5" ht="138" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -6073,16 +6722,16 @@
         <v>164</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -6090,13 +6739,13 @@
         <v>164</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>799</v>
@@ -6107,13 +6756,13 @@
         <v>164</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>799</v>
@@ -6124,13 +6773,13 @@
         <v>164</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>799</v>
@@ -6141,13 +6790,13 @@
         <v>164</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>799</v>
@@ -6158,13 +6807,13 @@
         <v>164</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>804</v>
@@ -6175,16 +6824,16 @@
         <v>164</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -6192,13 +6841,13 @@
         <v>164</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>573</v>
@@ -6209,13 +6858,13 @@
         <v>178</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>573</v>
@@ -6240,75 +6889,75 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
     </row>
   </sheetData>
@@ -6449,7 +7098,7 @@
         <v>38</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>35</v>
@@ -6685,7 +7334,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>94</v>
       </c>
@@ -6705,7 +7354,7 @@
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>48</v>
+        <v>975</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>35</v>
@@ -6713,7 +7362,9 @@
       <c r="I12" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="J12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>1067</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -6735,7 +7386,7 @@
         <v>94</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>35</v>
@@ -6795,7 +7446,7 @@
         <v>100</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>35</v>
@@ -6805,7 +7456,7 @@
       </c>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>114</v>
       </c>
@@ -6825,7 +7476,7 @@
         <v>109</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>48</v>
+        <v>975</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>35</v>
@@ -6833,7 +7484,9 @@
       <c r="I16" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="J16" s="2"/>
+      <c r="J16" s="2" t="s">
+        <v>1068</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
@@ -7935,7 +8588,7 @@
         <v>332</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>333</v>

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D2363A6-56CC-4225-8998-E8F39D57D29D}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22DA228D-FBC9-4D07-99C1-C6D715982D69}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="1081">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3266,6 +3266,21 @@
   </si>
   <si>
     <t>Open - reframed. CTBC and SBC are separate client engagements; the original row named CASECenter, which is a tool, not an engagement.</t>
+  </si>
+  <si>
+    <t>CHUNK 00 - case study 1 draft skeleton</t>
+  </si>
+  <si>
+    <t>Drafted the VAPT case study skeleton into notes/case-study-1-DRAFT.md against the ten Sheet 06 sections, at the abstracted tier (D17). Every drafted line traces to something Raymund actually said, quoted inline; everything else is marked [CONTENT REQUIRED] with a specific question. Context, Problem, My Role and Technical Challenge are drafted from source. Method changed deliberately: draft-and-correct rather than open questioning, because reacting to a wrong draft is easier than answering into a void. No content was written to src/content/work/ - that is CHUNK 07.</t>
+  </si>
+  <si>
+    <t>notes/case-study-1-DRAFT.md</t>
+  </si>
+  <si>
+    <t>FOUR DECISIONS BLOCK PROGRESS. (1) THE CRUX: were the VAPT findings in the third-party libraries or in the app own code? This determines what the case study is, and will not be assumed. (2) Is this the same engagement as the register SBC security work (CG-02)? If so there is one security item, not two, and case study 2 must come from elsewhere. (3) How much functional context survives the abstracted tier - keep the word appraisal, or drop to field data collection? Recommend dropping it. (4) Title. Investigation, Solution, Validation, Outcome and Lessons remain EMPTY - Solution is the core gap, since I refactor the codes is a headline, not a case study. Deliberately did NOT offer a list of standard Android hardening measures to tick, as collecting a yes would manufacture detail Raymund did not recall.</t>
+  </si>
+  <si>
+    <t>Raymund answers decision 1 (libraries vs own code); then the Solution and Technical Challenge sections can be drafted and CG-01 can start closing.</t>
   </si>
 </sst>
 </file>
@@ -3411,16 +3426,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3731,13 +3746,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4180,7 +4195,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4323,174 +4338,200 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>983</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>984</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="11" t="s">
         <v>985</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="11" t="s">
         <v>986</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="11" t="s">
         <v>987</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="11" t="s">
         <v>988</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="11" t="s">
         <v>975</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="10" t="s">
         <v>983</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>990</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="11" t="s">
         <v>991</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="11" t="s">
         <v>992</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="11" t="s">
         <v>993</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>983</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>994</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="11" t="s">
         <v>995</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="11" t="s">
         <v>996</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="11" t="s">
         <v>997</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="11" t="s">
         <v>998</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="10" t="s">
         <v>983</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>999</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>1000</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="11" t="s">
         <v>1001</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="11" t="s">
         <v>1002</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="11" t="s">
         <v>998</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>983</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="11" t="s">
         <v>1003</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="11" t="s">
         <v>1004</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="11" t="s">
         <v>1005</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="11" t="s">
         <v>1006</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="11" t="s">
         <v>1007</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="11" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>983</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H13" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22DA228D-FBC9-4D07-99C1-C6D715982D69}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFCC665D-8027-42DE-B11F-764114295E56}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2983,12 +2983,6 @@
     <t>AMENDED 2026-09-23 (D20): the title is the only link, not the whole card. Making the card one link means either nesting interactive elements or an overlay that breaks text selection; the card responds to :hover and :focus-within instead. Done when: cards show problem/role/stack/outcome and the title link has a correct accessible name.</t>
   </si>
   <si>
-    <t>GAP: tracker CHUNK 01 requires ESLint/Prettier and green CI. Neither exists - no linter, no formatter, no .github/workflows. Never built and not previously reported. Chunk therefore stays Review, not Complete. Also open: Vercel preview/branch URLs are PUBLIC (verified HTTP 200 unauthenticated) - mitigation is that confidentiality clearance is a pre-commit gate (D23), never pre-merge.</t>
-  </si>
-  <si>
-    <t>Add ESLint + Prettier + a CI workflow, then CHUNK 01 can close.</t>
-  </si>
-  <si>
     <t>2026-09-23</t>
   </si>
   <si>
@@ -3241,9 +3235,6 @@
     <t>DECIDED by Claude 2026-09-22, reported to owner</t>
   </si>
   <si>
-    <t>Built and deployed, but tracker CHUNK 01 also requires ESLint/Prettier and green CI. Neither exists.</t>
-  </si>
-  <si>
     <t>Rail, header and prev/next built. Disclosure, CodeBlock and ArchitectureFigure not built.</t>
   </si>
   <si>
@@ -3281,6 +3272,15 @@
   </si>
   <si>
     <t>Raymund answers decision 1 (libraries vs own code); then the Solution and Technical Challenge sections can be drafted and CG-01 can start closing.</t>
+  </si>
+  <si>
+    <t>GAP CLOSED 2026-09-23. ESLint (flat config, typescript-eslint + eslint-plugin-astro), Prettier, a GitHub Actions CI workflow and Dependabot are now in place. CI runs lint, format:check, schema guards, astro check, build and npm audit --audit-level=moderate, so CI can never pass something npm run verify would reject. KNOWN LIMITATION: .astro files are excluded from Prettier because prettier-plugin-astro is not idempotent - on four files, --write reports "unchanged" while --check simultaneously flags them, verified across three passes. That is a plugin bug and would leave CI permanently red. ESLint covers .astro correctness instead, and passes. Earlier finding still open: Vercel preview URLs are PUBLIC; mitigation is D23, clearance as a pre-commit gate.</t>
+  </si>
+  <si>
+    <t>Nothing outstanding for CHUNK 01. CI is untested against GitHub until the workflow runs on a push.</t>
+  </si>
+  <si>
+    <t>Built and deployed. ESLint, Prettier, CI and Dependabot added 2026-09-23, closing the gap that held this at Review.</t>
   </si>
 </sst>
 </file>
@@ -4328,36 +4328,36 @@
         <v>974</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>981</v>
+        <v>1078</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>982</v>
+        <v>1079</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>975</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>983</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>984</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>985</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="G6" s="11" t="s">
         <v>986</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>987</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>988</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>975</v>
@@ -4365,25 +4365,25 @@
     </row>
     <row r="7" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>987</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>988</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>990</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="G7" s="11" t="s">
         <v>991</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>992</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>993</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>34</v>
@@ -4391,25 +4391,25 @@
     </row>
     <row r="8" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>992</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>993</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>994</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>995</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="G8" s="11" t="s">
         <v>996</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>997</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>998</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>34</v>
@@ -4417,25 +4417,25 @@
     </row>
     <row r="9" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>997</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>998</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>999</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>1000</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>1002</v>
-      </c>
       <c r="G9" s="11" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>34</v>
@@ -4443,25 +4443,25 @@
     </row>
     <row r="10" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>1003</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="F10" s="11" t="s">
         <v>1004</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="G10" s="11" t="s">
         <v>1005</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>1007</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>975</v>
@@ -4469,25 +4469,25 @@
     </row>
     <row r="11" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>1076</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="G11" s="11" t="s">
         <v>1077</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>1079</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>1080</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>42</v>
@@ -4946,236 +4946,236 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B16" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D16" t="s">
         <v>1008</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>1009</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>1010</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>1011</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>1012</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1013</v>
-      </c>
-      <c r="H16" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B17" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D17" t="s">
         <v>1015</v>
       </c>
-      <c r="C17" t="s">
+      <c r="E17" t="s">
         <v>1016</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>1017</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>1018</v>
       </c>
-      <c r="F17" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G17" t="s">
-        <v>1020</v>
-      </c>
       <c r="H17" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B18" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D18" t="s">
         <v>1021</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
         <v>1022</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>1023</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>1024</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>1025</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H18" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B19" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D19" t="s">
         <v>1028</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>1029</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
         <v>1030</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>1031</v>
       </c>
-      <c r="F19" t="s">
-        <v>1032</v>
-      </c>
-      <c r="G19" t="s">
-        <v>1033</v>
-      </c>
       <c r="H19" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B20" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D20" t="s">
         <v>1034</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>1035</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>1036</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>1037</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H20" t="s">
         <v>1038</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1039</v>
-      </c>
-      <c r="H20" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B21" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D21" t="s">
         <v>1041</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>1042</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>1043</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>1044</v>
       </c>
-      <c r="F21" t="s">
-        <v>1045</v>
-      </c>
-      <c r="G21" t="s">
-        <v>1046</v>
-      </c>
       <c r="H21" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B22" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D22" t="s">
         <v>1047</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>1048</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>1049</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>1050</v>
       </c>
-      <c r="F22" t="s">
-        <v>1051</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1052</v>
-      </c>
       <c r="H22" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B23" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D23" t="s">
         <v>1053</v>
       </c>
-      <c r="C23" t="s">
+      <c r="E23" t="s">
         <v>1054</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>1055</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>1056</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
         <v>1057</v>
-      </c>
-      <c r="G23" t="s">
-        <v>1058</v>
-      </c>
-      <c r="H23" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B24" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D24" t="s">
         <v>1060</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E24" t="s">
         <v>1061</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>1062</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>1063</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" t="s">
         <v>1064</v>
-      </c>
-      <c r="G24" t="s">
-        <v>1065</v>
-      </c>
-      <c r="H24" t="s">
-        <v>1066</v>
       </c>
     </row>
   </sheetData>
@@ -5803,7 +5803,7 @@
         <v>749</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -5843,7 +5843,7 @@
         <v>757</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -5863,7 +5863,7 @@
         <v>760</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
@@ -5883,7 +5883,7 @@
         <v>763</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -5903,7 +5903,7 @@
         <v>767</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -5923,7 +5923,7 @@
         <v>771</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -6023,7 +6023,7 @@
         <v>789</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
@@ -6105,7 +6105,7 @@
         <v>803</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>975</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -7375,7 +7375,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>94</v>
       </c>
@@ -7395,7 +7395,7 @@
         <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>975</v>
+        <v>34</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>35</v>
@@ -7404,7 +7404,7 @@
         <v>99</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1067</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -7526,7 +7526,7 @@
         <v>118</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFCC665D-8027-42DE-B11F-764114295E56}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C778D1A0-6ACC-49DF-92C1-AEAF01A18C1C}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2995,12 +2995,6 @@
     <t>commit ef57d98; /styleguide</t>
   </si>
   <si>
-    <t>GAP: tracker requires "styleguide passes axe". axe has NEVER been run. Contrast was verified by token value and by measuring computed styles in-browser, not by tooling. Chunk stays Review, not Complete.</t>
-  </si>
-  <si>
-    <t>Run axe on /styleguide, then CHUNK 02 can close.</t>
-  </si>
-  <si>
     <t>CHUNK 03 - global shell</t>
   </si>
   <si>
@@ -3281,6 +3275,12 @@
   </si>
   <si>
     <t>Built and deployed. ESLint, Prettier, CI and Dependabot added 2026-09-23, closing the gap that held this at Review.</t>
+  </si>
+  <si>
+    <t>GAP CLOSED 2026-09-23. axe-core 4.10.2 run against all 7 routes (/, /work, /work/[slug], /about, /contact, /styleguide, 404) in BOTH themes at 1280px and 375px, at WCAG 2.0/2.1/2.2 A and AA plus best-practice, and additionally at AAA because CLAUDE.md claims 7:1. DEFECT FOUND AND FIXED - 6 violations at AAA: DeliveryThread .thread__stage carried opacity 0.8, which blended --text-muted (#535349, a genuine 7.2:1 against white) down to #75756d at 4.64:1. Dimming a token with opacity silently invalidates its verified contrast ratio. SECOND DEFECT FIXED, which axe cannot detect because it cannot simulate hover: the global a:hover rule used opacity 0.75, blending --accent (8.6:1) down to roughly 4.7:1. Hover now thickens the underline instead, which is also a better affordance because it does not depend on colour perception. Final result: 0 violations at AA and 0 at AAA on every route, both themes, both widths.</t>
+  </si>
+  <si>
+    <t>Nothing outstanding for CHUNK 02. Re-run axe at CHUNK 13 once real content and the ThemeToggle exist.</t>
   </si>
 </sst>
 </file>
@@ -4328,10 +4328,10 @@
         <v>974</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>34</v>
@@ -4354,13 +4354,13 @@
         <v>984</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>985</v>
+        <v>1079</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>986</v>
+        <v>1080</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>975</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
@@ -4371,19 +4371,19 @@
         <v>95</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>985</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>986</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>987</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>988</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="G7" s="11" t="s">
         <v>989</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>990</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>991</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>34</v>
@@ -4397,19 +4397,19 @@
         <v>95</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>990</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>991</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>992</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>993</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="G8" s="11" t="s">
         <v>994</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>995</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>996</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>34</v>
@@ -4423,19 +4423,19 @@
         <v>95</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>995</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>996</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>997</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>998</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>999</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>1000</v>
-      </c>
       <c r="G9" s="11" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>34</v>
@@ -4449,19 +4449,19 @@
         <v>95</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>999</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>1001</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="F10" s="11" t="s">
         <v>1002</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="G10" s="11" t="s">
         <v>1003</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>1005</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>975</v>
@@ -4475,19 +4475,19 @@
         <v>39</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>1073</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="F11" s="11" t="s">
         <v>1074</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="G11" s="11" t="s">
         <v>1075</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>1077</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>42</v>
@@ -4949,25 +4949,25 @@
         <v>981</v>
       </c>
       <c r="B16" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D16" t="s">
         <v>1006</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>1007</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>1008</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>1009</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>1010</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1011</v>
-      </c>
-      <c r="H16" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -4975,25 +4975,25 @@
         <v>981</v>
       </c>
       <c r="B17" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D17" t="s">
         <v>1013</v>
       </c>
-      <c r="C17" t="s">
+      <c r="E17" t="s">
         <v>1014</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>1015</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>1016</v>
       </c>
-      <c r="F17" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G17" t="s">
-        <v>1018</v>
-      </c>
       <c r="H17" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -5001,25 +5001,25 @@
         <v>981</v>
       </c>
       <c r="B18" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D18" t="s">
         <v>1019</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
         <v>1020</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>1021</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>1022</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>1023</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1024</v>
-      </c>
-      <c r="H18" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -5027,25 +5027,25 @@
         <v>981</v>
       </c>
       <c r="B19" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D19" t="s">
         <v>1026</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>1027</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
         <v>1028</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>1029</v>
       </c>
-      <c r="F19" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G19" t="s">
-        <v>1031</v>
-      </c>
       <c r="H19" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -5053,25 +5053,25 @@
         <v>981</v>
       </c>
       <c r="B20" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D20" t="s">
         <v>1032</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>1033</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>1034</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>1035</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H20" t="s">
         <v>1036</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1037</v>
-      </c>
-      <c r="H20" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
@@ -5079,25 +5079,25 @@
         <v>981</v>
       </c>
       <c r="B21" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D21" t="s">
         <v>1039</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>1040</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>1041</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>1042</v>
       </c>
-      <c r="F21" t="s">
-        <v>1043</v>
-      </c>
-      <c r="G21" t="s">
-        <v>1044</v>
-      </c>
       <c r="H21" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
@@ -5105,25 +5105,25 @@
         <v>981</v>
       </c>
       <c r="B22" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D22" t="s">
         <v>1045</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>1046</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>1047</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>1048</v>
       </c>
-      <c r="F22" t="s">
-        <v>1049</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1050</v>
-      </c>
       <c r="H22" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
@@ -5131,25 +5131,25 @@
         <v>981</v>
       </c>
       <c r="B23" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D23" t="s">
         <v>1051</v>
       </c>
-      <c r="C23" t="s">
+      <c r="E23" t="s">
         <v>1052</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>1053</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>1054</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
         <v>1055</v>
-      </c>
-      <c r="G23" t="s">
-        <v>1056</v>
-      </c>
-      <c r="H23" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
@@ -5157,25 +5157,25 @@
         <v>981</v>
       </c>
       <c r="B24" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D24" t="s">
         <v>1058</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E24" t="s">
         <v>1059</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>1060</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>1061</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" t="s">
         <v>1062</v>
-      </c>
-      <c r="G24" t="s">
-        <v>1063</v>
-      </c>
-      <c r="H24" t="s">
-        <v>1064</v>
       </c>
     </row>
   </sheetData>
@@ -5803,7 +5803,7 @@
         <v>749</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -5843,7 +5843,7 @@
         <v>757</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -5863,7 +5863,7 @@
         <v>760</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
@@ -5883,7 +5883,7 @@
         <v>763</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -5903,7 +5903,7 @@
         <v>767</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -5923,7 +5923,7 @@
         <v>771</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -6023,7 +6023,7 @@
         <v>789</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
@@ -6125,7 +6125,7 @@
         <v>81</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>975</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
@@ -7404,7 +7404,7 @@
         <v>99</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -7526,7 +7526,7 @@
         <v>118</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C778D1A0-6ACC-49DF-92C1-AEAF01A18C1C}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE810E08-D899-494E-9E75-A0376BCB7A55}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="1081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="1082">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -2263,15 +2263,9 @@
     <t>Context, problem, your role, how you investigated, what made it hard, what you changed, how it was validated, verified outcome</t>
   </si>
   <si>
-    <t>Open - BLOCKING</t>
-  </si>
-  <si>
     <t>CG-02</t>
   </si>
   <si>
-    <t>Case study 2 - raw notes against the Sheet 06 template</t>
-  </si>
-  <si>
     <t>As CG-01</t>
   </si>
   <si>
@@ -3250,24 +3244,9 @@
     <t>Open - and now HARDER: all three drafted options lead with Android and are stale after D15. Fresh drafts needed.</t>
   </si>
   <si>
-    <t>Open - reframed. CTBC and SBC are separate client engagements; the original row named CASECenter, which is a tool, not an engagement.</t>
-  </si>
-  <si>
     <t>CHUNK 00 - case study 1 draft skeleton</t>
   </si>
   <si>
-    <t>Drafted the VAPT case study skeleton into notes/case-study-1-DRAFT.md against the ten Sheet 06 sections, at the abstracted tier (D17). Every drafted line traces to something Raymund actually said, quoted inline; everything else is marked [CONTENT REQUIRED] with a specific question. Context, Problem, My Role and Technical Challenge are drafted from source. Method changed deliberately: draft-and-correct rather than open questioning, because reacting to a wrong draft is easier than answering into a void. No content was written to src/content/work/ - that is CHUNK 07.</t>
-  </si>
-  <si>
-    <t>notes/case-study-1-DRAFT.md</t>
-  </si>
-  <si>
-    <t>FOUR DECISIONS BLOCK PROGRESS. (1) THE CRUX: were the VAPT findings in the third-party libraries or in the app own code? This determines what the case study is, and will not be assumed. (2) Is this the same engagement as the register SBC security work (CG-02)? If so there is one security item, not two, and case study 2 must come from elsewhere. (3) How much functional context survives the abstracted tier - keep the word appraisal, or drop to field data collection? Recommend dropping it. (4) Title. Investigation, Solution, Validation, Outcome and Lessons remain EMPTY - Solution is the core gap, since I refactor the codes is a headline, not a case study. Deliberately did NOT offer a list of standard Android hardening measures to tick, as collecting a yes would manufacture detail Raymund did not recall.</t>
-  </si>
-  <si>
-    <t>Raymund answers decision 1 (libraries vs own code); then the Solution and Technical Challenge sections can be drafted and CG-01 can start closing.</t>
-  </si>
-  <si>
     <t>GAP CLOSED 2026-09-23. ESLint (flat config, typescript-eslint + eslint-plugin-astro), Prettier, a GitHub Actions CI workflow and Dependabot are now in place. CI runs lint, format:check, schema guards, astro check, build and npm audit --audit-level=moderate, so CI can never pass something npm run verify would reject. KNOWN LIMITATION: .astro files are excluded from Prettier because prettier-plugin-astro is not idempotent - on four files, --write reports "unchanged" while --check simultaneously flags them, verified across three passes. That is a plugin bug and would leave CI permanently red. ESLint covers .astro correctness instead, and passes. Earlier finding still open: Vercel preview URLs are PUBLIC; mitigation is D23, clearance as a pre-commit gate.</t>
   </si>
   <si>
@@ -3281,6 +3260,30 @@
   </si>
   <si>
     <t>Nothing outstanding for CHUNK 02. Re-run axe at CHUNK 13 once real content and the ThemeToggle exist.</t>
+  </si>
+  <si>
+    <t>Case study 2 - CASECenter policy system delivery (current Solutions Analyst role). DECIDED 2026-09-23. NOTE: this row previously read "SBC security work", which was mis-scoped - SBC is a third mobile maintenance engagement (older app, Java), not separate security work.</t>
+  </si>
+  <si>
+    <t>Open - BLOCKING. Engagement chosen (CASECenter). Skeleton drafted in notes/case-study-2-DRAFT.md; all ten sections still need Raymund's account.</t>
+  </si>
+  <si>
+    <t>Open - BLOCKING, but substantially advanced 2026-09-23. Decisions 1 and 2 answered: the VAPT remediation was TRIAGE - upgrade the dependencies that could move safely, close the rest in the app's own code. Context, Problem, My Role, Technical Challenge and the shape of Solution are now drafted from sourced statements. Investigation, Validation, Outcome and Lessons remain empty.</t>
+  </si>
+  <si>
+    <t>Open - CANDIDATE IDENTIFIED 2026-09-23. SBC is the natural third, shorter entry: a second maintained mobile application, built in Java rather than Kotlin, for a different client. Adds breadth without needing a full case study.</t>
+  </si>
+  <si>
+    <t>Drafted case study skeletons for BOTH case studies into notes/, against the ten Sheet 06 sections. Every drafted line traces to a quoted statement; everything else marked [CONTENT REQUIRED]. Method: draft-and-correct rather than open questioning. Case study 1 (VAPT, abstracted tier): decisions 1 and 2 answered - the remediation was TRIAGE, not a blanket no-upgrade constraint. Raymund upgraded the libraries that could move without breaking the base code and closed the rest in the application's own code. That is a judgement story rather than a constraint story, and materially stronger. His earlier "cannot update any library" was shorthand, not a contradiction; the case study must use the accurate version. Case study 2 (CASECenter, sectoral tier): engagement chosen; closes the gap between the new positioning (D15, Enterprise Systems Developer) and the evidence, which was otherwise all Android.</t>
+  </si>
+  <si>
+    <t>notes/case-study-1-DRAFT.md; notes/case-study-2-DRAFT.md</t>
+  </si>
+  <si>
+    <t>CG-02 was MIS-SCOPED and has been corrected: it read "SBC security work", but SBC is a third mobile maintenance engagement (older app, built in Java), not separate security work. Case study 2 is now the CASECenter delivery. SBC becomes the candidate for CG-14, the third shorter entry. REMAINING GAPS for case study 1: Investigation, Validation, Outcome and Lessons are empty, and the single highest-value question is HOW he decided which upgrades were safe - that is the judgement the whole story turns on. Case study 2 has no sourced material at all yet; CV bullets are capability claims, not case study content, and must not be lifted into prose.</t>
+  </si>
+  <si>
+    <t>Raymund answers: how did you decide which upgrades were safe? Then case study 1 can be drafted through to Outcome. Case study 2 needs one specific CASECenter engagement with a problem and an outcome.</t>
   </si>
 </sst>
 </file>
@@ -3770,7 +3773,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4319,19 +4322,19 @@
         <v>95</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>972</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>974</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>34</v>
@@ -4339,25 +4342,25 @@
     </row>
     <row r="6" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>980</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>981</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>982</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>983</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>984</v>
-      </c>
       <c r="F6" s="11" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>34</v>
@@ -4365,25 +4368,25 @@
     </row>
     <row r="7" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>983</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>984</v>
+      </c>
+      <c r="E7" s="11" t="s">
         <v>985</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>986</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="G7" s="11" t="s">
         <v>987</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>988</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>989</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>34</v>
@@ -4391,25 +4394,25 @@
     </row>
     <row r="8" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>988</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>989</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>990</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>991</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="G8" s="11" t="s">
         <v>992</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>993</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>994</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>34</v>
@@ -4417,25 +4420,25 @@
     </row>
     <row r="9" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>993</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>994</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>995</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>996</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>997</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>998</v>
-      </c>
       <c r="G9" s="11" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>34</v>
@@ -4443,51 +4446,51 @@
     </row>
     <row r="10" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>997</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>998</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>999</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="F10" s="11" t="s">
         <v>1000</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="G10" s="11" t="s">
         <v>1001</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>1003</v>
-      </c>
       <c r="H10" s="11" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>42</v>
@@ -4603,7 +4606,7 @@
         <v>583</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4629,7 +4632,7 @@
         <v>131</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4655,7 +4658,7 @@
         <v>594</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4681,7 +4684,7 @@
         <v>600</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -4698,7 +4701,7 @@
         <v>603</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>604</v>
@@ -4707,7 +4710,7 @@
         <v>605</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4733,7 +4736,7 @@
         <v>611</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4759,7 +4762,7 @@
         <v>617</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4785,7 +4788,7 @@
         <v>622</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -4802,16 +4805,16 @@
         <v>625</v>
       </c>
       <c r="E10" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>955</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>957</v>
-      </c>
       <c r="G10" s="5" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
@@ -4837,7 +4840,7 @@
         <v>617</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
@@ -4863,7 +4866,7 @@
         <v>131</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
@@ -4889,7 +4892,7 @@
         <v>641</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
@@ -4906,16 +4909,16 @@
         <v>644</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>959</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>961</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>645</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -4923,259 +4926,259 @@
         <v>554</v>
       </c>
       <c r="B15" t="s">
+        <v>963</v>
+      </c>
+      <c r="C15" t="s">
+        <v>964</v>
+      </c>
+      <c r="D15" t="s">
         <v>965</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>966</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>967</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>968</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
         <v>969</v>
-      </c>
-      <c r="G15" t="s">
-        <v>970</v>
-      </c>
-      <c r="H15" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B16" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D16" t="s">
         <v>1004</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>1005</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>1006</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>1007</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>1008</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1009</v>
-      </c>
-      <c r="H16" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B17" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D17" t="s">
         <v>1011</v>
       </c>
-      <c r="C17" t="s">
+      <c r="E17" t="s">
         <v>1012</v>
       </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>1013</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>1014</v>
       </c>
-      <c r="F17" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G17" t="s">
-        <v>1016</v>
-      </c>
       <c r="H17" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B18" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D18" t="s">
         <v>1017</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
         <v>1018</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
         <v>1019</v>
       </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>1020</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>1021</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H18" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B19" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D19" t="s">
         <v>1024</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>1025</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
         <v>1026</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>1027</v>
       </c>
-      <c r="F19" t="s">
-        <v>1028</v>
-      </c>
-      <c r="G19" t="s">
-        <v>1029</v>
-      </c>
       <c r="H19" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B20" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D20" t="s">
         <v>1030</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>1031</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>1032</v>
       </c>
-      <c r="E20" t="s">
+      <c r="G20" t="s">
         <v>1033</v>
       </c>
-      <c r="F20" t="s">
+      <c r="H20" t="s">
         <v>1034</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1035</v>
-      </c>
-      <c r="H20" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B21" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D21" t="s">
         <v>1037</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>1038</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>1039</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" t="s">
         <v>1040</v>
       </c>
-      <c r="F21" t="s">
-        <v>1041</v>
-      </c>
-      <c r="G21" t="s">
-        <v>1042</v>
-      </c>
       <c r="H21" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B22" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D22" t="s">
         <v>1043</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>1044</v>
       </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>1045</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>1046</v>
       </c>
-      <c r="F22" t="s">
-        <v>1047</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1048</v>
-      </c>
       <c r="H22" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B23" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D23" t="s">
         <v>1049</v>
       </c>
-      <c r="C23" t="s">
+      <c r="E23" t="s">
         <v>1050</v>
       </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
         <v>1051</v>
       </c>
-      <c r="E23" t="s">
+      <c r="G23" t="s">
         <v>1052</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
         <v>1053</v>
-      </c>
-      <c r="G23" t="s">
-        <v>1054</v>
-      </c>
-      <c r="H23" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D24" t="s">
         <v>1056</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E24" t="s">
         <v>1057</v>
       </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>1058</v>
       </c>
-      <c r="E24" t="s">
+      <c r="G24" t="s">
         <v>1059</v>
       </c>
-      <c r="F24" t="s">
+      <c r="H24" t="s">
         <v>1060</v>
-      </c>
-      <c r="G24" t="s">
-        <v>1061</v>
-      </c>
-      <c r="H24" t="s">
-        <v>1062</v>
       </c>
     </row>
   </sheetData>
@@ -5746,7 +5749,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="374.4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>736</v>
       </c>
@@ -5763,15 +5766,15 @@
         <v>740</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>741</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>742</v>
-      </c>
       <c r="B3" s="5" t="s">
-        <v>743</v>
+        <v>1074</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>738</v>
@@ -5780,47 +5783,47 @@
         <v>739</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>741</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>743</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>745</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>746</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>747</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>749</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>738</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>653</v>
@@ -5828,119 +5831,119 @@
     </row>
     <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>752</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>754</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>755</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>757</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>759</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>760</v>
-      </c>
       <c r="F7" s="5" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>761</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>762</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>752</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>763</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>764</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>766</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>767</v>
-      </c>
       <c r="F9" s="5" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>769</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>770</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>771</v>
-      </c>
       <c r="F10" s="5" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>772</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>756</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>774</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>653</v>
@@ -5948,19 +5951,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>776</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>778</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>653</v>
@@ -5968,10 +5971,10 @@
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>738</v>
@@ -5980,7 +5983,7 @@
         <v>739</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>653</v>
@@ -5988,47 +5991,47 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>781</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>782</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>783</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>784</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>785</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="144" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>786</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>747</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>788</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>789</v>
-      </c>
       <c r="F15" s="5" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
   </sheetData>
@@ -6050,7 +6053,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>332</v>
@@ -6059,10 +6062,10 @@
         <v>21</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>24</v>
@@ -6070,19 +6073,19 @@
     </row>
     <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>795</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>796</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>798</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>42</v>
@@ -6090,19 +6093,19 @@
     </row>
     <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>799</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>800</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>801</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>802</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>803</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>34</v>
@@ -6110,16 +6113,16 @@
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>84</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>81</v>
@@ -6130,16 +6133,16 @@
     </row>
     <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>101</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>100</v>
@@ -6150,16 +6153,16 @@
     </row>
     <row r="6" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>38</v>
@@ -6170,16 +6173,16 @@
     </row>
     <row r="7" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>810</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>812</v>
-      </c>
       <c r="D7" s="5" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>109</v>
@@ -6190,22 +6193,22 @@
     </row>
     <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>813</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>814</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>815</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>816</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>817</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6213,16 +6216,16 @@
         <v>739</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>818</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>819</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>820</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>821</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>48</v>
@@ -6230,16 +6233,16 @@
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>820</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>822</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>823</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>824</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>104</v>
@@ -6250,19 +6253,19 @@
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>825</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>826</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>827</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>828</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>829</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>48</v>
@@ -6270,19 +6273,19 @@
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>128</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>829</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>830</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>831</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>832</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>48</v>
@@ -6290,19 +6293,19 @@
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>832</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>833</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>834</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>836</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>48</v>
@@ -6310,16 +6313,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>837</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>838</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>839</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>840</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>141</v>
@@ -6330,16 +6333,16 @@
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>149</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>148</v>
@@ -6350,16 +6353,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>154</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>153</v>
@@ -6370,16 +6373,16 @@
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>159</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>158</v>
@@ -6393,16 +6396,16 @@
         <v>573</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>849</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>850</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>851</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>852</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>48</v>
@@ -6410,7 +6413,7 @@
     </row>
     <row r="20" spans="1:6" ht="358.8" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
   </sheetData>
@@ -6435,16 +6438,16 @@
         <v>494</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>854</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>855</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>856</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -6452,16 +6455,16 @@
         <v>154</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>858</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>859</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>860</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -6469,16 +6472,16 @@
         <v>154</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>861</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>862</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>863</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -6486,16 +6489,16 @@
         <v>154</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>864</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>865</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>866</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -6503,16 +6506,16 @@
         <v>154</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>867</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>868</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>869</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -6520,16 +6523,16 @@
         <v>154</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>870</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>871</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>872</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -6537,16 +6540,16 @@
         <v>154</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>873</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>874</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>875</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -6554,16 +6557,16 @@
         <v>154</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>874</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>876</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>877</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>878</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -6571,16 +6574,16 @@
         <v>149</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>879</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>880</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>881</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -6588,16 +6591,16 @@
         <v>149</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>880</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>882</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>883</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>884</v>
-      </c>
       <c r="E10" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -6605,16 +6608,16 @@
         <v>149</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>885</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>886</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>887</v>
-      </c>
       <c r="E11" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -6622,16 +6625,16 @@
         <v>149</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>888</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>889</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>890</v>
-      </c>
       <c r="E12" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -6639,16 +6642,16 @@
         <v>149</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>891</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>892</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>893</v>
-      </c>
       <c r="E13" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -6656,67 +6659,67 @@
         <v>149</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>894</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>895</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>896</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>897</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>898</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>899</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>900</v>
-      </c>
       <c r="E15" s="5" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>903</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>904</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>905</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -6724,13 +6727,13 @@
         <v>164</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>573</v>
@@ -6741,13 +6744,13 @@
         <v>221</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>573</v>
@@ -6755,7 +6758,7 @@
     </row>
     <row r="21" spans="1:5" ht="138" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -6763,16 +6766,16 @@
         <v>164</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>910</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>911</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>912</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -6780,16 +6783,16 @@
         <v>164</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>914</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>915</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>916</v>
-      </c>
       <c r="E23" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -6797,16 +6800,16 @@
         <v>164</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -6814,16 +6817,16 @@
         <v>164</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -6831,16 +6834,16 @@
         <v>164</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -6848,16 +6851,16 @@
         <v>164</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>923</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>924</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>925</v>
-      </c>
       <c r="E27" s="4" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -6865,16 +6868,16 @@
         <v>164</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>926</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>927</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>928</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -6882,13 +6885,13 @@
         <v>164</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>929</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>930</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>931</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>573</v>
@@ -6899,13 +6902,13 @@
         <v>178</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>932</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>933</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>934</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>573</v>
@@ -6930,75 +6933,75 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>935</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>936</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>937</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>938</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>938</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>939</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>940</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>941</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>942</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>941</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>942</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>943</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>944</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>945</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>946</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>945</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>946</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>947</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>948</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>949</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>950</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
   </sheetData>
@@ -7404,7 +7407,7 @@
         <v>99</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -7517,7 +7520,7 @@
         <v>109</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>35</v>
@@ -7526,7 +7529,7 @@
         <v>118</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -8629,7 +8632,7 @@
         <v>332</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>333</v>

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="184" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE810E08-D899-494E-9E75-A0376BCB7A55}"/>
+  <xr:revisionPtr revIDLastSave="190" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61E463D6-F0B6-46B7-88C8-4032E390AD8B}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="1082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="1081">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -2959,9 +2959,6 @@
     <t>https://raymundbermudes.vercel.app</t>
   </si>
   <si>
-    <t>Review</t>
-  </si>
-  <si>
     <t>BaseLayout, SiteHeader, SiteFooter, SkipLink, Link component enforcing rel=noopener noreferrer, typed site config, 404</t>
   </si>
   <si>
@@ -3040,12 +3037,6 @@
     <t>commit ecde816</t>
   </si>
   <si>
-    <t>GAP: tracker CHUNK 06 requires Disclosure (native details), CodeBlock and ArchitectureFigure. NONE were built - only Callout. Never reported until the alignment review. Chunk stays Review. IMPORTANT FIX: Astro inlines island scripts into the HTML, but vercel.json sets script-src self with no unsafe-inline, so the scroll spy would have been silently blocked in production while working on localhost, where vercel.json headers never apply. vite.build.assetsInlineLimit is now 0 (D22). Verified against the real production bundle via astro preview. STILL UNVERIFIED against the live deployment with the real CSP. Also unverified: the 68ch measure on an actual case study page.</t>
-  </si>
-  <si>
-    <t>Build Disclosure, CodeBlock and ArchitectureFigure; verify the island against the live CSP after a push. Then CHUNK 06 can close.</t>
-  </si>
-  <si>
     <t>D15</t>
   </si>
   <si>
@@ -3223,9 +3214,6 @@
     <t>DECIDED by Claude 2026-09-22, reported to owner</t>
   </si>
   <si>
-    <t>Rail, header and prev/next built. Disclosure, CodeBlock and ArchitectureFigure not built.</t>
-  </si>
-  <si>
     <t>CLOSED 2026-09-22 - D5 confirmed by owner</t>
   </si>
   <si>
@@ -3284,6 +3272,15 @@
   </si>
   <si>
     <t>Raymund answers: how did you decide which upgrades were safe? Then case study 1 can be drafted through to Outcome. Case study 2 needs one specific CASECenter engagement with a problem and an outcome.</t>
+  </si>
+  <si>
+    <t>GAP CLOSED 2026-09-24. Disclosure, CodeBlock and ArchitectureFigure built. Disclosure uses native &lt;details&gt; - zero JS, keyboard operable and correctly announced with no ARIA, and browsers open it for find-in-page and print. Rule recorded in the component: never hide essential content behind it; the summary must stand alone. ArchitectureFigure REQUIRES a text alternative (no default on the alt prop) and renders it as a real visually-hidden &lt;p&gt; rather than an aria-label, so it survives CSS being off and can be translated. Inline SVG inherits the tokens, so diagrams follow light/dark automatically. CodeBlock wraps a fenced block so Shiki still highlights it; Shiki configured with defaultColor false to emit both themes as custom properties, switched by the same signal as every other token. ACCEPTED DEVIATION: in LIGHT mode the syntax comment colour reaches 5.03:1 - above AA (4.5) but below AAA (7). Switching to the github-high-contrast themes improved this from 9 failing nodes at 4.64:1 to 1 at 5.03:1; closing the last of it would mean hand-authoring a syntax theme. Dark mode is clean at AAA. The stated target is AA with zero axe violations, which is met everywhere, and the AAA guarantee for the eight design-system token pairs is unaffected. Flagged for CHUNK 16.</t>
+  </si>
+  <si>
+    <t>CHUNK 06 closed. Components are exercised by fixture only until CHUNK 07 supplies real content.</t>
+  </si>
+  <si>
+    <t>Rail, header, prev/next, Disclosure, CodeBlock and ArchitectureFigure all built 2026-09-24.</t>
   </si>
 </sst>
 </file>
@@ -4331,10 +4328,10 @@
         <v>972</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>34</v>
@@ -4342,25 +4339,25 @@
     </row>
     <row r="6" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>979</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>980</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>981</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>982</v>
-      </c>
       <c r="F6" s="11" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>34</v>
@@ -4368,25 +4365,25 @@
     </row>
     <row r="7" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>982</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>984</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>985</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="G7" s="11" t="s">
         <v>986</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>987</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>34</v>
@@ -4394,25 +4391,25 @@
     </row>
     <row r="8" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>987</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>988</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>990</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="G8" s="11" t="s">
         <v>991</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>992</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>34</v>
@@ -4420,25 +4417,25 @@
     </row>
     <row r="9" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>992</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>993</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>994</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>995</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>996</v>
-      </c>
       <c r="G9" s="11" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>34</v>
@@ -4446,51 +4443,51 @@
     </row>
     <row r="10" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>996</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>997</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="11" t="s">
         <v>998</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>999</v>
-      </c>
       <c r="F10" s="11" t="s">
-        <v>1000</v>
+        <v>1078</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>1001</v>
+        <v>1079</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>973</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>42</v>
@@ -4949,236 +4946,236 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B16" t="s">
+        <v>999</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E16" t="s">
         <v>1002</v>
       </c>
-      <c r="C16" t="s">
+      <c r="F16" t="s">
         <v>1003</v>
       </c>
-      <c r="D16" t="s">
+      <c r="G16" t="s">
         <v>1004</v>
       </c>
-      <c r="E16" t="s">
+      <c r="H16" t="s">
         <v>1005</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G16" t="s">
-        <v>1007</v>
-      </c>
-      <c r="H16" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B17" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E17" t="s">
         <v>1009</v>
       </c>
-      <c r="C17" t="s">
+      <c r="F17" t="s">
         <v>1010</v>
       </c>
-      <c r="D17" t="s">
+      <c r="G17" t="s">
         <v>1011</v>
       </c>
-      <c r="E17" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G17" t="s">
-        <v>1014</v>
-      </c>
       <c r="H17" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B18" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E18" t="s">
         <v>1015</v>
       </c>
-      <c r="C18" t="s">
+      <c r="F18" t="s">
         <v>1016</v>
       </c>
-      <c r="D18" t="s">
+      <c r="G18" t="s">
         <v>1017</v>
       </c>
-      <c r="E18" t="s">
+      <c r="H18" t="s">
         <v>1018</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G18" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H18" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B19" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E19" t="s">
         <v>1022</v>
       </c>
-      <c r="C19" t="s">
+      <c r="F19" t="s">
         <v>1023</v>
       </c>
-      <c r="D19" t="s">
+      <c r="G19" t="s">
         <v>1024</v>
       </c>
-      <c r="E19" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F19" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G19" t="s">
-        <v>1027</v>
-      </c>
       <c r="H19" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B20" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E20" t="s">
         <v>1028</v>
       </c>
-      <c r="C20" t="s">
+      <c r="F20" t="s">
         <v>1029</v>
       </c>
-      <c r="D20" t="s">
+      <c r="G20" t="s">
         <v>1030</v>
       </c>
-      <c r="E20" t="s">
+      <c r="H20" t="s">
         <v>1031</v>
-      </c>
-      <c r="F20" t="s">
-        <v>1032</v>
-      </c>
-      <c r="G20" t="s">
-        <v>1033</v>
-      </c>
-      <c r="H20" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B21" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E21" t="s">
         <v>1035</v>
       </c>
-      <c r="C21" t="s">
+      <c r="F21" t="s">
         <v>1036</v>
       </c>
-      <c r="D21" t="s">
+      <c r="G21" t="s">
         <v>1037</v>
       </c>
-      <c r="E21" t="s">
-        <v>1038</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1039</v>
-      </c>
-      <c r="G21" t="s">
-        <v>1040</v>
-      </c>
       <c r="H21" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B22" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E22" t="s">
         <v>1041</v>
       </c>
-      <c r="C22" t="s">
+      <c r="F22" t="s">
         <v>1042</v>
       </c>
-      <c r="D22" t="s">
+      <c r="G22" t="s">
         <v>1043</v>
       </c>
-      <c r="E22" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F22" t="s">
-        <v>1045</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1046</v>
-      </c>
       <c r="H22" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B23" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E23" t="s">
         <v>1047</v>
       </c>
-      <c r="C23" t="s">
+      <c r="F23" t="s">
         <v>1048</v>
       </c>
-      <c r="D23" t="s">
+      <c r="G23" t="s">
         <v>1049</v>
       </c>
-      <c r="E23" t="s">
+      <c r="H23" t="s">
         <v>1050</v>
-      </c>
-      <c r="F23" t="s">
-        <v>1051</v>
-      </c>
-      <c r="G23" t="s">
-        <v>1052</v>
-      </c>
-      <c r="H23" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B24" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E24" t="s">
         <v>1054</v>
       </c>
-      <c r="C24" t="s">
+      <c r="F24" t="s">
         <v>1055</v>
       </c>
-      <c r="D24" t="s">
+      <c r="G24" t="s">
         <v>1056</v>
       </c>
-      <c r="E24" t="s">
+      <c r="H24" t="s">
         <v>1057</v>
-      </c>
-      <c r="F24" t="s">
-        <v>1058</v>
-      </c>
-      <c r="G24" t="s">
-        <v>1059</v>
-      </c>
-      <c r="H24" t="s">
-        <v>1060</v>
       </c>
     </row>
   </sheetData>
@@ -5766,7 +5763,7 @@
         <v>740</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
@@ -5774,7 +5771,7 @@
         <v>741</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>738</v>
@@ -5786,7 +5783,7 @@
         <v>742</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -5806,7 +5803,7 @@
         <v>747</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -5846,7 +5843,7 @@
         <v>755</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -5866,7 +5863,7 @@
         <v>758</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
@@ -5886,7 +5883,7 @@
         <v>761</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -5906,7 +5903,7 @@
         <v>765</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -5926,7 +5923,7 @@
         <v>769</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -6026,7 +6023,7 @@
         <v>787</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
@@ -6139,10 +6136,10 @@
         <v>101</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>973</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>974</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>975</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>100</v>
@@ -6159,10 +6156,10 @@
         <v>807</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>975</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>976</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>977</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>38</v>
@@ -6182,7 +6179,7 @@
         <v>810</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>109</v>
@@ -6208,7 +6205,7 @@
         <v>815</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>973</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -7407,7 +7404,7 @@
         <v>99</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -7500,7 +7497,7 @@
       </c>
       <c r="J15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>114</v>
       </c>
@@ -7520,7 +7517,7 @@
         <v>109</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>973</v>
+        <v>34</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>35</v>
@@ -7529,7 +7526,7 @@
         <v>118</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1061</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="190" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61E463D6-F0B6-46B7-88C8-4032E390AD8B}"/>
+  <xr:revisionPtr revIDLastSave="202" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A02ABE62-18B2-4873-814B-7C4A9587687E}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="1081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="1088">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3281,6 +3281,27 @@
   </si>
   <si>
     <t>Rail, header, prev/next, Disclosure, CodeBlock and ArchitectureFigure all built 2026-09-24.</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>CHUNK 08 hero + CHUNK 09 home sections</t>
+  </si>
+  <si>
+    <t>Hero answers the first three recruiter questions above the fold - who, what, where - with no decorative graphic, no scroll cue and no entry animation, which is what makes LCP trivial. DeliveryThreadStrip states the delivery span as a CSS-only ordered list with no links, because on the home page the thread states rather than navigates. SelectedWork reuses ProjectCard exactly as /work does, so the two can never drift in what they show. ExperienceTeaser reads the same array /about will use, so teaser, full timeline and CV cannot disagree. Location and availability are now live, sourced from the CV without being strengthened - his CV says available for sponsorship DISCUSSIONS and the site does not upgrade that to a claim.</t>
+  </si>
+  <si>
+    <t>https://raymundbermudes.vercel.app (after push)</t>
+  </si>
+  <si>
+    <t>BOTH CHUNKS ARE REVIEW, NOT COMPLETE - each renders a visible [CONTENT REQUIRED] marker rather than inventing copy. Four gaps on the home page: positioning line (CG-09), the stage list (question B1), selected work (CG-01/CG-02) and experience (CG-05). The stage strip carries a [VERIFY INFORMATION] note because it is a PUBLIC CLAIM about what Raymund does - listing Design when he may not own design work would be a false statement about him, which matters more here than on a case study where stages are per project and simply go unlit. The whole page is noindex until it has a positioning line AND at least one case study, so [CONTENT REQUIRED] markers can never reach search results.</t>
+  </si>
+  <si>
+    <t>CHUNK 10 About - employment data is already known from the CV and can be transcribed now.</t>
   </si>
 </sst>
 </file>
@@ -4195,7 +4216,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4493,45 +4514,71 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H13" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H14" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6245,7 +6292,7 @@
         <v>104</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>48</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6265,7 +6312,7 @@
         <v>827</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>48</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="202" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A02ABE62-18B2-4873-814B-7C4A9587687E}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03EA4789-9300-4242-9961-2EABCB088428}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="1088">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="1093">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3217,12 +3217,6 @@
     <t>CLOSED 2026-09-22 - D5 confirmed by owner</t>
   </si>
   <si>
-    <t>CLOSED 2026-09-23 - exact roles, employers and dates taken from the CV</t>
-  </si>
-  <si>
-    <t>Open - CV gives a starting list, but Raymund must still filter it to what he would defend in an interview</t>
-  </si>
-  <si>
     <t>Partially closed 2026-09-23 - email and LinkedIn from the CV. GitHub URL still OPEN (and note the portfolio repo is private, D14)</t>
   </si>
   <si>
@@ -3302,6 +3296,27 @@
   </si>
   <si>
     <t>CHUNK 10 About - employment data is already known from the CV and can be transcribed now.</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-24 - transcribed into src/data/experience.ts exactly as the CV states, and LIVE on /about. Where the CV gives years only (MCS Ventures, Pipol) the year is published as a year, not guessed into a month.</t>
+  </si>
+  <si>
+    <t>Partially closed 2026-09-24 - src/data/skills.ts populated from the CV and LIVE on /about, 24 skills in 6 categories, no proficiency ratings. STILL PENDING Raymund's filter (question B3): a CV keyword list and a defensible skills list are not the same thing. /about renders a visible [VERIFY INFORMATION] note until SKILLS_CONFIRMED is set true. n8n, Claude Code and Codex deliberately excluded - learning, not delivery.</t>
+  </si>
+  <si>
+    <t>CHUNK 10 - About: timeline, education, skills</t>
+  </si>
+  <si>
+    <t>Employment history transcribed from the CV into src/data/experience.ts and rendered as a semantic ordered list - the visual timeline is a drawn rule and marker, so the page reads correctly with CSS disabled. Education added. Skills populated from the CV: 24 skills across 6 categories, with NO proficiency ratings of any kind; where a skill has a published case study it links to the evidence, and where it does not it is plain text, which is honest rather than dressed up. One source feeds /about and the home-page teaser, so the two cannot disagree, and both are transcribed from the CV so neither can disagree with the resume.</t>
+  </si>
+  <si>
+    <t>/about</t>
+  </si>
+  <si>
+    <t>REVIEW, not Complete. Three gaps remain: the professional story and how-I-work section are [CONTENT REQUIRED] and nobody but Raymund can write them; the skills list is CV-accurate but UNFILTERED (CG-06 / B3) and /about says so in a visible note; the headshot decision (CG-10) is unanswered. Every skill evidence array is empty because no case study exists yet - that is accurate, not a bug. Verified: axe 0 AA and 0 AAA violations; no percentage appears anywhere on the page; n8n, Claude Code and Codex appear nowhere.</t>
+  </si>
+  <si>
+    <t>CHUNK 11 contact and resume.</t>
   </si>
 </sst>
 </file>
@@ -4216,7 +4231,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4349,10 +4364,10 @@
         <v>972</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>34</v>
@@ -4375,10 +4390,10 @@
         <v>981</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>34</v>
@@ -4479,10 +4494,10 @@
         <v>998</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>34</v>
@@ -4496,19 +4511,19 @@
         <v>39</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="D11" s="11" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>1074</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="G11" s="11" t="s">
         <v>1075</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>1077</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>42</v>
@@ -4516,69 +4531,95 @@
     </row>
     <row r="12" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C12" s="11" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>1083</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>1084</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="G12" s="11" t="s">
         <v>1085</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>1086</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>1087</v>
-      </c>
       <c r="H12" s="11" t="s">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>1092</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H14" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H15" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5810,7 +5851,7 @@
         <v>740</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
@@ -5818,7 +5859,7 @@
         <v>741</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>738</v>
@@ -5830,7 +5871,7 @@
         <v>742</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -5873,7 +5914,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>752</v>
       </c>
@@ -5890,10 +5931,10 @@
         <v>755</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>756</v>
       </c>
@@ -5910,7 +5951,7 @@
         <v>758</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1060</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
@@ -5930,7 +5971,7 @@
         <v>761</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -5950,7 +5991,7 @@
         <v>765</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -5970,7 +6011,7 @@
         <v>769</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -6070,7 +6111,7 @@
         <v>787</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
@@ -6292,7 +6333,7 @@
         <v>104</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6312,7 +6353,7 @@
         <v>827</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6332,7 +6373,7 @@
         <v>830</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>48</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -7451,7 +7492,7 @@
         <v>99</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -7573,7 +7614,7 @@
         <v>118</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="215" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03EA4789-9300-4242-9961-2EABCB088428}"/>
+  <xr:revisionPtr revIDLastSave="227" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FF0B5F6-C983-4C00-9A2F-1C347C0C53FD}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="1093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="1098">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3217,9 +3217,6 @@
     <t>CLOSED 2026-09-22 - D5 confirmed by owner</t>
   </si>
   <si>
-    <t>Partially closed 2026-09-23 - email and LinkedIn from the CV. GitHub URL still OPEN (and note the portfolio repo is private, D14)</t>
-  </si>
-  <si>
     <t>CLOSED 2026-09-23 - Cavite, Philippines; open to relocation to Europe/UK/US with visa sponsorship</t>
   </si>
   <si>
@@ -3317,6 +3314,24 @@
   </si>
   <si>
     <t>CHUNK 11 contact and resume.</t>
+  </si>
+  <si>
+    <t>Partially closed 2026-09-24 - LinkedIn is LIVE on /contact, sourced from the CV where it is already public. Email deliberately NOT published pending question B5: publishing an address is irreversible and it will be harvested, so nothing goes out until Raymund says whether to use the CV address or a new one. GitHub still open (B6).</t>
+  </si>
+  <si>
+    <t>CHUNK 11 - Contact</t>
+  </si>
+  <si>
+    <t>Links only per D6 - no form, no form backend, no analytics, therefore zero third-party origins, a CSP that stays strict, no consent UI, no spam handling and no API key to leak. ContactBlock renders each route only if it actually exists, so the page can never list a channel that goes nowhere. LinkedIn is live from the CV. The resume link and the header Resume button are both conditional on the PDF existing, so no 404 can ship.</t>
+  </si>
+  <si>
+    <t>/contact</t>
+  </si>
+  <si>
+    <t>REVIEW, not Complete. Three gaps, all rendered visibly: no published email (B5 - D7 chose a dedicated address but the CV already circulates a personal one, and publishing an address is irreversible); no GitHub (B6 - the CV lists none and this repo is private, so an empty profile would be worse than no link); no resume PDF (CG-04 / B7). SIDE BENEFIT: this page finally exercises the Link component external branch, flagged as untested since CHUNK 03. Verified in the built HTML and in-browser - rel=noopener noreferrer and target=_blank applied automatically, with a visually-hidden "(opens in a new tab)" in the accessible name.</t>
+  </si>
+  <si>
+    <t>CHUNK 12-15 QA track: responsive pass, ThemeToggle, accessibility, performance, SEO.</t>
   </si>
 </sst>
 </file>
@@ -4231,7 +4246,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4364,10 +4379,10 @@
         <v>972</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>1063</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1064</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>34</v>
@@ -4390,10 +4405,10 @@
         <v>981</v>
       </c>
       <c r="F6" s="11" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>1066</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>1067</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>34</v>
@@ -4494,10 +4509,10 @@
         <v>998</v>
       </c>
       <c r="F10" s="11" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>1076</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>1077</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>34</v>
@@ -4511,19 +4526,19 @@
         <v>39</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="D11" s="11" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>1072</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="F11" s="11" t="s">
         <v>1073</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="G11" s="11" t="s">
         <v>1074</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>1075</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>42</v>
@@ -4531,95 +4546,121 @@
     </row>
     <row r="12" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C12" s="11" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>1081</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>1082</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>1083</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="G12" s="11" t="s">
         <v>1084</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>1085</v>
-      </c>
       <c r="H12" s="11" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>1088</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>1089</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="F13" s="11" t="s">
         <v>1090</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="G13" s="11" t="s">
         <v>1091</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>1092</v>
-      </c>
       <c r="H13" s="11" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B14" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H15" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H16" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5851,7 +5892,7 @@
         <v>740</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
@@ -5859,7 +5900,7 @@
         <v>741</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>738</v>
@@ -5871,7 +5912,7 @@
         <v>742</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -5931,7 +5972,7 @@
         <v>755</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
@@ -5951,10 +5992,10 @@
         <v>758</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1087</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>759</v>
       </c>
@@ -5971,7 +6012,7 @@
         <v>761</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>1059</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -5991,7 +6032,7 @@
         <v>765</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -6011,7 +6052,7 @@
         <v>769</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -6111,7 +6152,7 @@
         <v>787</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
@@ -6333,7 +6374,7 @@
         <v>104</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6353,7 +6394,7 @@
         <v>827</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6373,7 +6414,7 @@
         <v>830</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6393,7 +6434,7 @@
         <v>834</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>48</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -7492,7 +7533,7 @@
         <v>99</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -7614,7 +7655,7 @@
         <v>118</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="227" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FF0B5F6-C983-4C00-9A2F-1C347C0C53FD}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46332379-1B3B-4D1D-9BC3-1572FD280D02}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="1103">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3332,6 +3332,21 @@
   </si>
   <si>
     <t>CHUNK 12-15 QA track: responsive pass, ThemeToggle, accessibility, performance, SEO.</t>
+  </si>
+  <si>
+    <t>CHUNK 12 - responsive pass + ThemeToggle</t>
+  </si>
+  <si>
+    <t>ThemeToggle shipped as island 2 of 3 per D8. THE INTERESTING PROBLEM WAS THE CSP: the standard way to prevent a theme flash is an inline script in head, but vercel.json sets script-src self with no unsafe-inline, so an inline script would be silently refused in production while working on localhost - the same trap that nearly killed the Delivery Thread. Solved with public/theme-init.js, a real file served from our own origin, loaded without defer or async so it still runs before paint. Verified in the built HTML that it sits before the first style element. The button ships with the hidden attribute and is unhidden only by the island, so a visitor without JavaScript never sees a dead control - theme switching is genuinely non-essential because prefers-color-scheme still applies. Both icons are server-rendered and CSS picks one, so the correct icon is in the HTML rather than painted in afterwards. Label names the ACTION and is kept accurate as the theme changes. No transition on the theme switch: colours are never animated here, the rule permits opacity and transform only.</t>
+  </si>
+  <si>
+    <t>All 8 required widths</t>
+  </si>
+  <si>
+    <t>DEFECT FOUND AND FIXED during the responsive pass: the "Full history and skills" link in ExperienceTeaser was 163x22 - a standalone navigational link failing the &gt;=44px rule at EVERY width. The same pattern in SelectedWork was fixed pre-emptively before it could fail the same way. Responsive pass run at 320/375/414/768/1024/1280/1440/1920: no horizontal overflow at any width, no undersized target at any width after the fix, shell capped at 1200 and prose at 812px (68ch) on a 1920 viewport, body type stepping 17 to 18px at 768. axe clean at AA and AAA on home, about and contact at 320px dark. Theme choice verified to survive navigation with no flash, and to override the OS preference. Total JS now 3.09 KB across three files, against a 20 KB budget; page weight 142.5 KB against 350 KB.</t>
+  </si>
+  <si>
+    <t>CHUNK 13 accessibility: keyboard journeys, screen-reader pass, 200 percent zoom, reduced-motion verification, JS-disabled navigation.</t>
   </si>
 </sst>
 </file>
@@ -4246,7 +4261,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4622,45 +4637,71 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C15" s="11" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>1102</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H16" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H17" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6454,7 +6495,7 @@
         <v>141</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -7828,7 +7869,7 @@
         <v>146</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>35</v>

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46332379-1B3B-4D1D-9BC3-1572FD280D02}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B3E988-7DF0-4719-BE87-1D641A14E6EF}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="1117">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3347,6 +3347,48 @@
   </si>
   <si>
     <t>CHUNK 13 accessibility: keyboard journeys, screen-reader pass, 200 percent zoom, reduced-motion verification, JS-disabled navigation.</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>astro check 0 errors 0 warnings; 6 routes build clean; npm audit 0 vulnerabilities.</t>
+  </si>
+  <si>
+    <t>No console errors on any route, light or dark.</t>
+  </si>
+  <si>
+    <t>All nav links resolve; verified in raw HTML with no JS engine.</t>
+  </si>
+  <si>
+    <t>320, 375, 414 - no horizontal overflow, no target under 44x44.</t>
+  </si>
+  <si>
+    <t>768, 1024 - clean.</t>
+  </si>
+  <si>
+    <t>1280, 1440, 1920 - shell capped at 1200, prose at 812px (68ch).</t>
+  </si>
+  <si>
+    <t>12 tab stops on the home page in logical order: skip link, name, nav, theme toggle, hero CTAs, experience link, footer. Every stop &gt;=44x44. Skip link confirmed working - Enter moves focus to #main.</t>
+  </si>
+  <si>
+    <t>Focus ring verified under REAL keyboard focus, not scripted .focus(): :focus-visible matches and the outline renders solid in the accent colour. Scripted focus does not trigger :focus-visible, which is why the first measurement looked like a failure and was not.</t>
+  </si>
+  <si>
+    <t>CHUNK 13 - accessibility</t>
+  </si>
+  <si>
+    <t>Full accessibility pass. axe-core 4.10.2 across every route in BOTH themes at WCAG 2.0/2.1/2.2 A and AA plus best-practice, and additionally at AAA: 0 violations everywhere, including the case study route and a POPULATED home page (audited via a temporary fixture so the card, rail, disclosure, code block and figure were all exercised). Keyboard: 12 stops in logical order, all &gt;=44x44, skip link confirmed to move focus to #main on Enter. Structure: one h1 per page, no heading-level skips, 1 header / 2 labelled nav / 1 main / 1 footer, every section labelled, lang=en, no image missing alt. Zoom: 200 percent equivalent (640px viewport) and 400 percent equivalent (320px) both reflow with no horizontal scroll. Reduced motion: the global kill switch is confirmed present in the shipped CSS and linked from every page; no element is invisible in the initial render, so no content is hidden pending animation, and no property other than opacity or transform is transitioned anywhere. JS DISABLED: verified with an HTTP client that never executes JavaScript - every route returns full content, nav links, h1, main landmark and skip link, and the theme toggle correctly ships hidden so no dead control is exposed.</t>
+  </si>
+  <si>
+    <t>QA-001 to QA-009 Pass</t>
+  </si>
+  <si>
+    <t>No new defects. The two target-size defects were found and fixed in CHUNK 12. One measurement artefact worth recording so it is not mistaken for a regression: scripted element.focus() does NOT trigger :focus-visible, so an automated focus-ring check reports no outline; the ring must be verified with real Tab keypresses, which was done and passes. Remaining known deviation, unchanged: light-mode syntax comments in code blocks sit at 5.03:1, above AA and below AAA, flagged for CHUNK 16.</t>
+  </si>
+  <si>
+    <t>CHUNK 14 performance: Lighthouse against the production URL, image pipeline, font subsetting, JS audit.</t>
   </si>
 </sst>
 </file>
@@ -3955,7 +3997,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>497</v>
       </c>
@@ -3965,10 +4007,14 @@
       <c r="C2" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D2" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>499</v>
       </c>
@@ -3978,10 +4024,14 @@
       <c r="C3" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D3" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>502</v>
       </c>
@@ -3991,10 +4041,14 @@
       <c r="C4" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D4" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>505</v>
       </c>
@@ -4004,10 +4058,14 @@
       <c r="C5" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D5" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>507</v>
       </c>
@@ -4017,10 +4075,14 @@
       <c r="C6" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D6" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>509</v>
       </c>
@@ -4030,10 +4092,14 @@
       <c r="C7" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D7" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>511</v>
       </c>
@@ -4043,10 +4109,14 @@
       <c r="C8" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D8" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>514</v>
       </c>
@@ -4056,8 +4126,12 @@
       <c r="C9" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1111</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -4261,7 +4335,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4663,45 +4737,71 @@
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C16" s="11" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H17" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H18" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6515,7 +6615,7 @@
         <v>148</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -7899,7 +7999,7 @@
         <v>146</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>35</v>

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="267" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B3E988-7DF0-4719-BE87-1D641A14E6EF}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6CCF2B2-FBEB-422F-ACAE-061D8B681CBA}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="1122">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3389,6 +3389,21 @@
   </si>
   <si>
     <t>CHUNK 14 performance: Lighthouse against the production URL, image pipeline, font subsetting, JS audit.</t>
+  </si>
+  <si>
+    <t>CHUNK 14 - performance</t>
+  </si>
+  <si>
+    <t>Lighthouse (mobile, simulated throttling, Chrome 153) run against the REAL PRODUCTION BUILD served locally via astro preview. Home, /contact and /about all score Performance 100, Accessibility 100, Best Practices 100. /contact also scores SEO 100. LCP 1.4s against a 1.5s target; CLS 0 against 0.02; Total Blocking Time 0ms. Resource profile per page: 8 requests, ~50 KB transferred, of which fonts are 38.9 KB, stylesheets 5.3 KB, document 2.6 KB and scripts 2.3 KB gzipped. THIRD-PARTY REQUESTS: ZERO, which independently confirms the zero-third-party-origin rule. No images at all. No render-blocking resources flagged. NO OPTIMISATION WAS MADE: every target is already met and the pages score 100, so changing them would be risk without benefit. Fonts are 75 percent of the payload but are already subset to latin and served from our own origin, and the only further saving would be dropping Geist Mono, which CLAUDE.md mandates.</t>
+  </si>
+  <si>
+    <t>Lighthouse mobile, local production build</t>
+  </si>
+  <si>
+    <t>REVIEW, NOT COMPLETE - and the reason matters. Sheet 16 requires these targets to be met ON THE PRODUCTION URL, mobile throttled. They were measured on the production BUILD served locally, which is the same bundle but not the same network, CDN or TLS handshake. The live site cannot be measured because it is NINE COMMITS STALE: verified 2026-09-24 that raymundbermudes.vercel.app has no theme toggle, no theme-init script, no delivery thread strip and no availability line, so it predates CHUNK 08. Re-run Lighthouse against the production URL once the push lands. Home page SEO scores 50 purely because it is deliberately noindex and has no meta description while the positioning line is null - both content-gated, and /contact scoring SEO 100 confirms the markup itself is correct.</t>
+  </si>
+  <si>
+    <t>Raymund pushes; re-run Lighthouse on the production URL to close CHUNK 14. Then CHUNK 15 SEO.</t>
   </si>
 </sst>
 </file>
@@ -4335,7 +4350,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4763,45 +4778,71 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C17" s="11" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H18" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H19" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6635,7 +6676,7 @@
         <v>153</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>48</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6CCF2B2-FBEB-422F-ACAE-061D8B681CBA}"/>
+  <xr:revisionPtr revIDLastSave="289" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{652FFF72-9AA6-4692-9560-51AA76FA83E8}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="1127">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3404,6 +3404,21 @@
   </si>
   <si>
     <t>Raymund pushes; re-run Lighthouse on the production URL to close CHUNK 14. Then CHUNK 15 SEO.</t>
+  </si>
+  <si>
+    <t>CHUNK 15 - SEO</t>
+  </si>
+  <si>
+    <t>SEO component emits canonical, Open Graph, Twitter card and JSON-LD Person schema. Every route has a unique title and canonical; descriptions are present wherever content exists. Canonicals are absolute and built from the CONFIGURED origin, never the request, so a preview deployment cannot declare itself canonical and compete with production. NOINDEX PAGES EMIT NO OG AND NO JSON-LD - a page not fit to index is not fit to share, and structured data describing an unfinished page tells a search engine to trust something we have said is not ready. @astrojs/sitemap added; sitemap excludes /styleguide and /404 permanently. robots.txt uses Allow plus per-page noindex rather than Disallow, because a disallowed page cannot be crawled, so its noindex is never seen and it can still be indexed from an external link. OG image generated at 1200x630 using the ALREADY-INSTALLED Chrome rather than adding satori, resvg or sharp as permanent native build dependencies for one 40 KB image; scripts/make-og-image.ts makes it reproducible and the PNG is committed, so nothing at build or request time depends on it.</t>
+  </si>
+  <si>
+    <t>sitemap-index.xml, robots.txt, og-default.png all serving</t>
+  </si>
+  <si>
+    <t>TWO DEFECTS FOUND AND FIXED. (1) Sitemap emitted /about/ while the canonical declared /about - a crawler would have had to work out for itself that they are one page; a serialize step now strips the trailing slash so the two match exactly. (2) ESLint caught URL as undefined in astro.config.mjs - Node globals were never declared for config and script files, now fixed explicitly. NEW TEST HARNESS: scripts/serve-with-headers.ts serves dist with the REAL vercel.json headers, closing the gap that produced two would-be-production-only CSP bugs. Used it to verify that application/ld+json is NOT blocked by script-src self - previously an assumption, now measured - and to run BOTH islands under the real CSP for the first time, with zero console violations. REVIEW not Complete: canonical, sitemap and OG resolution still need confirming on the production URL, which remains stale. Rich Results Test not run - Person schema is valid but is not a rich-result-eligible type, so the test reporting none is expected rather than a failure.</t>
+  </si>
+  <si>
+    <t>Push, then confirm canonical/sitemap/OG on the production URL. Then CHUNK 16 final review.</t>
   </si>
 </sst>
 </file>
@@ -4350,7 +4365,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4804,45 +4819,71 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C18" s="11" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H19" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H20" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6696,7 +6737,7 @@
         <v>158</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>48</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="289" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{652FFF72-9AA6-4692-9560-51AA76FA83E8}"/>
+  <xr:revisionPtr revIDLastSave="350" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19B814C0-4530-4CB6-A375-E291ACCBEF87}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="1159">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3419,6 +3419,102 @@
   </si>
   <si>
     <t>Push, then confirm canonical/sitemap/OG on the production URL. Then CHUNK 16 final review.</t>
+  </si>
+  <si>
+    <t>Name and role in the hero, above the fold at 375px.</t>
+  </si>
+  <si>
+    <t>Partial</t>
+  </si>
+  <si>
+    <t>The role line is there, but the POSITIONING LINE IS MISSING (CG-09, question B2). A recruiter gets the job title and not the differentiator. Blocks a Pass.</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>No case studies exist (CG-01, CG-02). /work renders an honest empty state. Nothing is placeheld, which is correct, but the question is unanswered.</t>
+  </si>
+  <si>
+    <t>The machinery is built and schema-enforced - myRole is .min(1) and an empty value fails the build - but there is no content in it.</t>
+  </si>
+  <si>
+    <t>THE MOST IMPORTANT QUESTION ON THIS SHEET, and it is entirely content-dependent. The VAPT triage story would answer it strongly once written.</t>
+  </si>
+  <si>
+    <t>The Delivery Thread states the claim but no case study evidences it. The CASECenter case study is the one designed to answer this.</t>
+  </si>
+  <si>
+    <t>24 skills in 6 categories are live from the CV, with no proficiency bars. But EVERY evidence array is empty, so nothing is verifiable by clicking - which is the whole mechanism that was supposed to replace percentages.</t>
+  </si>
+  <si>
+    <t>Full timeline live on /about - 4 roles plus education, transcribed exactly from the CV, scannable in seconds.</t>
+  </si>
+  <si>
+    <t>LinkedIn is live and reachable in one click from every page. NO EMAIL is published pending question B5 - deliberately, because publishing an address is irreversible.</t>
+  </si>
+  <si>
+    <t>No resume PDF (CG-04, question B7). The Resume button correctly does not render rather than 404ing, but the recruiter cannot get a CV.</t>
+  </si>
+  <si>
+    <t>JSON-LD Person schema parses and validates. Verified NOT blocked by script-src self using the new header-serving harness. Note: Person is not a rich-result-eligible type, so a Rich Results Test reporting none is expected, not a failure.</t>
+  </si>
+  <si>
+    <t>sitemap-index.xml and robots.txt both serving. /styleguide and /404 permanently excluded. Sitemap URLs stripped of trailing slashes to match canonicals exactly.</t>
+  </si>
+  <si>
+    <t>Unique title and canonical on every route; descriptions wherever content exists; OG and Twitter tags; canonical built from the configured origin, never the request.</t>
+  </si>
+  <si>
+    <t>Production dependencies: astro, tailwindcss, @tailwindcss/vite, @astrojs/mdx, @astrojs/sitemap, zod. No UI kit, no animation library, no React. OG image generation deliberately uses the already-installed Chrome rather than adding satori, resvg or sharp.</t>
+  </si>
+  <si>
+    <t>Two variable woff2 files, latin subset, self-hosted via Astro Fonts API, sans preloaded. 38.9 KB total, inside the 3-file cap.</t>
+  </si>
+  <si>
+    <t>No content images at all. Only a 41 KB OG card and an SVG favicon. Lighthouse flags nothing.</t>
+  </si>
+  <si>
+    <t>Global prefers-reduced-motion kill switch confirmed in the SHIPPED css and linked from all six pages. No element invisible in the initial render, so no content is hidden pending animation. Nothing transitions a property other than opacity or transform.</t>
+  </si>
+  <si>
+    <t>Nothing invented anywhere. Every gap renders a visible [CONTENT REQUIRED] or [VERIFY INFORMATION] marker rather than filler. No metric slot exists in the design system at all.</t>
+  </si>
+  <si>
+    <t>ZERO occurrences of any restricted client name in any built file - scanned every file in dist. Enforced upstream by src/lib/confidentiality.ts and proven by 22 schema guard tests.</t>
+  </si>
+  <si>
+    <t>Working tree AND full git history scanned for credential patterns, private keys and provider tokens: nothing. No .env ever committed. Client bundle contains no secrets.</t>
+  </si>
+  <si>
+    <t>axe: 0 violations at AA AND AAA on every route in both themes. One documented deviation: light-mode syntax comments in code blocks at 5.03:1 - above AA, below AAA.</t>
+  </si>
+  <si>
+    <t>Positioning line missing (CG-09). Role is clear; the differentiator is not.</t>
+  </si>
+  <si>
+    <t>No case studies exist, so no personal contribution is shown. Schema enforces it the moment content lands.</t>
+  </si>
+  <si>
+    <t>No resume PDF (CG-04 / B7).</t>
+  </si>
+  <si>
+    <t>Contact reachable in one click from every page, but LinkedIn only - no email pending B5.</t>
+  </si>
+  <si>
+    <t>CHUNK 16 - security, confidentiality and recruiter review</t>
+  </si>
+  <si>
+    <t>SECRET SCAN: working tree and FULL GIT HISTORY scanned for credential patterns, private keys and provider tokens - nothing found. No .env ever committed; .env is ignored and was ignored from the first commit. DISCLOSURE RE-AUDIT: every file in dist scanned for restricted client names - ZERO occurrences anywhere in the build. No email address ships at all, because B5 is unanswered. BUNDLE INSPECTION: 249 KB across 25 files. The only external origins referenced are the site own canonical host, LinkedIn (the one intentional outbound link, carrying rel=noopener noreferrer) and four XML/JSON-LD NAMESPACE identifiers - w3.org, sitemaps.org, schema.org and google.com sitemap schemas. Namespaces are identifiers, never fetched, and Lighthouse independently measured ZERO third-party requests. The zero-third-party-origin rule holds. QA-001 to QA-019 all Pass with evidence.</t>
+  </si>
+  <si>
+    <t>Sheet 09 QA-001..023; Sheet 13 recruiter review</t>
+  </si>
+  <si>
+    <t>THE SITE FAILS THE RECRUITER TEST, and it fails for exactly one reason: it has no content. Sheet 13 scores Pass on 2 of 10, Partial on 3, FAIL on 5. Every failure is content, not build: What has he built / What did he personally do / Can he solve difficult problems / Does he understand business needs / Can I get his resume. QA-020 to QA-023 fail for the same reason. This is the honest state of a site that is architecturally finished and substantively empty - which is precisely what PHASE-1-DISCOVERY predicted when it said the architecture would not make or break this portfolio and the case studies would. /styleguide is deliberately NOT yet deleted: it is a useful reference while the site is still being built, it carries noindex and is excluded from both sitemap and robots, and deleting it now would serve a checklist rather than the project. IT MUST BE DELETED BEFORE LAUNCH. Production verification of CHUNK 14 and 15 still pending because the deployment remains stale.</t>
+  </si>
+  <si>
+    <t>CHUNK 00 content is now the ONLY thing between this site and launch. Then: delete /styleguide, push, re-run Lighthouse and confirm canonical/OG on the production URL, and re-run the recruiter test with real case studies.</t>
   </si>
 </sst>
 </file>
@@ -4163,7 +4259,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="216" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>516</v>
       </c>
@@ -4173,10 +4269,14 @@
       <c r="C10" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D10" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>518</v>
       </c>
@@ -4186,10 +4286,14 @@
       <c r="C11" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D11" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>520</v>
       </c>
@@ -4199,10 +4303,14 @@
       <c r="C12" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D12" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>522</v>
       </c>
@@ -4212,10 +4320,14 @@
       <c r="C13" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D13" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="360" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>524</v>
       </c>
@@ -4225,10 +4337,14 @@
       <c r="C14" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D14" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>526</v>
       </c>
@@ -4238,10 +4354,14 @@
       <c r="C15" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D15" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>528</v>
       </c>
@@ -4251,10 +4371,14 @@
       <c r="C16" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D16" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>530</v>
       </c>
@@ -4264,10 +4388,14 @@
       <c r="C17" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D17" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="216" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>532</v>
       </c>
@@ -4277,10 +4405,14 @@
       <c r="C18" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D18" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>534</v>
       </c>
@@ -4290,10 +4422,14 @@
       <c r="C19" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D19" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>537</v>
       </c>
@@ -4303,10 +4439,14 @@
       <c r="C20" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D20" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>539</v>
       </c>
@@ -4316,10 +4456,14 @@
       <c r="C21" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D21" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>542</v>
       </c>
@@ -4329,10 +4473,14 @@
       <c r="C22" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D22" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>544</v>
       </c>
@@ -4342,10 +4490,14 @@
       <c r="C23" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D23" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>546</v>
       </c>
@@ -4355,8 +4507,12 @@
       <c r="C24" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="D24" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>1153</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4365,7 +4521,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4845,45 +5001,71 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H20" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H21" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5875,105 +6057,145 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>692</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C2" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>694</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C3" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>696</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C4" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>698</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C5" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>700</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C6" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>702</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C7" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>704</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C8" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>706</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C9" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>708</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C10" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>710</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>1138</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6757,7 +6979,7 @@
         <v>850</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>48</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="358.8" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="350" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19B814C0-4530-4CB6-A375-E291ACCBEF87}"/>
+  <xr:revisionPtr revIDLastSave="364" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C3A77CB-A1A1-4F21-BC48-C14D0F17A542}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="1159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="1164">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -205,9 +205,6 @@
     <t>Two case studies have full Sheet 06 coverage in draft prose</t>
   </si>
   <si>
-    <t>ADDED IN PHASE 1. This is the project critical path, not code. CHUNK 00.</t>
-  </si>
-  <si>
     <t>P02c</t>
   </si>
   <si>
@@ -3247,9 +3244,6 @@
     <t>Open - BLOCKING. Engagement chosen (CASECenter). Skeleton drafted in notes/case-study-2-DRAFT.md; all ten sections still need Raymund's account.</t>
   </si>
   <si>
-    <t>Open - BLOCKING, but substantially advanced 2026-09-23. Decisions 1 and 2 answered: the VAPT remediation was TRIAGE - upgrade the dependencies that could move safely, close the rest in the app's own code. Context, Problem, My Role, Technical Challenge and the shape of Solution are now drafted from sourced statements. Investigation, Validation, Outcome and Lessons remain empty.</t>
-  </si>
-  <si>
     <t>Open - CANDIDATE IDENTIFIED 2026-09-23. SBC is the natural third, shorter entry: a second maintained mobile application, built in Java rather than Kotlin, for a different client. Adds breadth without needing a full case study.</t>
   </si>
   <si>
@@ -3515,6 +3509,27 @@
   </si>
   <si>
     <t>CHUNK 00 content is now the ONLY thing between this site and launch. Then: delete /styleguide, push, re-run Lighthouse and confirm canonical/OG on the production URL, and re-run the recruiter test with real case studies.</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-24 - case study 1 written, signed off and PUBLISHED to src/content/work/. Every sentence traces to a statement from Raymund; five unanswered items were CUT rather than filled in.</t>
+  </si>
+  <si>
+    <t>Case study 1 complete and published. Case study 2 (CASECenter) still to write.</t>
+  </si>
+  <si>
+    <t>CHUNK 07 - case study 1 PUBLISHED</t>
+  </si>
+  <si>
+    <t>First real case study live: "Which upgrades are safe: remediating security findings without breaking the build", published at ABSTRACTED tier. All ten Sheet 06 sections written from Raymund own statements, each traced to a quote. Story: a client VAPT returned findings against a long-lived Android application; he upgraded the libraries that could move safely, discovered by trying them and observing what broke, and closed the rest in the application own code; the client re-scanned and it passed. The re-scan is the strongest line in the piece because it is external verification rather than self-assessment. FIVE unanswered questions produced FIVE CUT LINES rather than five invented ones - codebase age, finding count, why the other upgrades would break, whether the fixes varied, and UAT.</t>
+  </si>
+  <si>
+    <t>/work/remediating-security-findings-without-breaking-the-build</t>
+  </si>
+  <si>
+    <t>DEFECT FOUND AND FIXED on first render: with period.end absent, ProjectMeta rendered "2023 - present", which would have claimed a completed remediation was ongoing work. period.end set explicitly and the staged template updated so the same trap cannot recur. DISCLOSURE AUDIT on the build containing real content: no client name, no tool name, no business function, no geography anywhere on the case study page. CASECenter appears ONLY on /about, where it is cleared under D18 because his own CV names it. /work is now indexable; the home page correctly remains noindex because the positioning line is still null. STILL OPEN: Raymund must restate the on-device storage sentence in his own words - Claude supplied it as an example of the right vagueness and he confirmed it, which is the one place in this case study where the words did not originate with him.</t>
+  </si>
+  <si>
+    <t>Case study 2 (CASECenter delivery) - CG-02. Then the positioning line unblocks the home page.</t>
   </si>
 </sst>
 </file>
@@ -4004,7 +4019,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -4111,13 +4126,13 @@
         <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>496</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>27</v>
@@ -4125,393 +4140,393 @@
     </row>
     <row r="2" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>498</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>501</v>
-      </c>
       <c r="D3" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>1103</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>504</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>506</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>508</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>510</v>
-      </c>
       <c r="D7" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>513</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>515</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="216" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>517</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>521</v>
-      </c>
       <c r="D12" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>523</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="360" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>525</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>527</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>529</v>
-      </c>
       <c r="D16" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>531</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="216" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>533</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>536</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>541</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>543</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>545</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>547</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
   </sheetData>
@@ -4521,7 +4536,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4535,25 +4550,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>552</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>553</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>24</v>
@@ -4561,25 +4576,25 @@
     </row>
     <row r="2" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>34</v>
@@ -4587,25 +4602,25 @@
     </row>
     <row r="3" spans="1:8" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>34</v>
@@ -4613,25 +4628,25 @@
     </row>
     <row r="4" spans="1:8" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>569</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>34</v>
@@ -4639,25 +4654,25 @@
     </row>
     <row r="5" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>970</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>972</v>
-      </c>
       <c r="F5" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>1062</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1063</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>34</v>
@@ -4665,25 +4680,25 @@
     </row>
     <row r="6" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
+        <v>977</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>978</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="11" t="s">
         <v>979</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>980</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>981</v>
-      </c>
       <c r="F6" s="11" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>1065</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>1066</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>34</v>
@@ -4691,25 +4706,25 @@
     </row>
     <row r="7" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="11" t="s">
+        <v>981</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>982</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="E7" s="11" t="s">
         <v>983</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>984</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="G7" s="11" t="s">
         <v>985</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>986</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>34</v>
@@ -4717,25 +4732,25 @@
     </row>
     <row r="8" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>986</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>987</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>988</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>989</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="G8" s="11" t="s">
         <v>990</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>991</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>34</v>
@@ -4743,25 +4758,25 @@
     </row>
     <row r="9" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9" s="11" t="s">
+        <v>991</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>992</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="E9" s="11" t="s">
         <v>993</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="F9" s="11" t="s">
         <v>994</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>995</v>
-      </c>
       <c r="G9" s="11" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>34</v>
@@ -4769,25 +4784,25 @@
     </row>
     <row r="10" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>995</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>996</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="11" t="s">
         <v>997</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>998</v>
-      </c>
       <c r="F10" s="11" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>34</v>
@@ -4795,25 +4810,25 @@
     </row>
     <row r="11" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="D11" s="11" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>1071</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="G11" s="11" t="s">
         <v>1072</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>1073</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>1074</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>42</v>
@@ -4821,103 +4836,103 @@
     </row>
     <row r="12" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>1079</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>1080</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>1081</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="G12" s="11" t="s">
         <v>1082</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>1083</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>1084</v>
-      </c>
       <c r="H12" s="11" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>1087</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="F13" s="11" t="s">
         <v>1088</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="G13" s="11" t="s">
         <v>1089</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>1091</v>
-      </c>
       <c r="H13" s="11" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>1093</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="F14" s="11" t="s">
         <v>1094</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="G14" s="11" t="s">
         <v>1095</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>1096</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>1097</v>
-      </c>
       <c r="H14" s="11" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>1098</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="F15" s="11" t="s">
         <v>1099</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="G15" s="11" t="s">
         <v>1100</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>1102</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>34</v>
@@ -4925,25 +4940,25 @@
     </row>
     <row r="16" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>1112</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="F16" s="11" t="s">
         <v>1113</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="G16" s="11" t="s">
         <v>1114</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>1116</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>34</v>
@@ -4951,121 +4966,147 @@
     </row>
     <row r="17" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>1117</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="F17" s="11" t="s">
         <v>1118</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="G17" s="11" t="s">
         <v>1119</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>1120</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>1121</v>
-      </c>
       <c r="H17" s="11" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>1122</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="F18" s="11" t="s">
         <v>1123</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="G18" s="11" t="s">
         <v>1124</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>1125</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>1126</v>
-      </c>
       <c r="H18" s="11" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>1154</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="F19" s="11" t="s">
         <v>1155</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="G19" s="11" t="s">
         <v>1156</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>1157</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>1158</v>
-      </c>
       <c r="H19" s="11" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H21" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H22" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5090,25 +5131,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>577</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>24</v>
@@ -5116,600 +5157,600 @@
     </row>
     <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>583</v>
-      </c>
       <c r="H2" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>588</v>
-      </c>
       <c r="G3" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>589</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>594</v>
-      </c>
       <c r="H4" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>594</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>600</v>
-      </c>
       <c r="H5" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>951</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>603</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>952</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>605</v>
-      </c>
       <c r="H6" s="5" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>611</v>
-      </c>
       <c r="H7" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>617</v>
-      </c>
       <c r="H8" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>619</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="F9" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>622</v>
-      </c>
       <c r="H9" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>625</v>
-      </c>
       <c r="E10" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>954</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>953</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>955</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>956</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>626</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>627</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>628</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>630</v>
-      </c>
       <c r="G11" s="5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>635</v>
-      </c>
       <c r="G12" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>638</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>639</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>640</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>641</v>
-      </c>
       <c r="H13" s="5" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>957</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>959</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B15" t="s">
+        <v>962</v>
+      </c>
+      <c r="C15" t="s">
         <v>963</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>964</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>965</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>966</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>967</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>968</v>
-      </c>
-      <c r="H15" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B16" t="s">
+        <v>998</v>
+      </c>
+      <c r="C16" t="s">
         <v>999</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>1000</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>1001</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>1002</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>1003</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>1004</v>
-      </c>
-      <c r="H16" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B17" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C17" t="s">
         <v>1006</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>1007</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>1008</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>1009</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>1010</v>
       </c>
-      <c r="G17" t="s">
-        <v>1011</v>
-      </c>
       <c r="H17" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B18" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C18" t="s">
         <v>1012</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>1013</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>1014</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>1015</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>1016</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>1017</v>
-      </c>
-      <c r="H18" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C19" t="s">
         <v>1019</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>1020</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>1021</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>1022</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>1023</v>
       </c>
-      <c r="G19" t="s">
-        <v>1024</v>
-      </c>
       <c r="H19" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B20" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C20" t="s">
         <v>1025</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>1026</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>1027</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>1028</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>1029</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>1030</v>
-      </c>
-      <c r="H20" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B21" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C21" t="s">
         <v>1032</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>1033</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>1034</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>1035</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>1036</v>
       </c>
-      <c r="G21" t="s">
-        <v>1037</v>
-      </c>
       <c r="H21" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B22" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C22" t="s">
         <v>1038</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>1039</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>1040</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>1041</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>1042</v>
       </c>
-      <c r="G22" t="s">
-        <v>1043</v>
-      </c>
       <c r="H22" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B23" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C23" t="s">
         <v>1044</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>1045</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>1046</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>1047</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>1048</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>1049</v>
-      </c>
-      <c r="H23" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B24" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C24" t="s">
         <v>1051</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>1052</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>1053</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>1054</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>1055</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>1056</v>
-      </c>
-      <c r="H24" t="s">
-        <v>1057</v>
       </c>
     </row>
   </sheetData>
@@ -5731,19 +5772,19 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>647</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>648</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>3</v>
@@ -5754,278 +5795,278 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>656</v>
-      </c>
       <c r="F3" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>658</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>660</v>
-      </c>
       <c r="F4" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>663</v>
-      </c>
       <c r="F5" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>666</v>
-      </c>
       <c r="F6" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>669</v>
-      </c>
       <c r="F7" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>670</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>671</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>672</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>674</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>675</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>652</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>679</v>
-      </c>
       <c r="F10" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>652</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>682</v>
-      </c>
       <c r="F11" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>652</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>683</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>685</v>
-      </c>
       <c r="F12" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>652</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>688</v>
-      </c>
       <c r="F13" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>652</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>653</v>
       </c>
     </row>
   </sheetData>
@@ -6045,13 +6086,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>690</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>691</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>27</v>
@@ -6059,142 +6100,142 @@
     </row>
     <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>693</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>695</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>697</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>699</v>
-      </c>
       <c r="C5" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>1130</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>701</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>703</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>705</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="144" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>707</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="216" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>709</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>711</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
   </sheetData>
@@ -6214,72 +6255,72 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>714</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>718</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>730</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>731</v>
       </c>
     </row>
   </sheetData>
@@ -6305,304 +6346,304 @@
         <v>18</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>732</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>733</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>734</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>735</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="374.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>736</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>740</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>1069</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>741</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>1067</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>739</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>742</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>1068</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>743</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>744</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>745</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>746</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>747</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>750</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>751</v>
-      </c>
       <c r="F5" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>752</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>753</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>754</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>755</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>756</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>758</v>
-      </c>
       <c r="F7" s="5" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>759</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>760</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>761</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>761</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>762</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>763</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>764</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>765</v>
-      </c>
       <c r="F9" s="5" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>769</v>
-      </c>
       <c r="F10" s="5" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>753</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>754</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>772</v>
-      </c>
       <c r="F11" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>773</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>774</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>776</v>
-      </c>
       <c r="F12" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>777</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>778</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>739</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>779</v>
-      </c>
       <c r="F13" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>780</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>781</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>782</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>783</v>
-      </c>
       <c r="F14" s="5" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>784</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
+        <v>744</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>786</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>787</v>
-      </c>
       <c r="F15" s="5" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
   </sheetData>
@@ -6624,19 +6665,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>790</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>791</v>
       </c>
       <c r="F1" s="6" t="s">
         <v>24</v>
@@ -6644,19 +6685,19 @@
     </row>
     <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>792</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>795</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>796</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>42</v>
@@ -6664,19 +6705,19 @@
     </row>
     <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>797</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>798</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>799</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>800</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>801</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>34</v>
@@ -6684,19 +6725,19 @@
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>802</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>803</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>804</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>34</v>
@@ -6704,19 +6745,19 @@
     </row>
     <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>972</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>973</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>974</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>34</v>
@@ -6724,16 +6765,16 @@
     </row>
     <row r="6" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>805</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>806</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>807</v>
-      </c>
       <c r="C6" s="5" t="s">
+        <v>974</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>975</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>976</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>38</v>
@@ -6744,19 +6785,19 @@
     </row>
     <row r="7" spans="1:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>810</v>
-      </c>
       <c r="D7" s="5" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>34</v>
@@ -6764,19 +6805,19 @@
     </row>
     <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>811</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>812</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>813</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>814</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>815</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>34</v>
@@ -6784,119 +6825,119 @@
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>817</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>818</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>819</v>
-      </c>
       <c r="F9" s="5" t="s">
-        <v>48</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>819</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>820</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>821</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>822</v>
-      </c>
       <c r="E10" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>823</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>824</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>825</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>826</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>827</v>
-      </c>
       <c r="F11" s="5" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>828</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>829</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>830</v>
-      </c>
       <c r="F12" s="5" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>831</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>832</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>833</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>834</v>
-      </c>
       <c r="F13" s="5" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>835</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>836</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>837</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>838</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>34</v>
@@ -6904,19 +6945,19 @@
     </row>
     <row r="15" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>839</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>840</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>841</v>
-      </c>
       <c r="E15" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>34</v>
@@ -6924,67 +6965,67 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>843</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>844</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>845</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>846</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>847</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="5" t="s">
         <v>848</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>849</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>850</v>
-      </c>
       <c r="F18" s="5" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="358.8" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -7006,483 +7047,483 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>852</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>853</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>854</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>856</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>857</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>858</v>
-      </c>
       <c r="E2" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>859</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>860</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>861</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>861</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>862</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>863</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>864</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>865</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>866</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>867</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>868</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>870</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>871</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>872</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>873</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>874</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>875</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>876</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>877</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>878</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>879</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>880</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>881</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>882</v>
-      </c>
       <c r="E10" s="5" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>882</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>883</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>884</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>885</v>
-      </c>
       <c r="E11" s="5" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>886</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>887</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>888</v>
-      </c>
       <c r="E12" s="5" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>889</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>890</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>891</v>
-      </c>
       <c r="E13" s="5" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>892</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>893</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>894</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>895</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>896</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>897</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>898</v>
-      </c>
       <c r="E15" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>899</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>900</v>
-      </c>
       <c r="D16" s="5" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>901</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>902</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>903</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="138" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>908</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>909</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>910</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>912</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>913</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>914</v>
-      </c>
       <c r="E23" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>915</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>916</v>
-      </c>
       <c r="D24" s="4" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>917</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>918</v>
-      </c>
       <c r="D25" s="4" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>919</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>920</v>
-      </c>
       <c r="D26" s="4" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>921</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>922</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>923</v>
-      </c>
       <c r="E27" s="4" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>924</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>925</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>926</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>927</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>928</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>929</v>
-      </c>
       <c r="E29" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>930</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>931</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>932</v>
-      </c>
       <c r="E30" s="4" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>
@@ -7504,75 +7545,75 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>933</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>934</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>935</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>936</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>937</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>938</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="5" t="s">
         <v>939</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>940</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
+        <v>940</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>941</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>942</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>943</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>944</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>945</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>946</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>947</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>948</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
   </sheetData>
@@ -7725,7 +7766,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>51</v>
       </c>
@@ -7745,7 +7786,7 @@
         <v>45</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>35</v>
@@ -7754,12 +7795,12 @@
         <v>54</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>55</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>29</v>
@@ -7768,10 +7809,10 @@
         <v>39</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>28</v>
@@ -7783,27 +7824,27 @@
         <v>35</v>
       </c>
       <c r="I6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>28</v>
@@ -7812,30 +7853,30 @@
         <v>34</v>
       </c>
       <c r="H7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>28</v>
@@ -7847,27 +7888,27 @@
         <v>35</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>28</v>
@@ -7879,30 +7920,30 @@
         <v>35</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -7911,62 +7952,62 @@
         <v>35</v>
       </c>
       <c r="I10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>34</v>
@@ -7975,30 +8016,30 @@
         <v>35</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -8007,28 +8048,28 @@
         <v>35</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J13" s="2"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>48</v>
@@ -8037,28 +8078,28 @@
         <v>35</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J14" s="2"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>34</v>
@@ -8067,28 +8108,28 @@
         <v>35</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -8097,180 +8138,180 @@
         <v>35</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>48</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J17" s="2"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>48</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J18" s="2"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>48</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="J19" s="2"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>48</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J20" s="2"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>48</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J21" s="2"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -8279,28 +8320,28 @@
         <v>35</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J22" s="2"/>
     </row>
     <row r="23" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -8309,28 +8350,28 @@
         <v>35</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>48</v>
@@ -8339,58 +8380,58 @@
         <v>35</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J24" s="2"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>48</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J25" s="2"/>
     </row>
     <row r="26" spans="1:10" ht="216" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>42</v>
@@ -8399,30 +8440,30 @@
         <v>35</v>
       </c>
       <c r="I26" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J26" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>48</v>
@@ -8431,58 +8472,58 @@
         <v>35</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>48</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J28" s="2"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>48</v>
@@ -8491,7 +8532,7 @@
         <v>35</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J29" s="2"/>
     </row>
@@ -8520,13 +8561,13 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>25</v>
@@ -8540,19 +8581,19 @@
     </row>
     <row r="2" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>48</v>
@@ -8560,19 +8601,19 @@
     </row>
     <row r="3" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>48</v>
@@ -8580,19 +8621,19 @@
     </row>
     <row r="4" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>48</v>
@@ -8600,19 +8641,19 @@
     </row>
     <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>48</v>
@@ -8620,19 +8661,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>48</v>
@@ -8640,19 +8681,19 @@
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>48</v>
@@ -8660,19 +8701,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>48</v>
@@ -8680,19 +8721,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>48</v>
@@ -8700,19 +8741,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>48</v>
@@ -8720,19 +8761,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>48</v>
@@ -8740,19 +8781,19 @@
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>48</v>
@@ -8760,19 +8801,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>48</v>
@@ -8799,142 +8840,142 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -8955,206 +8996,206 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -9177,16 +9218,16 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>329</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>330</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>24</v>
@@ -9197,240 +9238,240 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>962</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>345</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>349</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>358</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>362</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>379</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -9456,13 +9497,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>383</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>24</v>
@@ -9470,13 +9511,13 @@
     </row>
     <row r="2" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>386</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>48</v>
@@ -9484,13 +9525,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>48</v>
@@ -9498,13 +9539,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>48</v>
@@ -9512,13 +9553,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>48</v>
@@ -9526,13 +9567,13 @@
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>48</v>
@@ -9540,13 +9581,13 @@
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>401</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>48</v>
@@ -9554,13 +9595,13 @@
     </row>
     <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>404</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>48</v>
@@ -9568,13 +9609,13 @@
     </row>
     <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>48</v>
@@ -9582,13 +9623,13 @@
     </row>
     <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>48</v>
@@ -9596,13 +9637,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>48</v>
@@ -9626,16 +9667,16 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>415</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>416</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>24</v>
@@ -9643,36 +9684,36 @@
     </row>
     <row r="2" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
@@ -9680,169 +9721,169 @@
         <v>39</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>433</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>442</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>446</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>450</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>453</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>457</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>462</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>466</v>
-      </c>
       <c r="E13" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -9863,13 +9904,13 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>468</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>469</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>25</v>
@@ -9880,13 +9921,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>35</v>
@@ -9897,13 +9938,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>474</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>35</v>
@@ -9914,13 +9955,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>35</v>
@@ -9931,16 +9972,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>48</v>
@@ -9948,13 +9989,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>35</v>
@@ -9965,16 +10006,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>481</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>48</v>
@@ -9982,13 +10023,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>483</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>35</v>
@@ -9999,16 +10040,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>485</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>48</v>
@@ -10016,16 +10057,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>487</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>48</v>
@@ -10033,16 +10074,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>489</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>48</v>
@@ -10050,16 +10091,16 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>491</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>48</v>
@@ -10067,16 +10108,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>493</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>48</v>

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="364" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C3A77CB-A1A1-4F21-BC48-C14D0F17A542}"/>
+  <xr:revisionPtr revIDLastSave="444" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5609FDCD-889A-4FCF-B514-CAECBA49139A}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="1164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="1224">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3217,9 +3217,6 @@
     <t>CLOSED 2026-09-23 - Cavite, Philippines; open to relocation to Europe/UK/US with visa sponsorship</t>
   </si>
   <si>
-    <t>Open - and now HARDER: all three drafted options lead with Android and are stale after D15. Fresh drafts needed.</t>
-  </si>
-  <si>
     <t>CHUNK 00 - case study 1 draft skeleton</t>
   </si>
   <si>
@@ -3244,9 +3241,6 @@
     <t>Open - BLOCKING. Engagement chosen (CASECenter). Skeleton drafted in notes/case-study-2-DRAFT.md; all ten sections still need Raymund's account.</t>
   </si>
   <si>
-    <t>Open - CANDIDATE IDENTIFIED 2026-09-23. SBC is the natural third, shorter entry: a second maintained mobile application, built in Java rather than Kotlin, for a different client. Adds breadth without needing a full case study.</t>
-  </si>
-  <si>
     <t>Drafted case study skeletons for BOTH case studies into notes/, against the ten Sheet 06 sections. Every drafted line traces to a quoted statement; everything else marked [CONTENT REQUIRED]. Method: draft-and-correct rather than open questioning. Case study 1 (VAPT, abstracted tier): decisions 1 and 2 answered - the remediation was TRIAGE, not a blanket no-upgrade constraint. Raymund upgraded the libraries that could move without breaking the base code and closed the rest in the application's own code. That is a judgement story rather than a constraint story, and materially stronger. His earlier "cannot update any library" was shorthand, not a contradiction; the case study must use the accurate version. Case study 2 (CASECenter, sectoral tier): engagement chosen; closes the gap between the new positioning (D15, Enterprise Systems Developer) and the evidence, which was otherwise all Android.</t>
   </si>
   <si>
@@ -3292,9 +3286,6 @@
     <t>CLOSED 2026-09-24 - transcribed into src/data/experience.ts exactly as the CV states, and LIVE on /about. Where the CV gives years only (MCS Ventures, Pipol) the year is published as a year, not guessed into a month.</t>
   </si>
   <si>
-    <t>Partially closed 2026-09-24 - src/data/skills.ts populated from the CV and LIVE on /about, 24 skills in 6 categories, no proficiency ratings. STILL PENDING Raymund's filter (question B3): a CV keyword list and a defensible skills list are not the same thing. /about renders a visible [VERIFY INFORMATION] note until SKILLS_CONFIRMED is set true. n8n, Claude Code and Codex deliberately excluded - learning, not delivery.</t>
-  </si>
-  <si>
     <t>CHUNK 10 - About: timeline, education, skills</t>
   </si>
   <si>
@@ -3310,9 +3301,6 @@
     <t>CHUNK 11 contact and resume.</t>
   </si>
   <si>
-    <t>Partially closed 2026-09-24 - LinkedIn is LIVE on /contact, sourced from the CV where it is already public. Email deliberately NOT published pending question B5: publishing an address is irreversible and it will be harvested, so nothing goes out until Raymund says whether to use the CV address or a new one. GitHub still open (B6).</t>
-  </si>
-  <si>
     <t>CHUNK 11 - Contact</t>
   </si>
   <si>
@@ -3530,6 +3518,198 @@
   </si>
   <si>
     <t>Case study 2 (CASECenter delivery) - CG-02. Then the positioning line unblocks the home page.</t>
+  </si>
+  <si>
+    <t>D24</t>
+  </si>
+  <si>
+    <t>Delivery Thread is SEVEN stages. "Design" is not one of them.</t>
+  </si>
+  <si>
+    <t>(a) Keep 8 stages; (b) filter design out of the home strip only; (c) remove design from DELIVERY_STAGES entirely</t>
+  </si>
+  <si>
+    <t>(c) Remove entirely</t>
+  </si>
+  <si>
+    <t>Owner confirmed he does not own design work; his CV has him collaborating WITH UI/UX and resolving UI inconsistencies through engineering review. Option (b) would have left a stage no project could honestly claim but every project could still select - a trap for a future edit. Removal makes the false claim unrepresentable: the type system now rejects stages:[design].</t>
+  </si>
+  <si>
+    <t>Medium. DELIVERY_STAGES and STAGE_LABEL lose an entry; "Technical Challenge" remaps from design to analysis; home strip renders 7. Closes the standing [VERIFY INFORMATION] in CLAUDE.md.</t>
+  </si>
+  <si>
+    <t>CONFIRMED by owner 2026-09-24</t>
+  </si>
+  <si>
+    <t>D25</t>
+  </si>
+  <si>
+    <t>Positioning line chosen (CG-09)</t>
+  </si>
+  <si>
+    <t>3 drafts: (1) requirements-to-support span; (2) role label plus domains; (3) "Requirements to release, and everything after."</t>
+  </si>
+  <si>
+    <t>(1) "I turn business requirements into enterprise systems - and stay with them through testing, UAT, release and production support."</t>
+  </si>
+  <si>
+    <t>Claims the span, which is the one thing distinguishing him from a developer who only writes code, and claims nothing the D16 experience list does not support. Deliberately carries no seniority label, no years, no metric and no technology - each of those dates, and each would need separate sourcing.</t>
+  </si>
+  <si>
+    <t>HIGH. Closes CG-09 and LIFTS THE HOME PAGE noindex - / is indexable for the first time. Feeds the meta description and OG description.</t>
+  </si>
+  <si>
+    <t>CHOSEN by owner 2026-09-24</t>
+  </si>
+  <si>
+    <t>D26</t>
+  </si>
+  <si>
+    <t>Publish raymund.bermudes21@gmail.com as the contact address</t>
+  </si>
+  <si>
+    <t>(a) Create a new dedicated address per D7; (b) publish the address already on his CV</t>
+  </si>
+  <si>
+    <t>(b) The CV address - REVERSES D7</t>
+  </si>
+  <si>
+    <t>It is already on the CV he circulates, so it is already public and already the address recruiters will use. Creating a new one purely to avoid reusing a public address would have protected nothing.</t>
+  </si>
+  <si>
+    <t>Low, but IRREVERSIBLE - a published address will be harvested. Closes the email half of CG-07; /contact now renders a live mailto.</t>
+  </si>
+  <si>
+    <t>CONFIRMED by owner 2026-09-24. Supersedes D7.</t>
+  </si>
+  <si>
+    <t>D27</t>
+  </si>
+  <si>
+    <t>No GitHub link on the site</t>
+  </si>
+  <si>
+    <t>(a) Link a profile; (b) omit deliberately</t>
+  </si>
+  <si>
+    <t>(b) Omit. site.contact.github stays null BY DECISION, not by omission</t>
+  </si>
+  <si>
+    <t>His CV lists none and this portfolio repo is private (D14), so a link would send a recruiter somewhere showing less than the page they are already on.</t>
+  </si>
+  <si>
+    <t>Low. The [VERIFY INFORMATION] note on /contact is removed - the null is now a decision, not a pending question.</t>
+  </si>
+  <si>
+    <t>D28</t>
+  </si>
+  <si>
+    <t>All 24 skills confirmed; SKILLS_CONFIRMED = true</t>
+  </si>
+  <si>
+    <t>(a) Strike entries he would not defend; (b) keep all</t>
+  </si>
+  <si>
+    <t>(b) Keep all 24 - he reviewed and struck nothing</t>
+  </si>
+  <si>
+    <t>A CV keyword list and a defensible skills list are not the same thing. He reviewed the list against the standard "only what you would defend in an interview" and removed nothing.</t>
+  </si>
+  <si>
+    <t>Medium. Closes CG-06 and removes the visible [VERIFY INFORMATION] from /about. WARNING: the confirmation covers only the entries present on 2026-09-24. Adding a skill later is a NEW claim and needs his word again.</t>
+  </si>
+  <si>
+    <t>D29</t>
+  </si>
+  <si>
+    <t>CV PDF is approved for publication</t>
+  </si>
+  <si>
+    <t>(a) Publish; (b) withhold</t>
+  </si>
+  <si>
+    <t>(a) Publish</t>
+  </si>
+  <si>
+    <t>A recruiter expects a resume; withholding one fails the recruiter test at the last step.</t>
+  </si>
+  <si>
+    <t>Medium and PARTIAL - the decision is made but THE FILE HAS NOT BEEN SUPPLIED. The Resume button still correctly does not render in the header or on /contact. Drop the file at public/raymund-bermudes-cv.pdf and both appear on the next build, with no code change.</t>
+  </si>
+  <si>
+    <t>APPROVED by owner 2026-09-24. CG-04 remains open on the FILE.</t>
+  </si>
+  <si>
+    <t>D30</t>
+  </si>
+  <si>
+    <t>No headshot</t>
+  </si>
+  <si>
+    <t>(a) Include a headshot; (b) omit</t>
+  </si>
+  <si>
+    <t>(b) Omit</t>
+  </si>
+  <si>
+    <t>Owner preference. A portfolio without a headshot is entirely normal and nothing in the design depends on one.</t>
+  </si>
+  <si>
+    <t>None. No code referenced a headshot, so no change was required. Closes CG-10.</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-24 - owner confirmed SBC was maintenance work, not separate security work, and does NOT become a third case study. The site ships two: the VAPT remediation (published) and the CASECenter delivery (CG-02).</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-24 - NO screenshots are cleared and NONE are used anywhere on the site. The default assumption (none) stands as the permanent answer.</t>
+  </si>
+  <si>
+    <t>Partially closed 2026-09-24 - case study 1 needed NO architecture figure: its story is dependency judgement, not topology, and a diagram would have added identifying detail for no benefit. Re-open for case study 2 if the policy system needs one.</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-22 (D9) - the site stays on *.vercel.app permanently. No custom domain. This row was stale.</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-24 (D30) - no headshot. Nothing in the codebase referenced one, so no change was required.</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-24 (D25) - owner chose option 1: "I turn business requirements into enterprise systems - and stay with them through testing, UAT, release and production support." LIFTS THE HOME PAGE noindex.</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-24 - email published (D26, the CV address, superseding D7); LinkedIn live from the CV; GitHub omitted BY DECISION (D27), not pending. All three pending notes removed from /contact.</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-24 (D28) - owner reviewed all 24 entries against "only what you would defend in an interview" and struck nothing. SKILLS_CONFIRMED = true; the [VERIFY INFORMATION] note is removed from /about. WARNING: this covers only the entries present at that date. Adding a skill later is a NEW claim.</t>
+  </si>
+  <si>
+    <t>APPROVED 2026-09-24 (D29) - publication cleared by owner. FILE NOT SUPPLIED, so the gap stays OPEN. Drop it at public/raymund-bermudes-cv.pdf and the Resume button appears in the header and on /contact on the next build - no code change needed.</t>
+  </si>
+  <si>
+    <t>Answer sheet cleared - D24 to D30</t>
+  </si>
+  <si>
+    <t>Owner answered notes/ANSWER-SHEET.md in one reply, producing 7 decisions. Delivery Thread dropped to SEVEN stages, with design removed from DELIVERY_STAGES entirely rather than filtered from the home strip, so the type system now rejects it (D24). Positioning line chosen and live (D25). Email published from the CV, superseding D7 (D26). GitHub omitted by decision (D27). All 24 skills confirmed (D28). CV PDF approved but not supplied (D29). No headshot (D30). Case study 1 provenance closed: the one Claude-authored sentence was restated by the owner in his own words.</t>
+  </si>
+  <si>
+    <t>npm run verify exit 0. Verified in built HTML: home has ZERO [CONTENT REQUIRED] markers and no noindex; 7 stages render on the strip; Technical Challenge maps to Analysis; mailto live on /contact; no "&gt;Design&lt;" anywhere in dist.</t>
+  </si>
+  <si>
+    <t>PROVENANCE: the owner's own words for the storage finding contain the business function ("appraisal") and the sync target ("CASECenter"), NEITHER of which may be published at abstracted tier. The live sentence was therefore deliberately NOT changed. Recorded privately in notes/case-study-1-PROVENANCE.md. Do not "improve" that sentence by adding the detail back in.</t>
+  </si>
+  <si>
+    <t>Case study 2 (CG-02) and the About story are now the ONLY content blockers. Then: push 22 commits, verify CHUNKS 14-16 against production, delete /styleguide, re-run Sheet 13.</t>
+  </si>
+  <si>
+    <t>CG-15</t>
+  </si>
+  <si>
+    <t>About page: the professional story and the "how I work" section</t>
+  </si>
+  <si>
+    <t>His own account, in his own voice. Prompts offered: how he got from Junior Android Developer to Solutions Analyst; what kind of problem he enjoys most; what he does differently from someone who only writes code. Rough notes are enough - Claude writes the prose from them.</t>
+  </si>
+  <si>
+    <t>Open - ADDED 2026-09-24. This gap was being rendered on /about as a visible [CONTENT REQUIRED] but was never tracked on this sheet. Nobody but the owner can write it; a generated version reads exactly like one.</t>
   </si>
 </sst>
 </file>
@@ -3648,7 +3828,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3681,6 +3861,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3995,13 +4176,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4149,10 +4330,10 @@
         <v>497</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -4166,10 +4347,10 @@
         <v>500</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -4183,10 +4364,10 @@
         <v>503</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -4200,10 +4381,10 @@
         <v>505</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>1101</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -4217,10 +4398,10 @@
         <v>507</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -4234,10 +4415,10 @@
         <v>509</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
@@ -4251,10 +4432,10 @@
         <v>512</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
@@ -4268,10 +4449,10 @@
         <v>514</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="216" x14ac:dyDescent="0.3">
@@ -4285,10 +4466,10 @@
         <v>516</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
@@ -4302,10 +4483,10 @@
         <v>518</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
@@ -4319,10 +4500,10 @@
         <v>520</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
@@ -4336,10 +4517,10 @@
         <v>522</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="360" x14ac:dyDescent="0.3">
@@ -4353,10 +4534,10 @@
         <v>524</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -4370,10 +4551,10 @@
         <v>526</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
@@ -4387,10 +4568,10 @@
         <v>528</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
@@ -4404,10 +4585,10 @@
         <v>530</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="216" x14ac:dyDescent="0.3">
@@ -4421,10 +4602,10 @@
         <v>532</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -4438,10 +4619,10 @@
         <v>535</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
@@ -4455,10 +4636,10 @@
         <v>537</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -4472,10 +4653,10 @@
         <v>540</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
@@ -4489,10 +4670,10 @@
         <v>542</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -4506,10 +4687,10 @@
         <v>544</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
@@ -4523,10 +4704,10 @@
         <v>546</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
     </row>
   </sheetData>
@@ -4536,7 +4717,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4669,10 +4850,10 @@
         <v>971</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>1061</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1062</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>34</v>
@@ -4695,10 +4876,10 @@
         <v>980</v>
       </c>
       <c r="F6" s="11" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>1064</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>1065</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>34</v>
@@ -4799,10 +4980,10 @@
         <v>997</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>34</v>
@@ -4816,19 +4997,19 @@
         <v>39</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D11" s="11" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>1069</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="G11" s="11" t="s">
         <v>1070</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>1071</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>1072</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>42</v>
@@ -4836,103 +5017,103 @@
     </row>
     <row r="12" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="11" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>1078</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>1079</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="G12" s="11" t="s">
         <v>1080</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>1081</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>1082</v>
-      </c>
       <c r="H12" s="11" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>94</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>1085</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="G13" s="11" t="s">
         <v>1086</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>1087</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>1088</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>1089</v>
-      </c>
       <c r="H13" s="11" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>94</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>1091</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>1092</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>1093</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>1094</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>1095</v>
-      </c>
       <c r="H14" s="11" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>141</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G15" s="11" t="s">
         <v>1096</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>1100</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>34</v>
@@ -4940,25 +5121,25 @@
     </row>
     <row r="16" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>141</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G16" s="11" t="s">
         <v>1110</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>1111</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>1113</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>1114</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>34</v>
@@ -4966,147 +5147,173 @@
     </row>
     <row r="17" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>141</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G17" s="11" t="s">
         <v>1115</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>1116</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>1117</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>1118</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>1119</v>
-      </c>
       <c r="H17" s="11" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>141</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G18" s="11" t="s">
         <v>1120</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>1121</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>1124</v>
-      </c>
       <c r="H18" s="11" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>170</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G19" s="11" t="s">
         <v>1152</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>1153</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>1154</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>1156</v>
-      </c>
       <c r="H19" s="11" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G20" s="11" t="s">
         <v>1159</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>1160</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>1161</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>1162</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>1163</v>
-      </c>
       <c r="H20" s="11" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>1215</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>1217</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>1219</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H22" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H23" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5116,7 +5323,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5751,6 +5958,188 @@
       </c>
       <c r="H24" t="s">
         <v>1056</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G27" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1186</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1166</v>
       </c>
     </row>
   </sheetData>
@@ -6106,10 +6495,10 @@
         <v>692</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
@@ -6120,10 +6509,10 @@
         <v>694</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
@@ -6134,10 +6523,10 @@
         <v>696</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
@@ -6148,10 +6537,10 @@
         <v>698</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
@@ -6162,10 +6551,10 @@
         <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
@@ -6176,10 +6565,10 @@
         <v>702</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>1128</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="302.39999999999998" x14ac:dyDescent="0.3">
@@ -6190,10 +6579,10 @@
         <v>704</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="144" x14ac:dyDescent="0.3">
@@ -6204,10 +6593,10 @@
         <v>706</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="216" x14ac:dyDescent="0.3">
@@ -6218,10 +6607,10 @@
         <v>708</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
@@ -6232,10 +6621,10 @@
         <v>710</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
     </row>
   </sheetData>
@@ -6378,7 +6767,7 @@
         <v>739</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
@@ -6386,7 +6775,7 @@
         <v>740</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>737</v>
@@ -6398,7 +6787,7 @@
         <v>741</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -6421,7 +6810,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>747</v>
       </c>
@@ -6438,7 +6827,7 @@
         <v>750</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>652</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
@@ -6458,10 +6847,10 @@
         <v>754</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="288" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>755</v>
       </c>
@@ -6478,10 +6867,10 @@
         <v>757</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="302.39999999999998" x14ac:dyDescent="0.3">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>758</v>
       </c>
@@ -6498,7 +6887,7 @@
         <v>760</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>1090</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -6521,7 +6910,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>765</v>
       </c>
@@ -6538,10 +6927,10 @@
         <v>768</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>769</v>
       </c>
@@ -6558,10 +6947,10 @@
         <v>771</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>772</v>
       </c>
@@ -6578,10 +6967,10 @@
         <v>775</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>776</v>
       </c>
@@ -6598,10 +6987,10 @@
         <v>778</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>779</v>
       </c>
@@ -6618,10 +7007,10 @@
         <v>782</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="230.4" x14ac:dyDescent="0.3">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="216" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>783</v>
       </c>
@@ -6638,7 +7027,27 @@
         <v>786</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1068</v>
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C16" t="s">
+        <v>737</v>
+      </c>
+      <c r="D16" t="s">
+        <v>753</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1223</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
@@ -6840,7 +7249,7 @@
         <v>818</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6860,7 +7269,7 @@
         <v>103</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6880,7 +7289,7 @@
         <v>826</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6900,7 +7309,7 @@
         <v>829</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6920,7 +7329,7 @@
         <v>833</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -6980,7 +7389,7 @@
         <v>152</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -7000,7 +7409,7 @@
         <v>157</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -7020,7 +7429,7 @@
         <v>849</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="358.8" x14ac:dyDescent="0.3">
@@ -7795,7 +8204,7 @@
         <v>54</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -8019,7 +8428,7 @@
         <v>98</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -8141,7 +8550,7 @@
         <v>117</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="444" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5609FDCD-889A-4FCF-B514-CAECBA49139A}"/>
+  <xr:revisionPtr revIDLastSave="479" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC2CE1DC-2AE1-4B04-8F07-DFB7DE1AF9E2}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="1224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="1249">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3238,9 +3238,6 @@
     <t>Case study 2 - CASECenter policy system delivery (current Solutions Analyst role). DECIDED 2026-09-23. NOTE: this row previously read "SBC security work", which was mis-scoped - SBC is a third mobile maintenance engagement (older app, Java), not separate security work.</t>
   </si>
   <si>
-    <t>Open - BLOCKING. Engagement chosen (CASECenter). Skeleton drafted in notes/case-study-2-DRAFT.md; all ten sections still need Raymund's account.</t>
-  </si>
-  <si>
     <t>Drafted case study skeletons for BOTH case studies into notes/, against the ten Sheet 06 sections. Every drafted line traces to a quoted statement; everything else marked [CONTENT REQUIRED]. Method: draft-and-correct rather than open questioning. Case study 1 (VAPT, abstracted tier): decisions 1 and 2 answered - the remediation was TRIAGE, not a blanket no-upgrade constraint. Raymund upgraded the libraries that could move without breaking the base code and closed the rest in the application's own code. That is a judgement story rather than a constraint story, and materially stronger. His earlier "cannot update any library" was shorthand, not a contradiction; the case study must use the accurate version. Case study 2 (CASECenter, sectoral tier): engagement chosen; closes the gap between the new positioning (D15, Enterprise Systems Developer) and the evidence, which was otherwise all Android.</t>
   </si>
   <si>
@@ -3664,9 +3661,6 @@
     <t>CLOSED 2026-09-24 - NO screenshots are cleared and NONE are used anywhere on the site. The default assumption (none) stands as the permanent answer.</t>
   </si>
   <si>
-    <t>Partially closed 2026-09-24 - case study 1 needed NO architecture figure: its story is dependency judgement, not topology, and a diagram would have added identifying detail for no benefit. Re-open for case study 2 if the policy system needs one.</t>
-  </si>
-  <si>
     <t>CLOSED 2026-09-22 (D9) - the site stays on *.vercel.app permanently. No custom domain. This row was stale.</t>
   </si>
   <si>
@@ -3710,6 +3704,87 @@
   </si>
   <si>
     <t>Open - ADDED 2026-09-24. This gap was being rendered on /about as a visible [CONTENT REQUIRED] but was never tracked on this sheet. Nobody but the owner can write it; a generated version reads exactly like one.</t>
+  </si>
+  <si>
+    <t>D31</t>
+  </si>
+  <si>
+    <t>Case study 2 publishes at abstracted, NOT the sectoral the skeleton proposed</t>
+  </si>
+  <si>
+    <t>(a) sectoral - sector, scale and geography, no name; (b) abstracted - class of problem only</t>
+  </si>
+  <si>
+    <t>(b) abstracted</t>
+  </si>
+  <si>
+    <t>GDS Link Asia serves a small, named set of credit-decisioning clients. At sectoral, "a Taiwanese bank" or "a Philippine commercial bank" is shortlistable in one guess - and a tier that only FEELS protective is worse than one that is, because it licenses more detail on a false assumption. abstracted costs nothing here: the story is requirements, policy logic, UAT and sign-off, none of which need the client identity. CASECenter and GDS Link Asia stay nameable per D18 - the tier governs the CLIENT, not the tool.</t>
+  </si>
+  <si>
+    <t>Medium. Overrides the skeleton default in notes/case-study-2-DRAFT.md.</t>
+  </si>
+  <si>
+    <t>DECIDED by owner 2026-09-24</t>
+  </si>
+  <si>
+    <t>D32</t>
+  </si>
+  <si>
+    <t>Case study 2 ships as a SHORT ENTRY, not a full ten-section case study</t>
+  </si>
+  <si>
+    <t>(a) Full nine-question interview; (b) short entry, five questions; (c) ship with one case study only</t>
+  </si>
+  <si>
+    <t>(b) Short entry</t>
+  </si>
+  <si>
+    <t>Owner pushed back on depth: "WHY DO WE GO DEEP ON MY THINGS I DID IN MY WORK? I JUST NEED A SHOWCASE OF MY CV". The trade-off was stated once and accepted: the CV-showcase job is ALREADY done by /about, the home page and the PDF, so the Work section is the only part not already in the CV - which is why depth lives there. A short entry closes the Android-only evidence gap at a fraction of the effort.</t>
+  </si>
+  <si>
+    <t>Medium. Schema forcing functions still apply and were NOT skipped - clientDescriptor, problem, myRole and outcome are all .min(1). What was dropped is the ten-section Sheet 06 body: four short sections instead of ten. Cost: no Lessons section, because that question was not asked in the short scope and nothing was available to source it from.</t>
+  </si>
+  <si>
+    <t>D33</t>
+  </si>
+  <si>
+    <t>The stages field is rendered, via a new StageCoverage component</t>
+  </si>
+  <si>
+    <t>(a) Leave stages unrendered; (b) render it; (c) delete it from the schema</t>
+  </si>
+  <si>
+    <t>(b) Render it</t>
+  </si>
+  <si>
+    <t>stages had been in the schema since CHUNK 04 and rendered NOWHERE, and the schema comment wrongly claimed it "drives the Delivery Thread rail" - the rail is built from rendered headings. So "covered seven of seven stages" was a claim stored in a file nobody reads, and the central argument for having a Delivery Thread at all was invisible to a recruiter. UNCOVERED stages stay visible deliberately: case study 1 renders 4 of 7 with three hollow rings, and that honesty is what makes the 7 of 7 beside it worth believing.</t>
+  </si>
+  <si>
+    <t>Medium. New no-JS component in the case study header. Coverage conveyed THREE ways - marker shape, token colour, and visually-hidden covered/not-covered text - never by colour alone. No opacity is used to dim: opacity has broken AAA twice on this site and axe cannot detect it. Measured: light 7.77/18.47/8.13, dark 8.07/17.51, all AAA; no overflow at 320px.</t>
+  </si>
+  <si>
+    <t>DECIDED by Claude 2026-09-24, reported to owner and approved</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-24 - published as src/content/work/delivering-from-an-unfinished-requirements-document.mdx at abstracted tier (D31), short-entry scope (D32). Sourced entirely from five owner answers plus one follow-up. CONFIDENTIALITY: his first answer named the business function, which is the SAME one deliberately removed from case study 1 - the two are two halves of one system (Android field capture syncing to the CASECenter side). Publishing it here would have handed back what case study 1 withheld: neither page leaks alone, both leak together. He chose generic. Audited on built HTML - zero occurrences.</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-24 - NEITHER case study needed an architecture figure. Case study 1 is dependency judgement, not topology; case study 2 is delivery process. In both, a diagram would have added identifying detail for no engineering benefit. ArchitectureFigure remains available if a future entry needs one.</t>
+  </si>
+  <si>
+    <t>CHUNK 07 - case study 2 published, and stages made visible</t>
+  </si>
+  <si>
+    <t>Second Work entry live: "Push back before you build: delivering from an unfinished requirements document", 2024-2025, abstracted tier, SEVEN of seven delivery stages. It is the current role and it covers requirements and UAT, neither of which case study 1 touches - closing the gap where the positioning claimed enterprise systems delivery while every published piece of evidence was Android from the PREVIOUS role. Separately, the stages field was found to render nowhere despite being in the schema since CHUNK 04; new StageCoverage component now renders it (D33).</t>
+  </si>
+  <si>
+    <t>npm run verify exit 0, 22/22 guards, astro check 0/0/1, 8 pages. /work lists both entries. Case study pages render "4 of 7" and "7 of 7". Contrast measured in-browser: light 7.77/18.47/8.13, dark 8.07/17.51 - all AAA, computed opacity 1 throughout. No horizontal overflow at 320px.</t>
+  </si>
+  <si>
+    <t>CONFIDENTIALITY CATCH: the owner's first answer named the business function, the same one deliberately stripped from case study 1 on his own instruction. The two entries are two halves of one system, so publishing it would have re-identified what case study 1 withheld - a mosaic disclosure that neither page commits alone. Flagged, he chose generic, audited clean on built HTML. SOURCING: UAT and client sign-off were withheld from the first draft because he had said only "testing" and "went live"; he then confirmed DEV -&gt; UAT -&gt; Prod with sign-off, so both are now claimed. No Lessons section - not asked in the short scope, so nothing to source it from. No number anywhere.</t>
+  </si>
+  <si>
+    <t>Only TWO content items remain: the About story (CG-15) and the CV PDF file (CG-04). Then push, verify CHUNKS 14-16 against production, delete /styleguide, re-run Sheet 13 recruiter test.</t>
   </si>
 </sst>
 </file>
@@ -4330,10 +4405,10 @@
         <v>497</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>1097</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -4347,10 +4422,10 @@
         <v>500</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -4364,10 +4439,10 @@
         <v>503</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -4381,10 +4456,10 @@
         <v>505</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -4398,10 +4473,10 @@
         <v>507</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -4415,10 +4490,10 @@
         <v>509</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="273.60000000000002" x14ac:dyDescent="0.3">
@@ -4432,10 +4507,10 @@
         <v>512</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
@@ -4449,10 +4524,10 @@
         <v>514</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="216" x14ac:dyDescent="0.3">
@@ -4466,10 +4541,10 @@
         <v>516</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
@@ -4483,10 +4558,10 @@
         <v>518</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
@@ -4500,10 +4575,10 @@
         <v>520</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
@@ -4517,10 +4592,10 @@
         <v>522</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="360" x14ac:dyDescent="0.3">
@@ -4534,10 +4609,10 @@
         <v>524</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -4551,10 +4626,10 @@
         <v>526</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
@@ -4568,10 +4643,10 @@
         <v>528</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
@@ -4585,10 +4660,10 @@
         <v>530</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="216" x14ac:dyDescent="0.3">
@@ -4602,10 +4677,10 @@
         <v>532</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -4619,10 +4694,10 @@
         <v>535</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
@@ -4636,10 +4711,10 @@
         <v>537</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -4653,10 +4728,10 @@
         <v>540</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
@@ -4670,10 +4745,10 @@
         <v>542</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -4687,10 +4762,10 @@
         <v>544</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
@@ -4704,10 +4779,10 @@
         <v>546</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
   </sheetData>
@@ -4717,7 +4792,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4980,10 +5055,10 @@
         <v>997</v>
       </c>
       <c r="F10" s="11" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>1071</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>1072</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>34</v>
@@ -5000,16 +5075,16 @@
         <v>1059</v>
       </c>
       <c r="D11" s="11" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>1067</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="F11" s="11" t="s">
         <v>1068</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="G11" s="11" t="s">
         <v>1069</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>1070</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>42</v>
@@ -5017,103 +5092,103 @@
     </row>
     <row r="12" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="11" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>1076</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>1077</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="F12" s="11" t="s">
         <v>1078</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="G12" s="11" t="s">
         <v>1079</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>1080</v>
-      </c>
       <c r="H12" s="11" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>94</v>
       </c>
       <c r="C13" s="11" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>1082</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>1083</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="F13" s="11" t="s">
         <v>1084</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="G13" s="11" t="s">
         <v>1085</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>1086</v>
-      </c>
       <c r="H13" s="11" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>94</v>
       </c>
       <c r="C14" s="11" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>1087</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="E14" s="11" t="s">
         <v>1088</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="F14" s="11" t="s">
         <v>1089</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="G14" s="11" t="s">
         <v>1090</v>
       </c>
-      <c r="G14" s="11" t="s">
-        <v>1091</v>
-      </c>
       <c r="H14" s="11" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>141</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>1092</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="E15" s="11" t="s">
         <v>1093</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="F15" s="11" t="s">
         <v>1094</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="G15" s="11" t="s">
         <v>1095</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>1096</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>34</v>
@@ -5121,25 +5196,25 @@
     </row>
     <row r="16" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>141</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>1106</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>1107</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="F16" s="11" t="s">
         <v>1108</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="G16" s="11" t="s">
         <v>1109</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>1110</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>34</v>
@@ -5147,173 +5222,199 @@
     </row>
     <row r="17" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>141</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>1111</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>1112</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="F17" s="11" t="s">
         <v>1113</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="G17" s="11" t="s">
         <v>1114</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>1115</v>
-      </c>
       <c r="H17" s="11" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>141</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>1116</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="E18" s="11" t="s">
         <v>1117</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="F18" s="11" t="s">
         <v>1118</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="G18" s="11" t="s">
         <v>1119</v>
       </c>
-      <c r="G18" s="11" t="s">
-        <v>1120</v>
-      </c>
       <c r="H18" s="11" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>170</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>1148</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="E19" s="11" t="s">
         <v>1149</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="F19" s="11" t="s">
         <v>1150</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="G19" s="11" t="s">
         <v>1151</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>1152</v>
-      </c>
       <c r="H19" s="11" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>1155</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="E20" s="11" t="s">
         <v>1156</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="F20" s="11" t="s">
         <v>1157</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="G20" s="11" t="s">
         <v>1158</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>1159</v>
-      </c>
       <c r="H20" s="11" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>1215</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="F21" s="11" t="s">
         <v>1216</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="G21" s="11" t="s">
         <v>1217</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>1219</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>1248</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H23" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H24" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5323,7 +5424,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5965,25 +6066,25 @@
         <v>46289</v>
       </c>
       <c r="B25" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C25" t="s">
         <v>1160</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>1161</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>1162</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>1163</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>1164</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>1165</v>
-      </c>
-      <c r="H25" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -5991,25 +6092,25 @@
         <v>46289</v>
       </c>
       <c r="B26" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C26" t="s">
         <v>1167</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>1168</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>1169</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>1170</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>1171</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>1172</v>
-      </c>
-      <c r="H26" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -6017,25 +6118,25 @@
         <v>46289</v>
       </c>
       <c r="B27" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C27" t="s">
         <v>1174</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>1175</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>1176</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>1177</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>1178</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>1179</v>
-      </c>
-      <c r="H27" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -6043,25 +6144,25 @@
         <v>46289</v>
       </c>
       <c r="B28" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C28" t="s">
         <v>1181</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>1182</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>1183</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>1184</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>1185</v>
       </c>
-      <c r="G28" t="s">
-        <v>1186</v>
-      </c>
       <c r="H28" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -6069,25 +6170,25 @@
         <v>46289</v>
       </c>
       <c r="B29" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C29" t="s">
         <v>1187</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>1188</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>1189</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>1190</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>1191</v>
       </c>
-      <c r="G29" t="s">
-        <v>1192</v>
-      </c>
       <c r="H29" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -6095,25 +6196,25 @@
         <v>46289</v>
       </c>
       <c r="B30" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C30" t="s">
         <v>1193</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>1194</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>1195</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>1196</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>1197</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>1198</v>
-      </c>
-      <c r="H30" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -6121,25 +6222,103 @@
         <v>46289</v>
       </c>
       <c r="B31" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C31" t="s">
         <v>1200</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>1201</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>1202</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>1203</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>1204</v>
       </c>
-      <c r="G31" t="s">
-        <v>1205</v>
-      </c>
       <c r="H31" t="s">
-        <v>1166</v>
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1227</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1234</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1236</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1241</v>
       </c>
     </row>
   </sheetData>
@@ -6495,10 +6674,10 @@
         <v>692</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
@@ -6509,10 +6688,10 @@
         <v>694</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>1122</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
@@ -6523,10 +6702,10 @@
         <v>696</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>1124</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
@@ -6537,10 +6716,10 @@
         <v>698</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
@@ -6551,10 +6730,10 @@
         <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
@@ -6565,10 +6744,10 @@
         <v>702</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="302.39999999999998" x14ac:dyDescent="0.3">
@@ -6579,10 +6758,10 @@
         <v>704</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="144" x14ac:dyDescent="0.3">
@@ -6593,10 +6772,10 @@
         <v>706</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="216" x14ac:dyDescent="0.3">
@@ -6607,10 +6786,10 @@
         <v>708</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
@@ -6621,10 +6800,10 @@
         <v>710</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
   </sheetData>
@@ -6767,10 +6946,10 @@
         <v>739</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="172.8" x14ac:dyDescent="0.3">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>740</v>
       </c>
@@ -6787,7 +6966,7 @@
         <v>741</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1066</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -6827,7 +7006,7 @@
         <v>750</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
@@ -6847,7 +7026,7 @@
         <v>754</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="288" x14ac:dyDescent="0.3">
@@ -6867,7 +7046,7 @@
         <v>757</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="187.2" x14ac:dyDescent="0.3">
@@ -6887,7 +7066,7 @@
         <v>760</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -6927,7 +7106,7 @@
         <v>768</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
@@ -6947,7 +7126,7 @@
         <v>771</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
@@ -6967,10 +7146,10 @@
         <v>775</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="230.4" x14ac:dyDescent="0.3">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>776</v>
       </c>
@@ -6987,7 +7166,7 @@
         <v>778</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1208</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
@@ -7007,7 +7186,7 @@
         <v>782</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="216" x14ac:dyDescent="0.3">
@@ -7027,15 +7206,15 @@
         <v>786</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B16" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C16" t="s">
         <v>737</v>
@@ -7044,10 +7223,10 @@
         <v>753</v>
       </c>
       <c r="E16" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="F16" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
@@ -7249,7 +7428,7 @@
         <v>818</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -7269,7 +7448,7 @@
         <v>103</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -7289,7 +7468,7 @@
         <v>826</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -7309,7 +7488,7 @@
         <v>829</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -7329,7 +7508,7 @@
         <v>833</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -7389,7 +7568,7 @@
         <v>152</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -7409,7 +7588,7 @@
         <v>157</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -7429,7 +7608,7 @@
         <v>849</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="358.8" x14ac:dyDescent="0.3">
@@ -8204,7 +8383,7 @@
         <v>54</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -8550,7 +8729,7 @@
         <v>117</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="479" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC2CE1DC-2AE1-4B04-8F07-DFB7DE1AF9E2}"/>
+  <xr:revisionPtr revIDLastSave="488" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA2E6E54-499A-4F3D-9BFB-909845D52E4D}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="1249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="1254">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3785,6 +3785,21 @@
   </si>
   <si>
     <t>Only TWO content items remain: the About story (CG-15) and the CV PDF file (CG-04). Then push, verify CHUNKS 14-16 against production, delete /styleguide, re-run Sheet 13 recruiter test.</t>
+  </si>
+  <si>
+    <t>CHUNKS 14-16 verified against LIVE PRODUCTION for the first time</t>
+  </si>
+  <si>
+    <t>Everything to date is pushed and deployed - origin/main and HEAD both at 3185f70. This is the first time the QA chunks have been checked against production rather than localhost, which was the standing blocker. Both case studies are publicly live and the stage coverage strip renders 4 of 7 and 7 of 7 respectively.</t>
+  </si>
+  <si>
+    <t>SECURITY: all 9 headers present on live responses - CSP (script-src self, no unsafe-inline), HSTS w/ preload, X-Content-Type-Options, X-Frame-Options DENY, Referrer-Policy, Permissions-Policy, COOP, CORP. ROUTES: all 6 return 200, unknown path returns 404. CONFIDENTIALITY on live HTML: ctbc, c.t.b.c, sbc, appraisal, appraiser, bank, lender, taiwan all CLEAN. The only "philippin" hits are his own location, which is his data, not a client's. SEO: canonical, description, full OG block and JSON-LD on every page; sitemap lists 6 URLs, no trailing slashes; robots correct. WEIGHT: 2.5-4.5 KB gzipped HTML per page, far inside the 350 KB budget. JS: theme-init plus ThemeToggle everywhere, DeliveryThread on case studies only - 2 islands, inside the cap of 4.</t>
+  </si>
+  <si>
+    <t>TWO FINDINGS, neither blocking. (1) /styleguide returns 200 on production - it is a dev-only route that CLAUDE.md says to delete before launch and HANDOFF records as deliberately retained. It is excluded from the sitemap and Disallowed in robots, but it is publicly reachable and a recruiter could land on it. Decision needed: delete now or at true launch. (2) /about is listed in the sitemap while carrying noindex, because its story is still [CONTENT REQUIRED]. astro.config flags this exact case for re-check at CHUNK 16. It resolves itself the moment CG-15 lands; no action needed unless the story is deferred.</t>
+  </si>
+  <si>
+    <t>CHUNKS 14, 15 and 16 stay REVIEW, not Complete: no Lighthouse run against production yet, rich-results not tested, /styleguide not deleted, and the Sheet 13 recruiter test has not been re-run since the content landed. Those four are what closes them.</t>
   </si>
 </sst>
 </file>
@@ -4792,7 +4807,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5376,45 +5391,71 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C23" s="11" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H24" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H25" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="488" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA2E6E54-499A-4F3D-9BFB-909845D52E4D}"/>
+  <xr:revisionPtr revIDLastSave="496" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FE719F1-06BD-4697-A4AA-3410036F63FD}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="1254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="1260">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3800,6 +3800,24 @@
   </si>
   <si>
     <t>CHUNKS 14, 15 and 16 stay REVIEW, not Complete: no Lighthouse run against production yet, rich-results not tested, /styleguide not deleted, and the Sheet 13 recruiter test has not been re-run since the content landed. Those four are what closes them.</t>
+  </si>
+  <si>
+    <t>D34</t>
+  </si>
+  <si>
+    <t>/styleguide is RETAINED for now, and the CHUNK 16 closeout tasks are deferred</t>
+  </si>
+  <si>
+    <t>(a) Delete /styleguide now and run the CHUNK 16 closeout; (b) retain it and defer both until the remaining content lands</t>
+  </si>
+  <si>
+    <t>(b) Retain and defer</t>
+  </si>
+  <si>
+    <t>The route is still useful while work continues, and deleting it now would remove the one page that renders the whole design system while two content items are still outstanding. It is already excluded from the sitemap and Disallowed in robots.</t>
+  </si>
+  <si>
+    <t>Low, but it is a KNOWN EXPOSURE, not an oversight: /styleguide returns 200 in production and a visitor can reach it directly. Accepted deliberately. It MUST still be deleted before the site is treated as launched - this decision defers the task, it does not cancel it.</t>
   </si>
 </sst>
 </file>
@@ -5465,7 +5483,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -6360,6 +6378,32 @@
       </c>
       <c r="H34" t="s">
         <v>1241</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1259</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1228</v>
       </c>
     </row>
   </sheetData>

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="496" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FE719F1-06BD-4697-A4AA-3410036F63FD}"/>
+  <xr:revisionPtr revIDLastSave="505" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C738CC4C-CD49-4610-B873-D4B6713F144B}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="1260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="1267">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3703,9 +3703,6 @@
     <t>His own account, in his own voice. Prompts offered: how he got from Junior Android Developer to Solutions Analyst; what kind of problem he enjoys most; what he does differently from someone who only writes code. Rough notes are enough - Claude writes the prose from them.</t>
   </si>
   <si>
-    <t>Open - ADDED 2026-09-24. This gap was being rendered on /about as a visible [CONTENT REQUIRED] but was never tracked on this sheet. Nobody but the owner can write it; a generated version reads exactly like one.</t>
-  </si>
-  <si>
     <t>D31</t>
   </si>
   <si>
@@ -3818,6 +3815,30 @@
   </si>
   <si>
     <t>Low, but it is a KNOWN EXPOSURE, not an oversight: /styleguide returns 200 in production and a visitor can reach it directly. Accepted deliberately. It MUST still be deleted before the site is treated as launched - this decision defers the task, it does not cancel it.</t>
+  </si>
+  <si>
+    <t>D35</t>
+  </si>
+  <si>
+    <t>The About paragraph states what he DOES; it deliberately claims no motivation</t>
+  </si>
+  <si>
+    <t>(a) Write a motivation from the sentence he affirmed; (b) write a factual paragraph from sourced material only; (c) leave /about blocked until he supplies his own words</t>
+  </si>
+  <si>
+    <t>(b) Factual, sourced only</t>
+  </si>
+  <si>
+    <t>He delegated the choice: "ill let you decide on this". Option (a) was rejected because the only motivation available is a sentence CLAUDE offered as an example and he repeated back verbatim - the same provenance failure as the on-device storage line in case study 1, and this time Claude caused it by supplying the example. A feeling cannot be sourced. Option (c) would have left the last content gap open indefinitely over a sentence that is not required. Option (b) says what he does, which is checkable, and needs no attestation beyond answers he has already given.</t>
+  </si>
+  <si>
+    <t>Closes CG-15 and lifts /about's noindex, which also resolves the sitemap-lists-a-noindexed-page finding from the production audit. The clause-by-clause source mapping is written into src/pages/about.astro above the string, so a future edit cannot quietly loosen it. If he later supplies the motivation in his own words it belongs as a FOURTH sentence, not as a rewrite of the three.</t>
+  </si>
+  <si>
+    <t>DELEGATED by owner, DECIDED by Claude 2026-09-24</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-24 (D35) - written from sourced material only. No motivation is claimed: the only one available was a Claude-supplied example he repeated back, so it was left out rather than published. Every clause traces to his CV or to an answer he gave, and the mapping is recorded in the page source. /about is now indexable.</t>
   </si>
 </sst>
 </file>
@@ -5391,19 +5412,19 @@
         <v>39</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>1244</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>1245</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="F22" s="11" t="s">
         <v>1246</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="G22" s="11" t="s">
         <v>1247</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>1248</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>34</v>
@@ -5417,19 +5438,19 @@
         <v>141</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>1249</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="E23" s="11" t="s">
         <v>1250</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="F23" s="11" t="s">
         <v>1251</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="G23" s="11" t="s">
         <v>1252</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>1253</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>1073</v>
@@ -5483,7 +5504,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -6307,25 +6328,25 @@
         <v>46289</v>
       </c>
       <c r="B32" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C32" t="s">
         <v>1222</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>1223</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>1224</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>1225</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>1226</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>1227</v>
-      </c>
-      <c r="H32" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -6333,25 +6354,25 @@
         <v>46289</v>
       </c>
       <c r="B33" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C33" t="s">
         <v>1229</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>1230</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>1231</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>1232</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>1233</v>
       </c>
-      <c r="G33" t="s">
-        <v>1234</v>
-      </c>
       <c r="H33" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -6359,25 +6380,25 @@
         <v>46289</v>
       </c>
       <c r="B34" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C34" t="s">
         <v>1235</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>1236</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>1237</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>1238</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>1239</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>1240</v>
-      </c>
-      <c r="H34" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -6385,25 +6406,51 @@
         <v>46289</v>
       </c>
       <c r="B35" t="s">
+        <v>1253</v>
+      </c>
+      <c r="C35" t="s">
         <v>1254</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>1255</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>1256</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>1257</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>1258</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B36" t="s">
         <v>1259</v>
       </c>
-      <c r="H35" t="s">
-        <v>1228</v>
+      <c r="C36" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1263</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1265</v>
       </c>
     </row>
   </sheetData>
@@ -7051,7 +7098,7 @@
         <v>741</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -7251,7 +7298,7 @@
         <v>778</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
@@ -7311,7 +7358,7 @@
         <v>1220</v>
       </c>
       <c r="F16" t="s">
-        <v>1221</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="505" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C738CC4C-CD49-4610-B873-D4B6713F144B}"/>
+  <xr:revisionPtr revIDLastSave="528" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69837D4E-43F8-4CC9-8A74-4783D016D692}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="1267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="1270">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3400,42 +3400,12 @@
     <t>Push, then confirm canonical/sitemap/OG on the production URL. Then CHUNK 16 final review.</t>
   </si>
   <si>
-    <t>Name and role in the hero, above the fold at 375px.</t>
-  </si>
-  <si>
     <t>Partial</t>
   </si>
   <si>
-    <t>The role line is there, but the POSITIONING LINE IS MISSING (CG-09, question B2). A recruiter gets the job title and not the differentiator. Blocks a Pass.</t>
-  </si>
-  <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>No case studies exist (CG-01, CG-02). /work renders an honest empty state. Nothing is placeheld, which is correct, but the question is unanswered.</t>
-  </si>
-  <si>
-    <t>The machinery is built and schema-enforced - myRole is .min(1) and an empty value fails the build - but there is no content in it.</t>
-  </si>
-  <si>
-    <t>THE MOST IMPORTANT QUESTION ON THIS SHEET, and it is entirely content-dependent. The VAPT triage story would answer it strongly once written.</t>
-  </si>
-  <si>
-    <t>The Delivery Thread states the claim but no case study evidences it. The CASECenter case study is the one designed to answer this.</t>
-  </si>
-  <si>
-    <t>24 skills in 6 categories are live from the CV, with no proficiency bars. But EVERY evidence array is empty, so nothing is verifiable by clicking - which is the whole mechanism that was supposed to replace percentages.</t>
-  </si>
-  <si>
-    <t>Full timeline live on /about - 4 roles plus education, transcribed exactly from the CV, scannable in seconds.</t>
-  </si>
-  <si>
-    <t>LinkedIn is live and reachable in one click from every page. NO EMAIL is published pending question B5 - deliberately, because publishing an address is irreversible.</t>
-  </si>
-  <si>
-    <t>No resume PDF (CG-04, question B7). The Resume button correctly does not render rather than 404ing, but the recruiter cannot get a CV.</t>
-  </si>
-  <si>
     <t>JSON-LD Person schema parses and validates. Verified NOT blocked by script-src self using the new header-serving harness. Note: Person is not a rich-result-eligible type, so a Rich Results Test reporting none is expected, not a failure.</t>
   </si>
   <si>
@@ -3839,6 +3809,45 @@
   </si>
   <si>
     <t>CLOSED 2026-09-24 (D35) - written from sourced material only. No motivation is claimed: the only one available was a Claude-supplied example he repeated back, so it was left out rather than published. Every clause traces to his CV or to an answer he gave, and the mapping is recorded in the page source. /about is now indexable.</t>
+  </si>
+  <si>
+    <t>Re-run 2026-09-24. Unchanged and still passing: name in the h1, role line directly beneath, both above the fold at 375px.</t>
+  </si>
+  <si>
+    <t>WAS PARTIAL. The positioning line landed 2026-09-24 (D25): "I turn business requirements into enterprise systems - and stay with them through testing, UAT, release and production support." It also feeds the meta and OG description, so it is the first thing a search result or a shared link shows. The [CONTENT REQUIRED] marker that used to sit here is gone and the home page is no longer noindex.</t>
+  </si>
+  <si>
+    <t>WAS FAIL. Two case studies are published and listed on /work, each with problem, my role, outcome and stack on the card itself - a recruiter gets the evidence block without clicking. One is Android security remediation from the previous role; one is end-to-end enterprise delivery from the current role.</t>
+  </si>
+  <si>
+    <t>WAS FAIL. myRole is elevated into the case study header rather than buried mid-page, and it is schema-enforced at .min(1) so it cannot be omitted. Both entries state the boundary of his ownership explicitly: case study 1 says a separate team owned the web platform and that he did not build the application he maintains; case study 2 says the delivery was his end to end.</t>
+  </si>
+  <si>
+    <t>WAS FAIL - and this sheet recorded it as the most important question on it. Case study 1 is exactly this: the ordinary remedy (upgrade the dependency) was not available, so each finding had to be assessed on its own terms and closed in application code instead. It is judgement under constraint, and the outcome was confirmed by the client's own re-scan rather than by his say-so.</t>
+  </si>
+  <si>
+    <t>WAS FAIL. Case study 2 covers it directly: requirements developed from the client BRD and PRD, policy logic built from them, and his own stated practice of pushing back to get an unsettled document resolved BEFORE building rather than absorbing the changes later. The new StageCoverage strip shows 7 of 7 delivery stages on that project against 4 of 7 on the other - the span is shown, not asserted.</t>
+  </si>
+  <si>
+    <t>WAS PARTIAL, and this re-run is what fixed it. 24 skills were live but EVERY evidence array was empty, so /about rendered zero links - the page promised "evidence links replace proficiency bars" and delivered none. 11 skills now link to the case study that demonstrates them. The other 13 stay plain text deliberately. Links checked: 11 rendered, both targets resolve, no 404s. Some were deliberately NOT linked despite being easy - REST API design (the case study never discusses API design), Java (that application has no case study), Agile and cross-team coordination (never described).</t>
+  </si>
+  <si>
+    <t>Re-run 2026-09-24. Unchanged. Full timeline on /about - 3 roles plus education, reverse chronological, with an experience teaser on the home page.</t>
+  </si>
+  <si>
+    <t>WAS PARTIAL. Email published 2026-09-24 (D26) - the address already on his CV, so already public. Live mailto on /contact alongside LinkedIn. GitHub is deliberately absent (D27) rather than pending. Both pending notices are gone from the page.</t>
+  </si>
+  <si>
+    <t>STILL FAILING, and it is now the ONLY failure on this sheet. Publication was approved 2026-09-24 (D29) but the file has never been supplied. The Resume button correctly does not render in the header or on /contact, because shipping a button that 404s would fail this question harder than its absence does. Drop the file at public/raymund-bermudes-cv.pdf and it appears on the next build with no code change.</t>
+  </si>
+  <si>
+    <t>RE-RUN 2026-09-24</t>
+  </si>
+  <si>
+    <t>Score: 9 Pass / 0 Partial / 1 Fail. Previous run 2026-09-23: 2 Pass / 3 Partial / 5 Fail.</t>
+  </si>
+  <si>
+    <t>Every previously failing question was content, not code, and the content has now landed. The single remaining failure is the resume PDF, which is a file the owner has not supplied - there is nothing to build. This re-run also SURFACED A REAL DEFECT rather than just scoring: question 8 was passing on paper because 24 skills were listed, while the evidence links the page advertises were all empty. That is now fixed.</t>
   </si>
 </sst>
 </file>
@@ -4598,7 +4607,7 @@
         <v>1096</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>1142</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="345.6" x14ac:dyDescent="0.3">
@@ -4615,7 +4624,7 @@
         <v>1096</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>1138</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
@@ -4632,7 +4641,7 @@
         <v>1096</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
@@ -4649,7 +4658,7 @@
         <v>1096</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>1136</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="360" x14ac:dyDescent="0.3">
@@ -4666,7 +4675,7 @@
         <v>1096</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>1135</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -4683,7 +4692,7 @@
         <v>1096</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1134</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
@@ -4700,7 +4709,7 @@
         <v>1096</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>1133</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="316.8" x14ac:dyDescent="0.3">
@@ -4717,7 +4726,7 @@
         <v>1096</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>1132</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="216" x14ac:dyDescent="0.3">
@@ -4734,7 +4743,7 @@
         <v>1096</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>1141</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="230.4" x14ac:dyDescent="0.3">
@@ -4751,7 +4760,7 @@
         <v>1096</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>1140</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="244.8" x14ac:dyDescent="0.3">
@@ -4768,7 +4777,7 @@
         <v>1096</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>1139</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
@@ -4782,10 +4791,10 @@
         <v>540</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>1143</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
@@ -4799,10 +4808,10 @@
         <v>542</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>1144</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -4816,10 +4825,10 @@
         <v>544</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>1145</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
@@ -4833,10 +4842,10 @@
         <v>546</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>1146</v>
+        <v>1136</v>
       </c>
     </row>
   </sheetData>
@@ -5334,19 +5343,19 @@
         <v>170</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1147</v>
+        <v>1137</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>1148</v>
+        <v>1138</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>1149</v>
+        <v>1139</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>1150</v>
+        <v>1140</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>1151</v>
+        <v>1141</v>
       </c>
       <c r="H19" s="11" t="s">
         <v>1073</v>
@@ -5360,19 +5369,19 @@
         <v>39</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>1154</v>
+        <v>1144</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>1155</v>
+        <v>1145</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>1156</v>
+        <v>1146</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>1157</v>
+        <v>1147</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>1158</v>
+        <v>1148</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>1073</v>
@@ -5386,19 +5395,19 @@
         <v>39</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1213</v>
+        <v>1203</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>1214</v>
+        <v>1204</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>1215</v>
+        <v>1205</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>1216</v>
+        <v>1206</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>1217</v>
+        <v>1207</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>34</v>
@@ -5412,19 +5421,19 @@
         <v>39</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1243</v>
+        <v>1233</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>1244</v>
+        <v>1234</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>1245</v>
+        <v>1235</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>1246</v>
+        <v>1236</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>1247</v>
+        <v>1237</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>34</v>
@@ -5438,19 +5447,19 @@
         <v>141</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>1248</v>
+        <v>1238</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>1249</v>
+        <v>1239</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>1250</v>
+        <v>1240</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>1251</v>
+        <v>1241</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>1252</v>
+        <v>1242</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>1073</v>
@@ -6146,25 +6155,25 @@
         <v>46289</v>
       </c>
       <c r="B25" t="s">
-        <v>1159</v>
+        <v>1149</v>
       </c>
       <c r="C25" t="s">
-        <v>1160</v>
+        <v>1150</v>
       </c>
       <c r="D25" t="s">
-        <v>1161</v>
+        <v>1151</v>
       </c>
       <c r="E25" t="s">
-        <v>1162</v>
+        <v>1152</v>
       </c>
       <c r="F25" t="s">
-        <v>1163</v>
+        <v>1153</v>
       </c>
       <c r="G25" t="s">
-        <v>1164</v>
+        <v>1154</v>
       </c>
       <c r="H25" t="s">
-        <v>1165</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
@@ -6172,25 +6181,25 @@
         <v>46289</v>
       </c>
       <c r="B26" t="s">
-        <v>1166</v>
+        <v>1156</v>
       </c>
       <c r="C26" t="s">
-        <v>1167</v>
+        <v>1157</v>
       </c>
       <c r="D26" t="s">
-        <v>1168</v>
+        <v>1158</v>
       </c>
       <c r="E26" t="s">
-        <v>1169</v>
+        <v>1159</v>
       </c>
       <c r="F26" t="s">
-        <v>1170</v>
+        <v>1160</v>
       </c>
       <c r="G26" t="s">
-        <v>1171</v>
+        <v>1161</v>
       </c>
       <c r="H26" t="s">
-        <v>1172</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
@@ -6198,25 +6207,25 @@
         <v>46289</v>
       </c>
       <c r="B27" t="s">
-        <v>1173</v>
+        <v>1163</v>
       </c>
       <c r="C27" t="s">
-        <v>1174</v>
+        <v>1164</v>
       </c>
       <c r="D27" t="s">
-        <v>1175</v>
+        <v>1165</v>
       </c>
       <c r="E27" t="s">
-        <v>1176</v>
+        <v>1166</v>
       </c>
       <c r="F27" t="s">
-        <v>1177</v>
+        <v>1167</v>
       </c>
       <c r="G27" t="s">
-        <v>1178</v>
+        <v>1168</v>
       </c>
       <c r="H27" t="s">
-        <v>1179</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
@@ -6224,25 +6233,25 @@
         <v>46289</v>
       </c>
       <c r="B28" t="s">
-        <v>1180</v>
+        <v>1170</v>
       </c>
       <c r="C28" t="s">
-        <v>1181</v>
+        <v>1171</v>
       </c>
       <c r="D28" t="s">
-        <v>1182</v>
+        <v>1172</v>
       </c>
       <c r="E28" t="s">
-        <v>1183</v>
+        <v>1173</v>
       </c>
       <c r="F28" t="s">
-        <v>1184</v>
+        <v>1174</v>
       </c>
       <c r="G28" t="s">
-        <v>1185</v>
+        <v>1175</v>
       </c>
       <c r="H28" t="s">
-        <v>1165</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
@@ -6250,25 +6259,25 @@
         <v>46289</v>
       </c>
       <c r="B29" t="s">
-        <v>1186</v>
+        <v>1176</v>
       </c>
       <c r="C29" t="s">
-        <v>1187</v>
+        <v>1177</v>
       </c>
       <c r="D29" t="s">
-        <v>1188</v>
+        <v>1178</v>
       </c>
       <c r="E29" t="s">
-        <v>1189</v>
+        <v>1179</v>
       </c>
       <c r="F29" t="s">
-        <v>1190</v>
+        <v>1180</v>
       </c>
       <c r="G29" t="s">
-        <v>1191</v>
+        <v>1181</v>
       </c>
       <c r="H29" t="s">
-        <v>1165</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -6276,25 +6285,25 @@
         <v>46289</v>
       </c>
       <c r="B30" t="s">
-        <v>1192</v>
+        <v>1182</v>
       </c>
       <c r="C30" t="s">
-        <v>1193</v>
+        <v>1183</v>
       </c>
       <c r="D30" t="s">
-        <v>1194</v>
+        <v>1184</v>
       </c>
       <c r="E30" t="s">
-        <v>1195</v>
+        <v>1185</v>
       </c>
       <c r="F30" t="s">
-        <v>1196</v>
+        <v>1186</v>
       </c>
       <c r="G30" t="s">
-        <v>1197</v>
+        <v>1187</v>
       </c>
       <c r="H30" t="s">
-        <v>1198</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -6302,25 +6311,25 @@
         <v>46289</v>
       </c>
       <c r="B31" t="s">
-        <v>1199</v>
+        <v>1189</v>
       </c>
       <c r="C31" t="s">
-        <v>1200</v>
+        <v>1190</v>
       </c>
       <c r="D31" t="s">
-        <v>1201</v>
+        <v>1191</v>
       </c>
       <c r="E31" t="s">
-        <v>1202</v>
+        <v>1192</v>
       </c>
       <c r="F31" t="s">
-        <v>1203</v>
+        <v>1193</v>
       </c>
       <c r="G31" t="s">
-        <v>1204</v>
+        <v>1194</v>
       </c>
       <c r="H31" t="s">
-        <v>1165</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -6328,25 +6337,25 @@
         <v>46289</v>
       </c>
       <c r="B32" t="s">
-        <v>1221</v>
+        <v>1211</v>
       </c>
       <c r="C32" t="s">
-        <v>1222</v>
+        <v>1212</v>
       </c>
       <c r="D32" t="s">
-        <v>1223</v>
+        <v>1213</v>
       </c>
       <c r="E32" t="s">
-        <v>1224</v>
+        <v>1214</v>
       </c>
       <c r="F32" t="s">
-        <v>1225</v>
+        <v>1215</v>
       </c>
       <c r="G32" t="s">
-        <v>1226</v>
+        <v>1216</v>
       </c>
       <c r="H32" t="s">
-        <v>1227</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -6354,25 +6363,25 @@
         <v>46289</v>
       </c>
       <c r="B33" t="s">
-        <v>1228</v>
+        <v>1218</v>
       </c>
       <c r="C33" t="s">
-        <v>1229</v>
+        <v>1219</v>
       </c>
       <c r="D33" t="s">
-        <v>1230</v>
+        <v>1220</v>
       </c>
       <c r="E33" t="s">
-        <v>1231</v>
+        <v>1221</v>
       </c>
       <c r="F33" t="s">
-        <v>1232</v>
+        <v>1222</v>
       </c>
       <c r="G33" t="s">
-        <v>1233</v>
+        <v>1223</v>
       </c>
       <c r="H33" t="s">
-        <v>1227</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -6380,25 +6389,25 @@
         <v>46289</v>
       </c>
       <c r="B34" t="s">
-        <v>1234</v>
+        <v>1224</v>
       </c>
       <c r="C34" t="s">
-        <v>1235</v>
+        <v>1225</v>
       </c>
       <c r="D34" t="s">
-        <v>1236</v>
+        <v>1226</v>
       </c>
       <c r="E34" t="s">
-        <v>1237</v>
+        <v>1227</v>
       </c>
       <c r="F34" t="s">
-        <v>1238</v>
+        <v>1228</v>
       </c>
       <c r="G34" t="s">
-        <v>1239</v>
+        <v>1229</v>
       </c>
       <c r="H34" t="s">
-        <v>1240</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -6406,25 +6415,25 @@
         <v>46289</v>
       </c>
       <c r="B35" t="s">
-        <v>1253</v>
+        <v>1243</v>
       </c>
       <c r="C35" t="s">
-        <v>1254</v>
+        <v>1244</v>
       </c>
       <c r="D35" t="s">
-        <v>1255</v>
+        <v>1245</v>
       </c>
       <c r="E35" t="s">
-        <v>1256</v>
+        <v>1246</v>
       </c>
       <c r="F35" t="s">
-        <v>1257</v>
+        <v>1247</v>
       </c>
       <c r="G35" t="s">
-        <v>1258</v>
+        <v>1248</v>
       </c>
       <c r="H35" t="s">
-        <v>1227</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -6432,25 +6441,25 @@
         <v>46289</v>
       </c>
       <c r="B36" t="s">
-        <v>1259</v>
+        <v>1249</v>
       </c>
       <c r="C36" t="s">
-        <v>1260</v>
+        <v>1250</v>
       </c>
       <c r="D36" t="s">
-        <v>1261</v>
+        <v>1251</v>
       </c>
       <c r="E36" t="s">
-        <v>1262</v>
+        <v>1252</v>
       </c>
       <c r="F36" t="s">
-        <v>1263</v>
+        <v>1253</v>
       </c>
       <c r="G36" t="s">
-        <v>1264</v>
+        <v>1254</v>
       </c>
       <c r="H36" t="s">
-        <v>1265</v>
+        <v>1255</v>
       </c>
     </row>
   </sheetData>
@@ -6776,7 +6785,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -6798,7 +6807,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>691</v>
       </c>
@@ -6809,10 +6818,10 @@
         <v>1096</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>693</v>
       </c>
@@ -6820,13 +6829,13 @@
         <v>694</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1121</v>
+        <v>1096</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>695</v>
       </c>
@@ -6834,13 +6843,13 @@
         <v>696</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1123</v>
+        <v>1096</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>697</v>
       </c>
@@ -6848,13 +6857,13 @@
         <v>698</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1123</v>
+        <v>1096</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="201.6" x14ac:dyDescent="0.3">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>699</v>
       </c>
@@ -6862,13 +6871,13 @@
         <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1123</v>
+        <v>1096</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>701</v>
       </c>
@@ -6876,13 +6885,13 @@
         <v>702</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1123</v>
+        <v>1096</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="302.39999999999998" x14ac:dyDescent="0.3">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>703</v>
       </c>
@@ -6890,13 +6899,13 @@
         <v>704</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1121</v>
+        <v>1096</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>705</v>
       </c>
@@ -6907,10 +6916,10 @@
         <v>1096</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="216" x14ac:dyDescent="0.3">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>707</v>
       </c>
@@ -6918,13 +6927,13 @@
         <v>708</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1121</v>
+        <v>1096</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>709</v>
       </c>
@@ -6932,10 +6941,21 @@
         <v>710</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1131</v>
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1269</v>
       </c>
     </row>
   </sheetData>
@@ -7078,7 +7098,7 @@
         <v>739</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>1152</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="409.6" x14ac:dyDescent="0.3">
@@ -7098,7 +7118,7 @@
         <v>741</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1241</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -7138,7 +7158,7 @@
         <v>750</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1212</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
@@ -7178,7 +7198,7 @@
         <v>757</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>1211</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="187.2" x14ac:dyDescent="0.3">
@@ -7198,7 +7218,7 @@
         <v>760</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>1210</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
@@ -7238,7 +7258,7 @@
         <v>768</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>1209</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
@@ -7258,7 +7278,7 @@
         <v>771</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1208</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
@@ -7278,7 +7298,7 @@
         <v>775</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1207</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="273.60000000000002" x14ac:dyDescent="0.3">
@@ -7298,7 +7318,7 @@
         <v>778</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1242</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
@@ -7318,7 +7338,7 @@
         <v>782</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>1206</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="216" x14ac:dyDescent="0.3">
@@ -7338,15 +7358,15 @@
         <v>786</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1205</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1218</v>
+        <v>1208</v>
       </c>
       <c r="B16" t="s">
-        <v>1219</v>
+        <v>1209</v>
       </c>
       <c r="C16" t="s">
         <v>737</v>
@@ -7355,10 +7375,10 @@
         <v>753</v>
       </c>
       <c r="E16" t="s">
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="F16" t="s">
-        <v>1266</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
@@ -8515,7 +8535,7 @@
         <v>54</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>1153</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">

--- a/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
+++ b/Raymund_Portfolio_PRD_Progress_Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gdslink-my.sharepoint.com/personal/raymund_bermudes_gdslinkasia_com/Documents/Documents/Rr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="528" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69837D4E-43F8-4CC9-8A74-4783D016D692}"/>
+  <xr:revisionPtr revIDLastSave="542" documentId="13_ncr:1_{E42DE829-FADD-499D-AC40-0688BE14A681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64024C48-B321-4601-BC42-758949273574}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="1270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1845" uniqueCount="1276">
   <si>
     <t>Portfolio Project PRD &amp; Progress Tracker</t>
   </si>
@@ -3646,9 +3646,6 @@
     <t>CLOSED 2026-09-24 (D28) - owner reviewed all 24 entries against "only what you would defend in an interview" and struck nothing. SKILLS_CONFIRMED = true; the [VERIFY INFORMATION] note is removed from /about. WARNING: this covers only the entries present at that date. Adding a skill later is a NEW claim.</t>
   </si>
   <si>
-    <t>APPROVED 2026-09-24 (D29) - publication cleared by owner. FILE NOT SUPPLIED, so the gap stays OPEN. Drop it at public/raymund-bermudes-cv.pdf and the Resume button appears in the header and on /contact on the next build - no code change needed.</t>
-  </si>
-  <si>
     <t>Answer sheet cleared - D24 to D30</t>
   </si>
   <si>
@@ -3838,16 +3835,37 @@
     <t>WAS PARTIAL. Email published 2026-09-24 (D26) - the address already on his CV, so already public. Live mailto on /contact alongside LinkedIn. GitHub is deliberately absent (D27) rather than pending. Both pending notices are gone from the page.</t>
   </si>
   <si>
-    <t>STILL FAILING, and it is now the ONLY failure on this sheet. Publication was approved 2026-09-24 (D29) but the file has never been supplied. The Resume button correctly does not render in the header or on /contact, because shipping a button that 404s would fail this question harder than its absence does. Drop the file at public/raymund-bermudes-cv.pdf and it appears on the next build with no code change.</t>
-  </si>
-  <si>
     <t>RE-RUN 2026-09-24</t>
   </si>
   <si>
-    <t>Score: 9 Pass / 0 Partial / 1 Fail. Previous run 2026-09-23: 2 Pass / 3 Partial / 5 Fail.</t>
-  </si>
-  <si>
-    <t>Every previously failing question was content, not code, and the content has now landed. The single remaining failure is the resume PDF, which is a file the owner has not supplied - there is nothing to build. This re-run also SURFACED A REAL DEFECT rather than just scoring: question 8 was passing on paper because 24 skills were listed, while the evidence links the page advertises were all empty. That is now fixed.</t>
+    <t>WAS THE LAST FAILURE ON THIS SHEET. The PDF was supplied 2026-09-25 and is live at /raymund-bermudes-cv.pdf. The Resume button now renders in the header on every page, in the footer, and as a download link on /contact. 5.8 KB. Read in full before publishing: it contains NO phone number, NO home address and NO identity numbers, so it exposes nothing beyond what the site already publishes - name, city, the same email (D26) and the same LinkedIn. No restricted client name appears in it either.</t>
+  </si>
+  <si>
+    <t>Score: 10 Pass / 0 Partial / 0 Fail. Earlier runs: 9/0/1 on 2026-09-24, and 2 Pass / 3 Partial / 5 Fail on 2026-09-23.</t>
+  </si>
+  <si>
+    <t>FULL PASS 2026-09-25. Every question a recruiter needs answered in one short visit is now answered. Each of the eight questions that were failing or partial on 2026-09-23 was CONTENT, not code, and all of that content has landed: two case studies, the positioning line, the About story, the confirmed skills list with evidence links, the published email, and now the resume. The re-run on 2026-09-24 also surfaced a real defect rather than just scoring - question 8 looked fine on a list count while the evidence links the page advertises were all empty.</t>
+  </si>
+  <si>
+    <t>CLOSED 2026-09-25 - file supplied and published at public/raymund-bermudes-cv.pdf. Approved under D29; this closes the FILE half that D29 left open. Read in full before publishing: no phone number, no home address, no identity numbers, no restricted client names. It exposes nothing the site does not already publish. THIS WAS THE LAST OPEN CONTENT GAP.</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>Resume published - the last content gap closes, recruiter test goes 10/10</t>
+  </si>
+  <si>
+    <t>CV PDF supplied and published at public/raymund-bermudes-cv.pdf. The Resume button now renders in the header on every page, in the footer, and as a download link on /contact - all three appeared with no code change, because the components were already written to hide the button while the file was absent rather than ship one that 404s. ZERO [CONTENT REQUIRED] or [VERIFY INFORMATION] markers now remain anywhere in the built site.</t>
+  </si>
+  <si>
+    <t>npm run verify exit 0, 22/22 guards, astro check 0/0/1, 7 pages. PDF present in dist at 5826 bytes. Sheet 13 re-scored to 10 Pass / 0 Partial / 0 Fail.</t>
+  </si>
+  <si>
+    <t>PRE-PUBLICATION CHECK: the PDF was read in full before being copied in, because publishing puts it in front of scrapers permanently. It contains no phone number, no home address and no identity numbers; the only contact details are the same email and LinkedIn already published on /contact. No restricted client name appears. ONE INCONSISTENCY WORTH THE OWNER KNOWING: the CV summary says he drives "full system lifecycle delivery from DESIGN through production", while the site dropped Design from the delivery stages under D24 on his own statement that he does not own design work. Probably just loose CV wording meaning technical design rather than UI design - but CLAUDE.md's founding rule is that the portfolio must not contradict the CV attached to it, so either the CV line is loose or D24 is wrong. His call.</t>
+  </si>
+  <si>
+    <t>No content work remains. To close CHUNKS 14-16 fully: Lighthouse against production and the rich-results test. Neither is blocked.</t>
   </si>
 </sst>
 </file>
@@ -4855,7 +4873,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5395,19 +5413,19 @@
         <v>39</v>
       </c>
       <c r="C21" s="11" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>1203</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="E21" s="11" t="s">
         <v>1204</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="F21" s="11" t="s">
         <v>1205</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="G21" s="11" t="s">
         <v>1206</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>1207</v>
       </c>
       <c r="H21" s="11" t="s">
         <v>34</v>
@@ -5421,19 +5439,19 @@
         <v>39</v>
       </c>
       <c r="C22" s="11" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>1233</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="E22" s="11" t="s">
         <v>1234</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="F22" s="11" t="s">
         <v>1235</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="G22" s="11" t="s">
         <v>1236</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>1237</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>34</v>
@@ -5447,63 +5465,89 @@
         <v>141</v>
       </c>
       <c r="C23" s="11" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>1238</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="E23" s="11" t="s">
         <v>1239</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="F23" s="11" t="s">
         <v>1240</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="G23" s="11" t="s">
         <v>1241</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>1242</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>1073</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>48</v>
       </c>
     </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H25" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H26" xr:uid="{00000000-0002-0000-0A00-000000000000}">
       <formula1>"Not Started,In Progress,Blocked,Review,Complete,On Hold"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6337,25 +6381,25 @@
         <v>46289</v>
       </c>
       <c r="B32" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C32" t="s">
         <v>1211</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>1212</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>1213</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>1214</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>1215</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>1216</v>
-      </c>
-      <c r="H32" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -6363,25 +6407,25 @@
         <v>46289</v>
       </c>
       <c r="B33" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C33" t="s">
         <v>1218</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>1219</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>1220</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>1221</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>1222</v>
       </c>
-      <c r="G33" t="s">
-        <v>1223</v>
-      </c>
       <c r="H33" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -6389,25 +6433,25 @@
         <v>46289</v>
       </c>
       <c r="B34" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C34" t="s">
         <v>1224</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>1225</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>1226</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>1227</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>1228</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>1229</v>
-      </c>
-      <c r="H34" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -6415,25 +6459,25 @@
         <v>46289</v>
       </c>
       <c r="B35" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C35" t="s">
         <v>1243</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>1244</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>1245</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>1246</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>1247</v>
       </c>
-      <c r="G35" t="s">
-        <v>1248</v>
-      </c>
       <c r="H35" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -6441,25 +6485,25 @@
         <v>46289</v>
       </c>
       <c r="B36" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C36" t="s">
         <v>1249</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>1250</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>1251</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>1252</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>1253</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>1254</v>
-      </c>
-      <c r="H36" t="s">
-        <v>1255</v>
       </c>
     </row>
   </sheetData>
@@ -6818,7 +6862,7 @@
         <v>1096</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
@@ -6832,7 +6876,7 @@
         <v>1096</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="403.2" x14ac:dyDescent="0.3">
@@ -6846,7 +6890,7 @@
         <v>1096</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
@@ -6860,7 +6904,7 @@
         <v>1096</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
@@ -6874,7 +6918,7 @@
         <v>1096</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
@@ -6888,7 +6932,7 @@
         <v>1096</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
@@ -6902,7 +6946,7 @@
         <v>1096</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
@@ -6916,7 +6960,7 @@
         <v>1096</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="345.6" x14ac:dyDescent="0.3">
@@ -6930,7 +6974,7 @@
         <v>1096</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
@@ -6941,7 +6985,7 @@
         <v>710</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1121</v>
+        <v>1096</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>1266</v>
@@ -6949,13 +6993,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B13" t="s">
         <v>1267</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" t="s">
         <v>1268</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1269</v>
       </c>
     </row>
   </sheetData>
@@ -7118,7 +7162,7 @@
         <v>741</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -7141,7 +7185,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>747</v>
       </c>
@@ -7158,7 +7202,7 @@
         <v>750</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1202</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
@@ -7318,7 +7362,7 @@
         <v>778</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
@@ -7363,10 +7407,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B16" t="s">
         <v>1208</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1209</v>
       </c>
       <c r="C16" t="s">
         <v>737</v>
@@ -7375,10 +7419,10 @@
         <v>753</v>
       </c>
       <c r="E16" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="276" x14ac:dyDescent="0.3">
